--- a/docs/wip/ICTU-Kwaliteitsaanpak-Checklist.xlsx
+++ b/docs/wip/ICTU-Kwaliteitsaanpak-Checklist.xlsx
@@ -436,7 +436,7 @@
 6. maken van testrapportages: JUnit, Robot Framework, TestNG, of hiermee compatible tools,
 7. maken van kwaliteitsrapportages: Quality-time,
 8. controleren van de configuratie op aanwezigheid van bekende kwetsbaarheden in configuratie: OpenVAS (Vulnerability Assessment System),
-9. controleren op aanwezigheid van bekende kwetsbaarheden in externe software: OWASP (Open Web Application Security Project) Dependency Checker en/of Dependency-Track,
+9. controleren op aanwezigheid van bekende kwetsbaarheden in externe software: OWASP (Open Web Application Security Project) Dependency-Check en/of Dependency-Track,
 10. statische controle van de software op aanwezigheid van kwetsbare constructies: SonarQube,
 11. dynamische controle van de software op aanwezigheid van kwetsbare constructies: OWASP ZAP (Zed Attack Proxy),
 12. controleren van container images op aanwezigheid van bekende kwetsbaarheden: Trivy,
@@ -884,7 +884,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="146">
   <si>
-    <t>Onderstaande checklist kan gebruikt worden voor het uitvoeren van een assessment tegen de ICTU Kwaliteitsaanpak Softwareontwikkeling versie wip, 26-04-2024.</t>
+    <t>Onderstaande checklist kan gebruikt worden voor het uitvoeren van een assessment tegen de ICTU Kwaliteitsaanpak Softwareontwikkeling versie wip, 10-06-2024.</t>
   </si>
   <si>
     <t>Gebruik de 'Status' kolom om aan te geven in hoeverre een maatregel uit de Kwaliteitsaanpak is toegepast. Bij maatregelen met submaatregelen hoeft alleen de status van de submaatregelen te worden ingevuld.</t>
@@ -1115,7 +1115,7 @@
     <t>8. controleren van de configuratie op aanwezigheid van bekende kwetsbaarheden in configuratie: OpenVAS (Vulnerability Assessment System),</t>
   </si>
   <si>
-    <t>9. controleren op aanwezigheid van bekende kwetsbaarheden in externe software: OWASP (Open Web Application Security Project) Dependency Checker en/of Dependency-Track,</t>
+    <t>9. controleren op aanwezigheid van bekende kwetsbaarheden in externe software: OWASP (Open Web Application Security Project) Dependency-Check en/of Dependency-Track,</t>
   </si>
   <si>
     <t>10. statische controle van de software op aanwezigheid van kwetsbare constructies: SonarQube,</t>
@@ -1418,7 +1418,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1" wrapText="1"/>
+      <alignment vertical="top" indent="1" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" indent="1" wrapText="1"/>

--- a/docs/wip/ICTU-Kwaliteitsaanpak-Checklist.xlsx
+++ b/docs/wip/ICTU-Kwaliteitsaanpak-Checklist.xlsx
@@ -157,7 +157,7 @@
 - Template infrastructuurarchitectuur.
 Testplannen en -rapportages
 De testplannen bestaan uit een mastertestplan (MTP), gemaakt op basis van een productrisicoanalyse (PRA), en detailtestplannen. Het doel van een mastertestplan is om betrokkenen bij het testproces te informeren over de strategie, aanpak, activiteiten, inclusief de onderlinge relaties en afhankelijkheden, en de op te leveren producten met betrekking tot het testtraject. Het mastertestplan beschrijft deze strategie, aanpak, activiteiten en eindproducten, die in de detailtestplannen verder worden gedetailleerd.
-De opdrachtgevende organisatie is verantwoordelijk voor het mastertestplan. Het project maakt een detailtestplan voor de testsoorten die tijdens de realisatiefase door het project worden uitgevoerd. Voor testen die onder verantwoordelijkheid van het project door een derde partij worden uitgevoerd, denk aan penetratietesten en evaluaties van gebruikskwaliteit, worden aparte detailtestplannen gemaakt.
+De opdrachtgevende organisatie is verantwoordelijk voor het mastertestplan. Het project maakt een detailtestplan voor de testsoorten die tijdens de realisatiefase door het project worden uitgevoerd. Voor testen die onder verantwoordelijkheid van het project door een derde partij worden uitgevoerd, denk aan penetratietesten en evaluaties van gebruikskwaliteit, worden aparte detailtestplannen gemaakt. Deze hebben doorgaans de vorm van een offerteaanvraag gemaakt door ICTU en een offerte met plan van aanpak gemaakt door de leverancier.
 Logische testgevallen worden vastgelegd en gekoppeld met use cases en user stories. Fysieke testgevallen worden vastgelegd in het formaat van de gebruikte tooling en gekoppeld met de logische testgevallen. Op basis hiervan worden testrapportages gegenereerd die laten zien dat alle use cases en user stories zijn getest en dat die tests zijn geslaagd.
 Beschikbare templates:
 - Template detailtestplan softwarerealisatie.
@@ -884,7 +884,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="146">
   <si>
-    <t>Onderstaande checklist kan gebruikt worden voor het uitvoeren van een assessment tegen de ICTU Kwaliteitsaanpak Softwareontwikkeling versie wip, 02-08-2024.</t>
+    <t>Onderstaande checklist kan gebruikt worden voor het uitvoeren van een assessment tegen de ICTU Kwaliteitsaanpak Softwareontwikkeling versie wip, 22-10-2024.</t>
   </si>
   <si>
     <t>Gebruik de 'Status' kolom om aan te geven in hoeverre een maatregel uit de Kwaliteitsaanpak is toegepast. Bij maatregelen met submaatregelen hoeft alleen de status van de submaatregelen te worden ingevuld.</t>

--- a/docs/wip/ICTU-Kwaliteitsaanpak-Checklist.xlsx
+++ b/docs/wip/ICTU-Kwaliteitsaanpak-Checklist.xlsx
@@ -160,6 +160,7 @@
 De opdrachtgevende organisatie is verantwoordelijk voor het mastertestplan. Het project maakt een detailtestplan voor de testsoorten die tijdens de realisatiefase door het project worden uitgevoerd. Voor testen die onder verantwoordelijkheid van het project door een derde partij worden uitgevoerd, denk aan penetratietesten en evaluaties van gebruikskwaliteit, worden aparte detailtestplannen gemaakt.
 Logische testgevallen worden vastgelegd en gekoppeld met use cases en user stories. Fysieke testgevallen worden vastgelegd in het formaat van de gebruikte tooling en gekoppeld met de logische testgevallen. Op basis hiervan worden testrapportages gegenereerd die laten zien dat alle use cases en user stories zijn getest en dat die tests zijn geslaagd.
 Beschikbare templates:
+- Template mastertestplan.
 - Template detailtestplan softwarerealisatie.
 Informatiebeveiligingsplan
 Het informatiebeveiligingsplan vormt een praktisch toepasbaar document dat uitlegt binnen welke kaders bescherming geleverd wordt tegen welke dreigingen en met welke maatregelen die bescherming vorm krijgt. Mogelijke bronnen voor het informatiebeveiligingsplan zijn de business impact analysis (BIA), privacy impact assessment (PIA) en de threat and vulnerability assessment (TVA).
@@ -884,7 +885,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="146">
   <si>
-    <t>Onderstaande checklist kan gebruikt worden voor het uitvoeren van een assessment tegen de ICTU Kwaliteitsaanpak Softwareontwikkeling versie wip, 02-08-2024.</t>
+    <t>Onderstaande checklist kan gebruikt worden voor het uitvoeren van een assessment tegen de ICTU Kwaliteitsaanpak Softwareontwikkeling versie wip, 22-10-2024.</t>
   </si>
   <si>
     <t>Gebruik de 'Status' kolom om aan te geven in hoeverre een maatregel uit de Kwaliteitsaanpak is toegepast. Bij maatregelen met submaatregelen hoeft alleen de status van de submaatregelen te worden ingevuld.</t>

--- a/docs/wip/ICTU-Kwaliteitsaanpak-Checklist.xlsx
+++ b/docs/wip/ICTU-Kwaliteitsaanpak-Checklist.xlsx
@@ -438,7 +438,7 @@
 8. controleren van de configuratie op aanwezigheid van bekende kwetsbaarheden in configuratie: OpenVAS (Vulnerability Assessment System),
 9. controleren op aanwezigheid van bekende kwetsbaarheden in externe software: OWASP (Open Web Application Security Project) Dependency-Check en/of Dependency-Track,
 10. statische controle van de software op aanwezigheid van kwetsbare constructies: SonarQube,
-11. dynamische controle van de software op aanwezigheid van kwetsbare constructies: OWASP ZAP (Zed Attack Proxy),
+11. dynamische controle van de software op aanwezigheid van kwetsbare constructies: ZAP (Zed Attack Proxy) by Checkmarx,
 12. controleren van container images op aanwezigheid van bekende kwetsbaarheden: Trivy,
 13. testen van performance en schaalbaarheid: JMeter en Performancetestrunner,
 14. testen op toegankelijkheid van de applicatie: Axe,
@@ -884,7 +884,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="146">
   <si>
-    <t>Onderstaande checklist kan gebruikt worden voor het uitvoeren van een assessment tegen de ICTU Kwaliteitsaanpak Softwareontwikkeling versie wip, 02-08-2024.</t>
+    <t>Onderstaande checklist kan gebruikt worden voor het uitvoeren van een assessment tegen de ICTU Kwaliteitsaanpak Softwareontwikkeling versie wip, 22-10-2024.</t>
   </si>
   <si>
     <t>Gebruik de 'Status' kolom om aan te geven in hoeverre een maatregel uit de Kwaliteitsaanpak is toegepast. Bij maatregelen met submaatregelen hoeft alleen de status van de submaatregelen te worden ingevuld.</t>
@@ -1121,7 +1121,7 @@
     <t>10. statische controle van de software op aanwezigheid van kwetsbare constructies: SonarQube,</t>
   </si>
   <si>
-    <t>11. dynamische controle van de software op aanwezigheid van kwetsbare constructies: OWASP ZAP (Zed Attack Proxy),</t>
+    <t>11. dynamische controle van de software op aanwezigheid van kwetsbare constructies: ZAP (Zed Attack Proxy) by Checkmarx,</t>
   </si>
   <si>
     <t>12. controleren van container images op aanwezigheid van bekende kwetsbaarheden: Trivy,</t>

--- a/docs/wip/ICTU-Kwaliteitsaanpak-Checklist.xlsx
+++ b/docs/wip/ICTU-Kwaliteitsaanpak-Checklist.xlsx
@@ -885,7 +885,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="146">
   <si>
-    <t>Onderstaande checklist kan gebruikt worden voor het uitvoeren van een assessment tegen de ICTU Kwaliteitsaanpak Softwareontwikkeling versie wip, 08-11-2024.</t>
+    <t>Onderstaande checklist kan gebruikt worden voor het uitvoeren van een assessment tegen de ICTU Kwaliteitsaanpak Softwareontwikkeling versie wip, 27-11-2024.</t>
   </si>
   <si>
     <t>Gebruik de 'Status' kolom om aan te geven in hoeverre een maatregel uit de Kwaliteitsaanpak is toegepast. Bij maatregelen met submaatregelen hoeft alleen de status van de submaatregelen te worden ingevuld.</t>

--- a/docs/wip/ICTU-Kwaliteitsaanpak-Checklist.xlsx
+++ b/docs/wip/ICTU-Kwaliteitsaanpak-Checklist.xlsx
@@ -379,6 +379,7 @@
 Release van software                                                                         Releaseserver in het ontwikkelplatform                                                   
 Maken van testrapportages                                                                    JUnit, Robot Framework, TestNG, of hiermee compatible tools                              
 Maken van kwaliteitsrapportages                                                              Quality-time                                                                             
+Actueel houden van externe software                                                          RenovateBot                                                                              
 Controleren op aanwezigheid van bekende kwetsbaarheden in externe software                   OWASP (Open Web Application Security Project) Dependency-Check en/of Dependency-Track    
 Statische controle van de software op aanwezigheid van kwetsbare constructies                SonarQube                                                                                
 Dynamische controle van de software op aanwezigheid van kwetsbare constructies               ZAP (Zed Attack Proxy) by Checkmarx                                                      
@@ -409,7 +410,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B70" authorId="0">
+    <comment ref="B71" authorId="0">
       <text>
         <r>
           <rPr>
@@ -429,7 +430,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B71" authorId="0">
+    <comment ref="B72" authorId="0">
       <text>
         <r>
           <rPr>
@@ -451,7 +452,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B73" authorId="0">
+    <comment ref="B74" authorId="0">
       <text>
         <r>
           <rPr>
@@ -472,7 +473,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B74" authorId="0">
+    <comment ref="B75" authorId="0">
       <text>
         <r>
           <rPr>
@@ -489,7 +490,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B75" authorId="0">
+    <comment ref="B76" authorId="0">
       <text>
         <r>
           <rPr>
@@ -506,7 +507,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B76" authorId="0">
+    <comment ref="B77" authorId="0">
       <text>
         <r>
           <rPr>
@@ -529,7 +530,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C76" authorId="0">
+    <comment ref="C77" authorId="0">
       <text>
         <r>
           <rPr>
@@ -542,7 +543,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B81" authorId="0">
+    <comment ref="B82" authorId="0">
       <text>
         <r>
           <rPr>
@@ -563,7 +564,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B82" authorId="0">
+    <comment ref="B83" authorId="0">
       <text>
         <r>
           <rPr>
@@ -588,7 +589,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B83" authorId="0">
+    <comment ref="B84" authorId="0">
       <text>
         <r>
           <rPr>
@@ -615,7 +616,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B84" authorId="0">
+    <comment ref="B85" authorId="0">
       <text>
         <r>
           <rPr>
@@ -633,7 +634,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B85" authorId="0">
+    <comment ref="B86" authorId="0">
       <text>
         <r>
           <rPr>
@@ -665,7 +666,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C85" authorId="0">
+    <comment ref="C86" authorId="0">
       <text>
         <r>
           <rPr>
@@ -678,7 +679,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B100" authorId="0">
+    <comment ref="B101" authorId="0">
       <text>
         <r>
           <rPr>
@@ -698,7 +699,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B102" authorId="0">
+    <comment ref="B103" authorId="0">
       <text>
         <r>
           <rPr>
@@ -718,7 +719,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B103" authorId="0">
+    <comment ref="B104" authorId="0">
       <text>
         <r>
           <rPr>
@@ -737,7 +738,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B104" authorId="0">
+    <comment ref="B105" authorId="0">
       <text>
         <r>
           <rPr>
@@ -758,7 +759,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B105" authorId="0">
+    <comment ref="B106" authorId="0">
       <text>
         <r>
           <rPr>
@@ -777,7 +778,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B106" authorId="0">
+    <comment ref="B107" authorId="0">
       <text>
         <r>
           <rPr>
@@ -795,7 +796,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B107" authorId="0">
+    <comment ref="B108" authorId="0">
       <text>
         <r>
           <rPr>
@@ -826,7 +827,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="140">
   <si>
     <t>Onderstaande checklist kan gebruikt worden voor het uitvoeren van een assessment tegen de ICTU Kwaliteitsaanpak Softwareontwikkeling versie wip, 24-03-2025.</t>
   </si>
@@ -1038,34 +1039,37 @@
     <t>7. Maken van kwaliteitsrapportages</t>
   </si>
   <si>
-    <t>8. Controleren op aanwezigheid van bekende kwetsbaarheden in externe software</t>
-  </si>
-  <si>
-    <t>9. Statische controle van de software op aanwezigheid van kwetsbare constructies</t>
-  </si>
-  <si>
-    <t>10. Dynamische controle van de software op aanwezigheid van kwetsbare constructies</t>
-  </si>
-  <si>
-    <t>11. Controleren van container images op aanwezigheid van bekende kwetsbaarheden</t>
-  </si>
-  <si>
-    <t>12. Testen van performance en schaalbaarheid</t>
-  </si>
-  <si>
-    <t>13. Testen op toegankelijkheid van de applicatie</t>
-  </si>
-  <si>
-    <t>14. Produceren van een "software bill of materials" (SBoM)</t>
-  </si>
-  <si>
-    <t>15. Opslaan van artifacten</t>
-  </si>
-  <si>
-    <t>16. Registratie van incidenten bij gebruik en beheer</t>
-  </si>
-  <si>
-    <t>17. Bij het uitvoeren van operationeel beheer; uitrollen van de software in de productieomgeving</t>
+    <t>8. Actueel houden van externe software</t>
+  </si>
+  <si>
+    <t>9. Controleren op aanwezigheid van bekende kwetsbaarheden in externe software</t>
+  </si>
+  <si>
+    <t>10. Statische controle van de software op aanwezigheid van kwetsbare constructies</t>
+  </si>
+  <si>
+    <t>11. Dynamische controle van de software op aanwezigheid van kwetsbare constructies</t>
+  </si>
+  <si>
+    <t>12. Controleren van container images op aanwezigheid van bekende kwetsbaarheden</t>
+  </si>
+  <si>
+    <t>13. Testen van performance en schaalbaarheid</t>
+  </si>
+  <si>
+    <t>14. Testen op toegankelijkheid van de applicatie</t>
+  </si>
+  <si>
+    <t>15. Produceren van een "software bill of materials" (SBoM)</t>
+  </si>
+  <si>
+    <t>16. Opslaan van artifacten</t>
+  </si>
+  <si>
+    <t>17. Registratie van incidenten bij gebruik en beheer</t>
+  </si>
+  <si>
+    <t>18. Bij het uitvoeren van operationeel beheer; uitrollen van de software in de productieomgeving</t>
   </si>
   <si>
     <t>M08</t>
@@ -1684,7 +1688,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D107"/>
+  <dimension ref="A1:D108"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -2268,79 +2272,79 @@
       <c r="D69" s="5"/>
     </row>
     <row r="70" spans="1:4">
-      <c r="A70" s="3" t="s">
+      <c r="A70" s="6"/>
+      <c r="B70" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="B70" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="C70" s="8"/>
+      <c r="C70" s="7"/>
       <c r="D70" s="5"/>
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B71" s="4" t="s">
         <v>82</v>
-      </c>
-      <c r="B71" s="4" t="s">
-        <v>83</v>
       </c>
       <c r="C71" s="8"/>
       <c r="D71" s="5"/>
     </row>
     <row r="72" spans="1:4">
-      <c r="A72" s="1" t="s">
+      <c r="A72" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B72" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="B72" s="1"/>
-      <c r="C72" s="1"/>
-      <c r="D72" s="1"/>
+      <c r="C72" s="8"/>
+      <c r="D72" s="5"/>
     </row>
     <row r="73" spans="1:4">
-      <c r="A73" s="3" t="s">
+      <c r="A73" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B73" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="C73" s="8"/>
-      <c r="D73" s="5"/>
+      <c r="B73" s="1"/>
+      <c r="C73" s="1"/>
+      <c r="D73" s="1"/>
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B74" s="4" t="s">
         <v>87</v>
-      </c>
-      <c r="B74" s="4" t="s">
-        <v>88</v>
       </c>
       <c r="C74" s="8"/>
       <c r="D74" s="5"/>
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B75" s="4" t="s">
         <v>89</v>
-      </c>
-      <c r="B75" s="4" t="s">
-        <v>90</v>
       </c>
       <c r="C75" s="8"/>
       <c r="D75" s="5"/>
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B76" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="B76" s="4" t="s">
+      <c r="C76" s="8"/>
+      <c r="D76" s="5"/>
+    </row>
+    <row r="77" spans="1:4">
+      <c r="A77" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C76" s="4"/>
-      <c r="D76" s="5"/>
-    </row>
-    <row r="77" spans="1:4">
-      <c r="A77" s="6"/>
-      <c r="B77" s="6" t="s">
+      <c r="B77" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="C77" s="7"/>
+      <c r="C77" s="4"/>
       <c r="D77" s="5"/>
     </row>
     <row r="78" spans="1:4">
@@ -2368,61 +2372,61 @@
       <c r="D80" s="5"/>
     </row>
     <row r="81" spans="1:4">
-      <c r="A81" s="3" t="s">
+      <c r="A81" s="6"/>
+      <c r="B81" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="B81" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="C81" s="8"/>
+      <c r="C81" s="7"/>
       <c r="D81" s="5"/>
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B82" s="4" t="s">
         <v>99</v>
-      </c>
-      <c r="B82" s="4" t="s">
-        <v>100</v>
       </c>
       <c r="C82" s="8"/>
       <c r="D82" s="5"/>
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B83" s="4" t="s">
         <v>101</v>
-      </c>
-      <c r="B83" s="4" t="s">
-        <v>102</v>
       </c>
       <c r="C83" s="8"/>
       <c r="D83" s="5"/>
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B84" s="4" t="s">
         <v>103</v>
-      </c>
-      <c r="B84" s="4" t="s">
-        <v>104</v>
       </c>
       <c r="C84" s="8"/>
       <c r="D84" s="5"/>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B85" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="B85" s="4" t="s">
+      <c r="C85" s="8"/>
+      <c r="D85" s="5"/>
+    </row>
+    <row r="86" spans="1:4">
+      <c r="A86" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C85" s="4"/>
-      <c r="D85" s="5"/>
-    </row>
-    <row r="86" spans="1:4">
-      <c r="A86" s="6"/>
-      <c r="B86" s="6" t="s">
+      <c r="B86" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="C86" s="7"/>
+      <c r="C86" s="4"/>
       <c r="D86" s="5"/>
     </row>
     <row r="87" spans="1:4">
@@ -2530,82 +2534,90 @@
       <c r="D99" s="5"/>
     </row>
     <row r="100" spans="1:4">
-      <c r="A100" s="3" t="s">
+      <c r="A100" s="6"/>
+      <c r="B100" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="B100" s="4" t="s">
+      <c r="C100" s="7"/>
+      <c r="D100" s="5"/>
+    </row>
+    <row r="101" spans="1:4">
+      <c r="A101" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="C100" s="8"/>
-      <c r="D100" s="5"/>
-    </row>
-    <row r="101" spans="1:4">
-      <c r="A101" s="1" t="s">
+      <c r="B101" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="B101" s="1"/>
-      <c r="C101" s="1"/>
-      <c r="D101" s="1"/>
+      <c r="C101" s="8"/>
+      <c r="D101" s="5"/>
     </row>
     <row r="102" spans="1:4">
-      <c r="A102" s="3" t="s">
+      <c r="A102" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B102" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="C102" s="8"/>
-      <c r="D102" s="5"/>
+      <c r="B102" s="1"/>
+      <c r="C102" s="1"/>
+      <c r="D102" s="1"/>
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B103" s="4" t="s">
         <v>126</v>
-      </c>
-      <c r="B103" s="4" t="s">
-        <v>127</v>
       </c>
       <c r="C103" s="8"/>
       <c r="D103" s="5"/>
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B104" s="4" t="s">
         <v>128</v>
-      </c>
-      <c r="B104" s="4" t="s">
-        <v>129</v>
       </c>
       <c r="C104" s="8"/>
       <c r="D104" s="5"/>
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B105" s="4" t="s">
         <v>130</v>
-      </c>
-      <c r="B105" s="4" t="s">
-        <v>131</v>
       </c>
       <c r="C105" s="8"/>
       <c r="D105" s="5"/>
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B106" s="4" t="s">
         <v>132</v>
-      </c>
-      <c r="B106" s="4" t="s">
-        <v>133</v>
       </c>
       <c r="C106" s="8"/>
       <c r="D106" s="5"/>
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B107" s="4" t="s">
         <v>134</v>
-      </c>
-      <c r="B107" s="4" t="s">
-        <v>135</v>
       </c>
       <c r="C107" s="8"/>
       <c r="D107" s="5"/>
+    </row>
+    <row r="108" spans="1:4">
+      <c r="A108" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B108" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C108" s="8"/>
+      <c r="D108" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -2642,7 +2654,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C102">
+  <conditionalFormatting sqref="C101">
     <cfRule type="cellIs" dxfId="0" priority="345" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -2726,6 +2738,20 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="C108">
+    <cfRule type="cellIs" dxfId="0" priority="369" operator="equal">
+      <formula>"voldoet"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="370" operator="equal">
+      <formula>"voldoet deels"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="371" operator="equal">
+      <formula>"voldoet niet"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="372" operator="equal">
+      <formula>"niet van toepassing"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C11">
     <cfRule type="cellIs" dxfId="0" priority="13" operator="equal">
       <formula>"voldoet"</formula>
@@ -3524,7 +3550,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C73">
+  <conditionalFormatting sqref="C72">
     <cfRule type="cellIs" dxfId="0" priority="241" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3566,7 +3592,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C77">
+  <conditionalFormatting sqref="C76">
     <cfRule type="cellIs" dxfId="0" priority="253" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3692,7 +3718,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C86">
+  <conditionalFormatting sqref="C85">
     <cfRule type="cellIs" dxfId="0" priority="285" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3902,7 +3928,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="92">
+  <dataValidations count="93">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C8">
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
@@ -4083,7 +4109,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C71">
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C73">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C72">
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C74">
@@ -4092,7 +4118,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C75">
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C77">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C76">
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C78">
@@ -4116,7 +4142,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C84">
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C86">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C85">
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C87">
@@ -4161,7 +4187,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C100">
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C102">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C101">
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C103">
@@ -4177,6 +4203,9 @@
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C107">
+      <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C108">
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4189,24 +4218,24 @@
     <hyperlink ref="A41" r:id="rId6" location="m04"/>
     <hyperlink ref="A42" r:id="rId7" location="m07"/>
     <hyperlink ref="A52" r:id="rId8" location="m16"/>
-    <hyperlink ref="A70" r:id="rId9" location="m08"/>
-    <hyperlink ref="A71" r:id="rId10" location="m26"/>
-    <hyperlink ref="A73" r:id="rId11" location="m14"/>
-    <hyperlink ref="A74" r:id="rId12" location="m21"/>
-    <hyperlink ref="A75" r:id="rId13" location="m23"/>
-    <hyperlink ref="A76" r:id="rId14" location="m05"/>
-    <hyperlink ref="A81" r:id="rId15" location="m35"/>
-    <hyperlink ref="A82" r:id="rId16" location="m10"/>
-    <hyperlink ref="A83" r:id="rId17" location="m28"/>
-    <hyperlink ref="A84" r:id="rId18" location="m30"/>
-    <hyperlink ref="A85" r:id="rId19" location="m34"/>
-    <hyperlink ref="A100" r:id="rId20" location="m27"/>
-    <hyperlink ref="A102" r:id="rId21" location="m29"/>
-    <hyperlink ref="A103" r:id="rId22" location="m19"/>
-    <hyperlink ref="A104" r:id="rId23" location="m18"/>
-    <hyperlink ref="A105" r:id="rId24" location="m11"/>
-    <hyperlink ref="A106" r:id="rId25" location="m12"/>
-    <hyperlink ref="A107" r:id="rId26" location="m33"/>
+    <hyperlink ref="A71" r:id="rId9" location="m08"/>
+    <hyperlink ref="A72" r:id="rId10" location="m26"/>
+    <hyperlink ref="A74" r:id="rId11" location="m14"/>
+    <hyperlink ref="A75" r:id="rId12" location="m21"/>
+    <hyperlink ref="A76" r:id="rId13" location="m23"/>
+    <hyperlink ref="A77" r:id="rId14" location="m05"/>
+    <hyperlink ref="A82" r:id="rId15" location="m35"/>
+    <hyperlink ref="A83" r:id="rId16" location="m10"/>
+    <hyperlink ref="A84" r:id="rId17" location="m28"/>
+    <hyperlink ref="A85" r:id="rId18" location="m30"/>
+    <hyperlink ref="A86" r:id="rId19" location="m34"/>
+    <hyperlink ref="A101" r:id="rId20" location="m27"/>
+    <hyperlink ref="A103" r:id="rId21" location="m29"/>
+    <hyperlink ref="A104" r:id="rId22" location="m19"/>
+    <hyperlink ref="A105" r:id="rId23" location="m18"/>
+    <hyperlink ref="A106" r:id="rId24" location="m11"/>
+    <hyperlink ref="A107" r:id="rId25" location="m12"/>
+    <hyperlink ref="A108" r:id="rId26" location="m33"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId27"/>
@@ -4226,7 +4255,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4234,10 +4263,10 @@
     </row>
     <row r="2" spans="1:4" ht="30" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>6</v>

--- a/docs/wip/ICTU-Kwaliteitsaanpak-Checklist.xlsx
+++ b/docs/wip/ICTU-Kwaliteitsaanpak-Checklist.xlsx
@@ -417,7 +417,7 @@
 5. release van software,
 6. maken van testrapportages,
 7. maken van kwaliteitsrapportages,
-8. controleren van de configuratie op aanwezigheid van bekende kwetsbaarheden,
+8. actueel houden van externe software,
 9. controleren van door de applicatie gebruikte versies van externe software op aanwezigheid van bekende kwetsbaarheden,
 10. statische controle van de software op aanwezigheid van kwetsbare constructies,
 11. dynamische controle van de software op aanwezigheid van kwetsbare constructies,
@@ -437,7 +437,7 @@
 5. release van software: Releaseserver in het ontwikkelplatform,
 6. maken van testrapportages: JUnit, Robot Framework, TestNG, of hiermee compatible tools,
 7. maken van kwaliteitsrapportages: Quality-time,
-8. controleren van de configuratie op aanwezigheid van bekende kwetsbaarheden in configuratie: OpenVAS (Vulnerability Assessment System),
+8. actueel houden van externe software: RenovateBot,
 9. controleren op aanwezigheid van bekende kwetsbaarheden in externe software: OWASP (Open Web Application Security Project) Dependency-Check en/of Dependency-Track,
 10. statische controle van de software op aanwezigheid van kwetsbare constructies: SonarQube,
 11. dynamische controle van de software op aanwezigheid van kwetsbare constructies: ZAP (Zed Attack Proxy) by Checkmarx,
@@ -1114,7 +1114,7 @@
     <t>7. maken van kwaliteitsrapportages: Quality-time,</t>
   </si>
   <si>
-    <t>8. controleren van de configuratie op aanwezigheid van bekende kwetsbaarheden in configuratie: OpenVAS (Vulnerability Assessment System),</t>
+    <t>8. actueel houden van externe software: RenovateBot,</t>
   </si>
   <si>
     <t>9. controleren op aanwezigheid van bekende kwetsbaarheden in externe software: OWASP (Open Web Application Security Project) Dependency-Check en/of Dependency-Track,</t>

--- a/docs/wip/ICTU-Kwaliteitsaanpak-Checklist.xlsx
+++ b/docs/wip/ICTU-Kwaliteitsaanpak-Checklist.xlsx
@@ -30,10 +30,10 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">M31: Het project beschikt over actuele vastgestelde informatie
-Voor een goede uitvoering van het project is specifieke informatie nodig. De opdrachtgevende organisatie zorgt dat het project bij de start van de voorfase inzicht heeft in de informatie die typisch wordt vastgelegd in een projectstartarchitectuur, business impact analysis en privacy impact assessment. Waar nodig werkt de opdrachtgevende organisatie de informatie bij tijdens de voorfase en realisatiefase.
+Voor een goede uitvoering van het project is specifieke informatie nodig. De opdrachtgevende organisatie zorgt dat het project bij de start van de voorfase inzicht heeft in de informatie die typisch wordt vastgelegd in een projectstartarchitectuur, business impact analyse en privacy impact assessment. Waar nodig werkt de opdrachtgevende organisatie de informatie bij tijdens de voorfase en realisatiefase.
 De opdrachtgevende organisatie zorgt dat het project vanaf de start van de voorfase beschikt over:
 1. Projectstartarchitectuur,
-2. Business impact analysis,
+2. Business impact analyse,
 3. Privacy impact assessment,
 4. Afspraken tussen opdrachtgevende organisatie en beheerorganisatie.
 Als de benodigde informatie niet gereed is bij de start van de voorfase dan maken opdrachtgevende organisatie en ICTU nadere afspraken over de manier waarop de benodigde informatie nog tijdens de voorfase beschikbaar komt voor het project.
@@ -49,8 +49,8 @@
 Zie https://www.noraonline.nl/wiki/PSA.
 Conform NORA werkt de opdrachtgevende organisatie na de start van het project de PSA uit in een solution architectuur (SA).
 Zie https://www.noraonline.nl/wiki/Solution-architectuur.
-Business impact analysis
-In een business impact analysis (BIA) legt de opdrachtgevende organisatie vast hoe belangrijk informatiebeveiliging is voor de eigen bedrijfsvoering/processen. Naast de gevoeligheid voor incidenten komt hierin ook de 'risk appetite' van de organisatie tot uiting: de risico’s die een organisatie bereid is te accepteren. Alleen de opdrachtgevende organisatie zelf kan hierover een uitspraak doen.
+Business impact analyse
+In een business impact analyse (BIA) legt de opdrachtgevende organisatie vast hoe belangrijk informatiebeveiliging is voor de eigen bedrijfsvoering/processen. Naast de gevoeligheid voor incidenten komt hierin ook de 'risk appetite' van de organisatie tot uiting: de risico’s die een organisatie bereid is te accepteren. Alleen de opdrachtgevende organisatie zelf kan hierover een uitspraak doen.
 Privacy impact assessment
 In een privacy impact assessment (PIA) legt de opdrachtgevende organisatie vast wat de privacy-gevoeligheid is van de gegevens die in een proces of informatiesysteem worden verzameld en verwerkt. De rechtmatigheid van de verwerking wordt beoordeeld. En de PIA stelt grenzen aan de gegevens die mogen worden verzameld en verwerkt. Zicht op privacygevoelige gegevens en het (laten) treffen van adequate en afdoende beschermingsmaatregelen is een wettelijke plicht die een organisatie niet aan een andere partij kan overdragen.
 Als een PIA niet nodig is, dan is een verklaring daaromtrent vereist.
@@ -94,7 +94,7 @@
 De onderstaande tabel bevat de in deze paragraaf beschreven producten. Het ✔ geeft aan in welke fase ze worden opgeleverd.
 Product                                             Voor start Voorfase Realisatiefase Verantwoordelijke organisatie 
 Projectstartarchitectuur                            x                                  opdrachtgever                 
-Business impact analysis                            x                                  opdrachtgever                 
+Business impact analyse                             x                                  opdrachtgever                 
 Privacy impact assessment                           x                                  opdrachtgever                 
 Plan van aanpak: voorfase                           x                                  ICTU                          
 Beschrijving van functionele eisen                             x        x              opdrachtgever                 
@@ -112,8 +112,8 @@
 Software bill of materials                                              x              ICTU                          
 Release notes                                                           x              ICTU                          
 Vrijgaveadvies                                                          x              opdrachtgever                 
-Projectstartarchitectuur, business impact analysis en privacy impact assessment
-De opdrachtgevende organisatie zorgt dat het project bij de start van de voorfase inzicht heeft in de informatie die typisch wordt vastgelegd in een projectstartarchitectuur, business impact analysis en privacy impact assessment. Zie M31: Het project beschikt over actuele vastgestelde informatie.
+Projectstartarchitectuur, business impact analyse en privacy impact assessment
+De opdrachtgevende organisatie zorgt dat het project bij de start van de voorfase inzicht heeft in de informatie die typisch wordt vastgelegd in een projectstartarchitectuur, business impact analyse en privacy impact assessment. Zie M31: Het project beschikt over actuele vastgestelde informatie.
 Plan van aanpak
 Het plan van aanpak voor de voorfase en het plan van aanpak voor de realisatiefase beschrijven de in deze fasen te realiseren producten en diensten, en de planning, werkwijze en verantwoordelijkheden voor de totstandkoming van die producten en diensten.
 Als tijdens de realisatiefase van het project bestaande software dient te worden afgebouwd, onderhouden en/of herbouwd, bevat het plan van aanpak voor de voorfase een onderzoek naar de kwaliteit van deze software, zie M32: Het project onderzoekt de kwaliteit van over te nemen software.
@@ -163,7 +163,7 @@
 - Template mastertestplan.
 - Template detailtestplan softwarerealisatie.
 Informatiebeveiligingsplan
-Het informatiebeveiligingsplan vormt een praktisch toepasbaar document dat uitlegt binnen welke kaders bescherming geleverd wordt tegen welke dreigingen en met welke maatregelen die bescherming vorm krijgt. Mogelijke bronnen voor het informatiebeveiligingsplan zijn de business impact analysis (BIA), privacy impact assessment (PIA) en de threat and vulnerability assessment (TVA).
+Het informatiebeveiligingsplan vormt een praktisch toepasbaar document dat uitlegt binnen welke kaders bescherming geleverd wordt tegen welke dreigingen en met welke maatregelen die bescherming vorm krijgt. Mogelijke bronnen voor het informatiebeveiligingsplan zijn de business impact analyse (BIA), privacy impact assessment (PIA) en de threat and vulnerability assessment (TVA).
 Het Besluit Voorschrift Informatiebeveiliging Rijksdienst 2007 (VIR 2007) bevat een methode om te komen tot een systematische aanpak van informatiebeveiliging. Eén van de vereisten van het VIR 2007 is dat voor elk informatiesysteem en voor elk verantwoordelijkheidsgebied een afhankelijkheids- en kwetsbaarheidsanalyse (A&amp;K-analyse) wordt uitgevoerd.
 Bij ICTU wordt daarvoor een TVA gebruikt. Hierin worden de betrouwbaarheidseisen, die aan de bedrijfsprocessen en dientengevolge aan het informatiesysteem of verantwoordelijkheidsgebied worden gesteld, tijdens een afhankelijkheidsanalyse geïnventariseerd. Vervolgens worden de bedreigingen geïdentificeerd en geanalyseerd. De TVA levert zodoende een deel van een traceerbare onderbouwing voor de te treffen beveiligingsmaatregelen. De TVA wordt tijdens de voorfase opgesteld op basis van de resultaten van de BIA, de eventuele PIA en de inhoud van de ontwerp- en architectuurdocumentatie.
 Kwaliteitsplan
@@ -921,7 +921,7 @@
     <t>1. Projectstartarchitectuur,</t>
   </si>
   <si>
-    <t>2. Business impact analysis,</t>
+    <t>2. Business impact analyse,</t>
   </si>
   <si>
     <t>3. Privacy impact assessment,</t>
@@ -939,7 +939,7 @@
     <t>1. Projectstartarchitectuur</t>
   </si>
   <si>
-    <t>2. Business impact analysis</t>
+    <t>2. Business impact analyse</t>
   </si>
   <si>
     <t>3. Privacy impact assessment</t>
@@ -1404,7 +1404,7 @@
   <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>

--- a/docs/wip/ICTU-Kwaliteitsaanpak-Checklist.xlsx
+++ b/docs/wip/ICTU-Kwaliteitsaanpak-Checklist.xlsx
@@ -417,17 +417,16 @@
 5. release van software,
 6. maken van testrapportages,
 7. maken van kwaliteitsrapportages,
-8. controleren van de configuratie op aanwezigheid van bekende kwetsbaarheden,
-9. controleren van door de applicatie gebruikte versies van externe software op aanwezigheid van bekende kwetsbaarheden,
-10. statische controle van de software op aanwezigheid van kwetsbare constructies,
-11. dynamische controle van de software op aanwezigheid van kwetsbare constructies,
-12. controleren van container images op aanwezigheid van bekende kwetsbaarheden,
-13. testen van performance en schaalbaarheid,
-14. testen op toegankelijkheid van de applicatie,
-15. produceren van een "software bill of materials" (SBoM),
-16. opslaan van artifacten,
-17. registratie van incidenten bij gebruik en beheer, en
-18. bij het uitvoeren van operationeel beheer; uitrollen van de software in de productieomgeving.
+8. controleren van door de applicatie gebruikte versies van externe software op aanwezigheid van bekende kwetsbaarheden,
+9. statische controle van de software op aanwezigheid van kwetsbare constructies,
+10. dynamische controle van de software op aanwezigheid van kwetsbare constructies,
+11. controleren van container images op aanwezigheid van bekende kwetsbaarheden,
+12. testen van performance en schaalbaarheid,
+13. testen op toegankelijkheid van de applicatie,
+14. produceren van een "software bill of materials" (SBoM),
+15. opslaan van artifacten,
+16. registratie van incidenten bij gebruik en beheer, en
+17. bij het uitvoeren van operationeel beheer; uitrollen van de software in de productieomgeving.
 Onder het ondersteunen van "agile werken" vallen het opvoeren van eisen, het opvoeren van logische testgevallen, het koppelen van logische testgevallen aan eisen, het bijhouden van een werkvoorraad, het plannen van iteraties en het toewijzen van eisen aan iteraties. De 'eisen' worden, conform Scrumterminologie, geregistreerd als epics en/of user stories, de werkvoorraad als product backlog en de iteraties als sprints. Het toewijzen van eisen aan iteraties gebeurt via de sprint backlog.
 ICTU adviseert en ondersteunt voor de genoemde taken onderstaande tools. Projecten gebruiken deze tools, of gelijkwaardige alternatieven:
 1. product en sprint backlog management en agile werken: Azure DevOps of Jira,
@@ -437,17 +436,16 @@
 5. release van software: Releaseserver in het ontwikkelplatform,
 6. maken van testrapportages: JUnit, Robot Framework, TestNG, of hiermee compatible tools,
 7. maken van kwaliteitsrapportages: Quality-time,
-8. controleren van de configuratie op aanwezigheid van bekende kwetsbaarheden in configuratie: OpenVAS (Vulnerability Assessment System),
-9. controleren op aanwezigheid van bekende kwetsbaarheden in externe software: OWASP (Open Web Application Security Project) Dependency-Check en/of Dependency-Track,
-10. statische controle van de software op aanwezigheid van kwetsbare constructies: SonarQube,
-11. dynamische controle van de software op aanwezigheid van kwetsbare constructies: ZAP (Zed Attack Proxy) by Checkmarx,
-12. controleren van container images op aanwezigheid van bekende kwetsbaarheden: Trivy,
-13. testen van performance en schaalbaarheid: JMeter en Performancetestrunner,
-14. testen op toegankelijkheid van de applicatie: Axe,
-15. produceren van een "software bill of materials" (SBoM): tools die een SBoM in CycloneDX-formaat (zie https://cyclonedx.org) genereren,
-16. opslaan van artifacten: Nexus of Harbor,
-17. registratie van incidenten bij gebruik en beheer: Jira, en
-18. bij het uitvoeren van operationeel beheer; uitrollen van de software in de productieomgeving: Ansible.
+8. controleren op aanwezigheid van bekende kwetsbaarheden in externe software: OWASP (Open Web Application Security Project) Dependency-Check en/of Dependency-Track,
+9. statische controle van de software op aanwezigheid van kwetsbare constructies: SonarQube,
+10. dynamische controle van de software op aanwezigheid van kwetsbare constructies: ZAP (Zed Attack Proxy) by Checkmarx,
+11. controleren van container images op aanwezigheid van bekende kwetsbaarheden: Trivy,
+12. testen van performance en schaalbaarheid: JMeter en Performancetestrunner,
+13. testen op toegankelijkheid van de applicatie: Axe,
+14. produceren van een "software bill of materials" (SBoM): tools die een SBoM in CycloneDX-formaat (zie https://cyclonedx.org) genereren,
+15. opslaan van artifacten: Nexus of Harbor,
+16. registratie van incidenten bij gebruik en beheer: Jira, en
+17. bij het uitvoeren van operationeel beheer; uitrollen van de software in de productieomgeving: Ansible.
 Rationale
 Projecten hebben een redelijke vrijheid bij het kiezen en gebruiken van tools, maar voor een aantal taken is het gebruik verplicht gesteld. Deze tools zijn nodig voor een efficiënte uitvoering van de Kwaliteitsaanpak. Uniform gebruik van deze tools maakt het mogelijk koppeling tussen die tools voor alle projecten te standaardiseren; daarnaast bevordert het de uitwisselbaarheid van medewerkers en neemt het risico op het gebruik van onvolwassen tools af. Tot slot is het gebruik in een aantal gevallen, ten behoeve van informatiebeveiliging bij de overheid, verplicht.
 </t>
@@ -467,7 +465,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B76" authorId="0">
+    <comment ref="B75" authorId="0">
       <text>
         <r>
           <rPr>
@@ -487,7 +485,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B77" authorId="0">
+    <comment ref="B76" authorId="0">
       <text>
         <r>
           <rPr>
@@ -509,7 +507,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B79" authorId="0">
+    <comment ref="B78" authorId="0">
       <text>
         <r>
           <rPr>
@@ -530,7 +528,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B80" authorId="0">
+    <comment ref="B79" authorId="0">
       <text>
         <r>
           <rPr>
@@ -547,7 +545,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B81" authorId="0">
+    <comment ref="B80" authorId="0">
       <text>
         <r>
           <rPr>
@@ -556,15 +554,15 @@
             <rFont val="Courier"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">M23: Het project zorgt voor de aanwezigheid van ervaring met de Kwaliteitsaanpak
-De software delivery manager zorgt ervoor dat bij nieuwe projecten wordt gestart met ten minste twee projectleden die bekend zijn met de Kwaliteitsaanpak.
+          <t xml:space="preserve">M23: Het project zorgt voor de aanwezigheid van kennis van en ervaring met de Kwaliteitsaanpak
+De software delivery manager zorgt ervoor dat bij nieuwe projecten wordt gestart met ten minste twee projectleden die bekend zijn met de Kwaliteitsaanpak. Projectleden die nog niet bekend zijn met de Kwaliteitsaanpak krijgen uitleg over de inhoud en achtergrond van de Kwaliteitsaanpak.
 Rationale
 Het inzetten van teamleden die bekend zijn met de Kwaliteitsaanpak zorgt voor een soepeler start van een nieuw project omdat zij bekend zijn met de inhoud van de Kwaliteitsaanpak, zoals kwaliteitsnormen en tools, en omdat zij al doende nieuwe teamleden bekend kunnen maken met de Kwaliteitsaanpak.
 </t>
         </r>
       </text>
     </comment>
-    <comment ref="B82" authorId="0">
+    <comment ref="B81" authorId="0">
       <text>
         <r>
           <rPr>
@@ -587,7 +585,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C82" authorId="0">
+    <comment ref="C81" authorId="0">
       <text>
         <r>
           <rPr>
@@ -600,7 +598,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B87" authorId="0">
+    <comment ref="B86" authorId="0">
       <text>
         <r>
           <rPr>
@@ -621,7 +619,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B88" authorId="0">
+    <comment ref="B87" authorId="0">
       <text>
         <r>
           <rPr>
@@ -646,7 +644,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B89" authorId="0">
+    <comment ref="B88" authorId="0">
       <text>
         <r>
           <rPr>
@@ -673,7 +671,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B90" authorId="0">
+    <comment ref="B89" authorId="0">
       <text>
         <r>
           <rPr>
@@ -691,7 +689,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B91" authorId="0">
+    <comment ref="B90" authorId="0">
       <text>
         <r>
           <rPr>
@@ -723,7 +721,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C91" authorId="0">
+    <comment ref="C90" authorId="0">
       <text>
         <r>
           <rPr>
@@ -736,7 +734,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B106" authorId="0">
+    <comment ref="B105" authorId="0">
       <text>
         <r>
           <rPr>
@@ -756,7 +754,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B108" authorId="0">
+    <comment ref="B107" authorId="0">
       <text>
         <r>
           <rPr>
@@ -776,7 +774,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B109" authorId="0">
+    <comment ref="B108" authorId="0">
       <text>
         <r>
           <rPr>
@@ -795,7 +793,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B110" authorId="0">
+    <comment ref="B109" authorId="0">
       <text>
         <r>
           <rPr>
@@ -816,7 +814,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B111" authorId="0">
+    <comment ref="B110" authorId="0">
       <text>
         <r>
           <rPr>
@@ -835,7 +833,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B112" authorId="0">
+    <comment ref="B111" authorId="0">
       <text>
         <r>
           <rPr>
@@ -853,7 +851,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B113" authorId="0">
+    <comment ref="B112" authorId="0">
       <text>
         <r>
           <rPr>
@@ -884,9 +882,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="146">
-  <si>
-    <t>Onderstaande checklist kan gebruikt worden voor het uitvoeren van een assessment tegen de ICTU Kwaliteitsaanpak Softwareontwikkeling versie wip, 04-03-2025.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="145">
+  <si>
+    <t>Onderstaande checklist kan gebruikt worden voor het uitvoeren van een assessment tegen de ICTU Kwaliteitsaanpak Softwareontwikkeling versie wip, 21-03-2025.</t>
   </si>
   <si>
     <t>Gebruik de 'Status' kolom om aan te geven in hoeverre een maatregel uit de Kwaliteitsaanpak is toegepast. Bij maatregelen met submaatregelen hoeft alleen de status van de submaatregelen te worden ingevuld.</t>
@@ -1114,37 +1112,34 @@
     <t>7. maken van kwaliteitsrapportages: Quality-time,</t>
   </si>
   <si>
-    <t>8. controleren van de configuratie op aanwezigheid van bekende kwetsbaarheden in configuratie: OpenVAS (Vulnerability Assessment System),</t>
-  </si>
-  <si>
-    <t>9. controleren op aanwezigheid van bekende kwetsbaarheden in externe software: OWASP (Open Web Application Security Project) Dependency-Check en/of Dependency-Track,</t>
-  </si>
-  <si>
-    <t>10. statische controle van de software op aanwezigheid van kwetsbare constructies: SonarQube,</t>
-  </si>
-  <si>
-    <t>11. dynamische controle van de software op aanwezigheid van kwetsbare constructies: ZAP (Zed Attack Proxy) by Checkmarx,</t>
-  </si>
-  <si>
-    <t>12. controleren van container images op aanwezigheid van bekende kwetsbaarheden: Trivy,</t>
-  </si>
-  <si>
-    <t>13. testen van performance en schaalbaarheid: JMeter en Performancetestrunner,</t>
-  </si>
-  <si>
-    <t>14. testen op toegankelijkheid van de applicatie: Axe,</t>
-  </si>
-  <si>
-    <t>15. produceren van een "software bill of materials" (SBoM): tools die een SBoM in CycloneDX-formaat (zie https://cyclonedx.org) genereren,</t>
-  </si>
-  <si>
-    <t>16. opslaan van artifacten: Nexus of Harbor,</t>
-  </si>
-  <si>
-    <t>17. registratie van incidenten bij gebruik en beheer: Jira, en</t>
-  </si>
-  <si>
-    <t>18. bij het uitvoeren van operationeel beheer; uitrollen van de software in de productieomgeving: Ansible.</t>
+    <t>8. controleren op aanwezigheid van bekende kwetsbaarheden in externe software: OWASP (Open Web Application Security Project) Dependency-Check en/of Dependency-Track,</t>
+  </si>
+  <si>
+    <t>9. statische controle van de software op aanwezigheid van kwetsbare constructies: SonarQube,</t>
+  </si>
+  <si>
+    <t>10. dynamische controle van de software op aanwezigheid van kwetsbare constructies: ZAP (Zed Attack Proxy) by Checkmarx,</t>
+  </si>
+  <si>
+    <t>11. controleren van container images op aanwezigheid van bekende kwetsbaarheden: Trivy,</t>
+  </si>
+  <si>
+    <t>12. testen van performance en schaalbaarheid: JMeter en Performancetestrunner,</t>
+  </si>
+  <si>
+    <t>13. testen op toegankelijkheid van de applicatie: Axe,</t>
+  </si>
+  <si>
+    <t>14. produceren van een "software bill of materials" (SBoM): tools die een SBoM in CycloneDX-formaat (zie https://cyclonedx.org) genereren,</t>
+  </si>
+  <si>
+    <t>15. opslaan van artifacten: Nexus of Harbor,</t>
+  </si>
+  <si>
+    <t>16. registratie van incidenten bij gebruik en beheer: Jira, en</t>
+  </si>
+  <si>
+    <t>17. bij het uitvoeren van operationeel beheer; uitrollen van de software in de productieomgeving: Ansible.</t>
   </si>
   <si>
     <t>M08</t>
@@ -1177,7 +1172,7 @@
     <t>M23</t>
   </si>
   <si>
-    <t>Het project zorgt voor de aanwezigheid van ervaring met de Kwaliteitsaanpak</t>
+    <t>Het project zorgt voor de aanwezigheid van kennis van en ervaring met de Kwaliteitsaanpak</t>
   </si>
   <si>
     <t>M05</t>
@@ -1752,7 +1747,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D113"/>
+  <dimension ref="A1:D112"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -2378,79 +2373,79 @@
       <c r="D74" s="5"/>
     </row>
     <row r="75" spans="1:4">
-      <c r="A75" s="6"/>
-      <c r="B75" s="6" t="s">
+      <c r="A75" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C75" s="7"/>
+      <c r="B75" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C75" s="4"/>
       <c r="D75" s="5"/>
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C76" s="4"/>
       <c r="D76" s="5"/>
     </row>
     <row r="77" spans="1:4">
-      <c r="A77" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="B77" s="3" t="s">
+      <c r="A77" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C77" s="4"/>
-      <c r="D77" s="5"/>
+      <c r="B77" s="1"/>
+      <c r="C77" s="1"/>
+      <c r="D77" s="1"/>
     </row>
     <row r="78" spans="1:4">
-      <c r="A78" s="1" t="s">
+      <c r="A78" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="B78" s="1"/>
-      <c r="C78" s="1"/>
-      <c r="D78" s="1"/>
+      <c r="B78" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C78" s="4"/>
+      <c r="D78" s="5"/>
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C79" s="4"/>
       <c r="D79" s="5"/>
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C80" s="4"/>
       <c r="D80" s="5"/>
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C81" s="4"/>
       <c r="D81" s="5"/>
     </row>
     <row r="82" spans="1:4">
-      <c r="A82" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="B82" s="3" t="s">
+      <c r="A82" s="6"/>
+      <c r="B82" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="C82" s="4"/>
+      <c r="C82" s="7"/>
       <c r="D82" s="5"/>
     </row>
     <row r="83" spans="1:4">
@@ -2478,61 +2473,61 @@
       <c r="D85" s="5"/>
     </row>
     <row r="86" spans="1:4">
-      <c r="A86" s="6"/>
-      <c r="B86" s="6" t="s">
+      <c r="A86" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C86" s="7"/>
+      <c r="B86" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C86" s="4"/>
       <c r="D86" s="5"/>
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C87" s="4"/>
       <c r="D87" s="5"/>
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C88" s="4"/>
       <c r="D88" s="5"/>
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C89" s="4"/>
       <c r="D89" s="5"/>
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C90" s="4"/>
       <c r="D90" s="5"/>
     </row>
     <row r="91" spans="1:4">
-      <c r="A91" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="B91" s="3" t="s">
+      <c r="A91" s="6"/>
+      <c r="B91" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="C91" s="4"/>
+      <c r="C91" s="7"/>
       <c r="D91" s="5"/>
     </row>
     <row r="92" spans="1:4">
@@ -2640,90 +2635,82 @@
       <c r="D104" s="5"/>
     </row>
     <row r="105" spans="1:4">
-      <c r="A105" s="6"/>
-      <c r="B105" s="6" t="s">
+      <c r="A105" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="C105" s="7"/>
+      <c r="B105" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C105" s="4"/>
       <c r="D105" s="5"/>
     </row>
     <row r="106" spans="1:4">
-      <c r="A106" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="B106" s="3" t="s">
+      <c r="A106" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="C106" s="4"/>
-      <c r="D106" s="5"/>
+      <c r="B106" s="1"/>
+      <c r="C106" s="1"/>
+      <c r="D106" s="1"/>
     </row>
     <row r="107" spans="1:4">
-      <c r="A107" s="1" t="s">
+      <c r="A107" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="B107" s="1"/>
-      <c r="C107" s="1"/>
-      <c r="D107" s="1"/>
+      <c r="B107" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C107" s="4"/>
+      <c r="D107" s="5"/>
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C108" s="4"/>
       <c r="D108" s="5"/>
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C109" s="4"/>
       <c r="D109" s="5"/>
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C110" s="4"/>
       <c r="D110" s="5"/>
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C111" s="4"/>
       <c r="D111" s="5"/>
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C112" s="4"/>
       <c r="D112" s="5"/>
-    </row>
-    <row r="113" spans="1:4">
-      <c r="A113" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="B113" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="C113" s="4"/>
-      <c r="D113" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -2830,7 +2817,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C106">
+  <conditionalFormatting sqref="C107">
     <cfRule type="cellIs" dxfId="0" priority="393" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -2928,20 +2915,6 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C113">
-    <cfRule type="cellIs" dxfId="0" priority="417" operator="equal">
-      <formula>"voldoet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="418" operator="equal">
-      <formula>"voldoet deels"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="419" operator="equal">
-      <formula>"voldoet niet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="420" operator="equal">
-      <formula>"niet van toepassing"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="C12">
     <cfRule type="cellIs" dxfId="0" priority="21" operator="equal">
       <formula>"voldoet"</formula>
@@ -3866,7 +3839,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C77">
+  <conditionalFormatting sqref="C78">
     <cfRule type="cellIs" dxfId="0" priority="281" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -4202,7 +4175,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="105">
+  <dataValidations count="104">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C7">
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
@@ -4413,7 +4386,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C76">
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C77">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C78">
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C79">
@@ -4497,7 +4470,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C105">
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C106">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C107">
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C108">
@@ -4513,9 +4486,6 @@
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C112">
-      <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C113">
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4537,7 +4507,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4545,10 +4515,10 @@
     </row>
     <row r="2" spans="1:4" ht="30" customHeight="1">
       <c r="A2" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>144</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>145</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>6</v>

--- a/docs/wip/ICTU-Kwaliteitsaanpak-Checklist.xlsx
+++ b/docs/wip/ICTU-Kwaliteitsaanpak-Checklist.xlsx
@@ -290,24 +290,6 @@
             <rFont val="Courier"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">M13: Het project gebruikt ISO-25010 voor de specificatie van productkwaliteitseisen
-Voor specificatie en documentatie van vereiste en gewenste kwaliteitseigenschappen, de niet-functionele eisen, maken projecten gebruik van de terminologie en categorisering uit NEN-ISO/IEC 25010:2023. Projecten gebruiken NEN-ISO/IEC 25010:2023 om te controleren of alle relevante kwaliteitseigenschappen van het op te leveren eindproduct worden meegenomen in de ontwikkeling en/of onderhoud van het product.
-De standaard NEN-ISO/IEC 25010:2023 biedt een model voor het beschrijven van productkwaliteit. Kwaliteitseigenschappen zijn voorzien van een naam, definitie en classificatie. NEN-ISO/IEC 25010:2023 dekt een breed spectrum van kwaliteitseigenschappen af.
-Rationale
-NEN-ISO/IEC 25010:2023 biedt een model voor productkwaliteit. De standaard biedt geen concrete maatregelen, maar biedt wel een begrippenkader en dekt het volledige spectrum van mogelijk relevante kwaliteitseigenschappen af. Het gebruiken van een standaard voor specificatie van kwaliteit voorkomt miscommunicatie over kwaliteitseigenschappen en de breedte van de standaard zorgt ervoor dat alle relevante aspecten aan bod komen.
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B41" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Courier"/>
-            <family val="2"/>
-          </rPr>
           <t xml:space="preserve">M04: Het project borgt de correcte werking van het product met geautomatiseerde regressietests
 Regressietests - tests die verifiëren of eerder ontwikkelde software nog steeds correct werkt na wijzigingen in de software of aansluiting op andere externe koppelvlakken - zijn geautomatiseerd.
 Het project hanteert een norm voor de dekking van regressietests, legt deze vast in Quality-time en bewaakt deze.
@@ -317,7 +299,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B42" authorId="0">
+    <comment ref="B41" authorId="0">
       <text>
         <r>
           <rPr>
@@ -346,7 +328,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C42" authorId="0">
+    <comment ref="C41" authorId="0">
       <text>
         <r>
           <rPr>
@@ -359,7 +341,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B52" authorId="0">
+    <comment ref="B51" authorId="0">
       <text>
         <r>
           <rPr>
@@ -396,7 +378,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C52" authorId="0">
+    <comment ref="C51" authorId="0">
       <text>
         <r>
           <rPr>
@@ -409,7 +391,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B70" authorId="0">
+    <comment ref="B69" authorId="0">
       <text>
         <r>
           <rPr>
@@ -429,7 +411,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B71" authorId="0">
+    <comment ref="B70" authorId="0">
       <text>
         <r>
           <rPr>
@@ -451,7 +433,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B73" authorId="0">
+    <comment ref="B72" authorId="0">
       <text>
         <r>
           <rPr>
@@ -472,7 +454,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B74" authorId="0">
+    <comment ref="B73" authorId="0">
       <text>
         <r>
           <rPr>
@@ -489,7 +471,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B75" authorId="0">
+    <comment ref="B74" authorId="0">
       <text>
         <r>
           <rPr>
@@ -506,7 +488,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B76" authorId="0">
+    <comment ref="B75" authorId="0">
       <text>
         <r>
           <rPr>
@@ -529,7 +511,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C76" authorId="0">
+    <comment ref="C75" authorId="0">
       <text>
         <r>
           <rPr>
@@ -542,7 +524,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B81" authorId="0">
+    <comment ref="B80" authorId="0">
       <text>
         <r>
           <rPr>
@@ -563,7 +545,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B82" authorId="0">
+    <comment ref="B81" authorId="0">
       <text>
         <r>
           <rPr>
@@ -588,7 +570,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B83" authorId="0">
+    <comment ref="B82" authorId="0">
       <text>
         <r>
           <rPr>
@@ -615,7 +597,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B84" authorId="0">
+    <comment ref="B83" authorId="0">
       <text>
         <r>
           <rPr>
@@ -633,7 +615,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B85" authorId="0">
+    <comment ref="B84" authorId="0">
       <text>
         <r>
           <rPr>
@@ -665,7 +647,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C85" authorId="0">
+    <comment ref="C84" authorId="0">
       <text>
         <r>
           <rPr>
@@ -678,7 +660,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B100" authorId="0">
+    <comment ref="B99" authorId="0">
       <text>
         <r>
           <rPr>
@@ -698,7 +680,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B102" authorId="0">
+    <comment ref="B101" authorId="0">
       <text>
         <r>
           <rPr>
@@ -718,7 +700,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B103" authorId="0">
+    <comment ref="B102" authorId="0">
       <text>
         <r>
           <rPr>
@@ -737,7 +719,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B104" authorId="0">
+    <comment ref="B103" authorId="0">
       <text>
         <r>
           <rPr>
@@ -758,7 +740,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B105" authorId="0">
+    <comment ref="B104" authorId="0">
       <text>
         <r>
           <rPr>
@@ -777,7 +759,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B106" authorId="0">
+    <comment ref="B105" authorId="0">
       <text>
         <r>
           <rPr>
@@ -795,7 +777,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B107" authorId="0">
+    <comment ref="B106" authorId="0">
       <text>
         <r>
           <rPr>
@@ -826,7 +808,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="137">
   <si>
     <t>Onderstaande checklist kan gebruikt worden voor het uitvoeren van een assessment tegen de ICTU Kwaliteitsaanpak Softwareontwikkeling versie wip, 24-03-2025.</t>
   </si>
@@ -964,12 +946,6 @@
   </si>
   <si>
     <t>Het project zorgt dat het product traceerbaar aan eisen voldoet</t>
-  </si>
-  <si>
-    <t>M13</t>
-  </si>
-  <si>
-    <t>Het project gebruikt ISO-25010 voor de specificatie van productkwaliteitseisen</t>
   </si>
   <si>
     <t>M04</t>
@@ -1684,7 +1660,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D107"/>
+  <dimension ref="A1:D106"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -2036,23 +2012,21 @@
       <c r="B41" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C41" s="8"/>
+      <c r="C41" s="4"/>
       <c r="D41" s="5"/>
     </row>
     <row r="42" spans="1:4">
-      <c r="A42" s="3" t="s">
+      <c r="A42" s="6"/>
+      <c r="B42" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B42" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C42" s="4"/>
+      <c r="C42" s="7"/>
       <c r="D42" s="5"/>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="6"/>
       <c r="B43" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C43" s="7"/>
       <c r="D43" s="5"/>
@@ -2060,7 +2034,7 @@
     <row r="44" spans="1:4">
       <c r="A44" s="6"/>
       <c r="B44" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C44" s="7"/>
       <c r="D44" s="5"/>
@@ -2068,7 +2042,7 @@
     <row r="45" spans="1:4">
       <c r="A45" s="6"/>
       <c r="B45" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C45" s="7"/>
       <c r="D45" s="5"/>
@@ -2076,7 +2050,7 @@
     <row r="46" spans="1:4">
       <c r="A46" s="6"/>
       <c r="B46" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C46" s="7"/>
       <c r="D46" s="5"/>
@@ -2084,7 +2058,7 @@
     <row r="47" spans="1:4">
       <c r="A47" s="6"/>
       <c r="B47" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C47" s="7"/>
       <c r="D47" s="5"/>
@@ -2092,7 +2066,7 @@
     <row r="48" spans="1:4">
       <c r="A48" s="6"/>
       <c r="B48" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C48" s="7"/>
       <c r="D48" s="5"/>
@@ -2100,7 +2074,7 @@
     <row r="49" spans="1:4">
       <c r="A49" s="6"/>
       <c r="B49" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C49" s="7"/>
       <c r="D49" s="5"/>
@@ -2108,33 +2082,33 @@
     <row r="50" spans="1:4">
       <c r="A50" s="6"/>
       <c r="B50" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C50" s="7"/>
       <c r="D50" s="5"/>
     </row>
     <row r="51" spans="1:4">
-      <c r="A51" s="6"/>
-      <c r="B51" s="6" t="s">
+      <c r="A51" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B51" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="C51" s="7"/>
+      <c r="C51" s="4"/>
       <c r="D51" s="5"/>
     </row>
     <row r="52" spans="1:4">
-      <c r="A52" s="3" t="s">
+      <c r="A52" s="6"/>
+      <c r="B52" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="B52" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C52" s="4"/>
+      <c r="C52" s="7"/>
       <c r="D52" s="5"/>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="6"/>
       <c r="B53" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C53" s="7"/>
       <c r="D53" s="5"/>
@@ -2142,7 +2116,7 @@
     <row r="54" spans="1:4">
       <c r="A54" s="6"/>
       <c r="B54" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C54" s="7"/>
       <c r="D54" s="5"/>
@@ -2150,7 +2124,7 @@
     <row r="55" spans="1:4">
       <c r="A55" s="6"/>
       <c r="B55" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C55" s="7"/>
       <c r="D55" s="5"/>
@@ -2158,7 +2132,7 @@
     <row r="56" spans="1:4">
       <c r="A56" s="6"/>
       <c r="B56" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C56" s="7"/>
       <c r="D56" s="5"/>
@@ -2166,7 +2140,7 @@
     <row r="57" spans="1:4">
       <c r="A57" s="6"/>
       <c r="B57" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C57" s="7"/>
       <c r="D57" s="5"/>
@@ -2174,7 +2148,7 @@
     <row r="58" spans="1:4">
       <c r="A58" s="6"/>
       <c r="B58" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C58" s="7"/>
       <c r="D58" s="5"/>
@@ -2182,7 +2156,7 @@
     <row r="59" spans="1:4">
       <c r="A59" s="6"/>
       <c r="B59" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C59" s="7"/>
       <c r="D59" s="5"/>
@@ -2190,7 +2164,7 @@
     <row r="60" spans="1:4">
       <c r="A60" s="6"/>
       <c r="B60" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C60" s="7"/>
       <c r="D60" s="5"/>
@@ -2198,7 +2172,7 @@
     <row r="61" spans="1:4">
       <c r="A61" s="6"/>
       <c r="B61" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C61" s="7"/>
       <c r="D61" s="5"/>
@@ -2206,7 +2180,7 @@
     <row r="62" spans="1:4">
       <c r="A62" s="6"/>
       <c r="B62" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C62" s="7"/>
       <c r="D62" s="5"/>
@@ -2214,7 +2188,7 @@
     <row r="63" spans="1:4">
       <c r="A63" s="6"/>
       <c r="B63" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C63" s="7"/>
       <c r="D63" s="5"/>
@@ -2222,7 +2196,7 @@
     <row r="64" spans="1:4">
       <c r="A64" s="6"/>
       <c r="B64" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C64" s="7"/>
       <c r="D64" s="5"/>
@@ -2230,7 +2204,7 @@
     <row r="65" spans="1:4">
       <c r="A65" s="6"/>
       <c r="B65" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C65" s="7"/>
       <c r="D65" s="5"/>
@@ -2238,7 +2212,7 @@
     <row r="66" spans="1:4">
       <c r="A66" s="6"/>
       <c r="B66" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C66" s="7"/>
       <c r="D66" s="5"/>
@@ -2246,7 +2220,7 @@
     <row r="67" spans="1:4">
       <c r="A67" s="6"/>
       <c r="B67" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C67" s="7"/>
       <c r="D67" s="5"/>
@@ -2254,17 +2228,19 @@
     <row r="68" spans="1:4">
       <c r="A68" s="6"/>
       <c r="B68" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C68" s="7"/>
       <c r="D68" s="5"/>
     </row>
     <row r="69" spans="1:4">
-      <c r="A69" s="6"/>
-      <c r="B69" s="6" t="s">
+      <c r="A69" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B69" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C69" s="7"/>
+      <c r="C69" s="8"/>
       <c r="D69" s="5"/>
     </row>
     <row r="70" spans="1:4">
@@ -2278,22 +2254,22 @@
       <c r="D70" s="5"/>
     </row>
     <row r="71" spans="1:4">
-      <c r="A71" s="3" t="s">
+      <c r="A71" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B71" s="4" t="s">
+      <c r="B71" s="1"/>
+      <c r="C71" s="1"/>
+      <c r="D71" s="1"/>
+    </row>
+    <row r="72" spans="1:4">
+      <c r="A72" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C71" s="8"/>
-      <c r="D71" s="5"/>
-    </row>
-    <row r="72" spans="1:4">
-      <c r="A72" s="1" t="s">
+      <c r="B72" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="B72" s="1"/>
-      <c r="C72" s="1"/>
-      <c r="D72" s="1"/>
+      <c r="C72" s="8"/>
+      <c r="D72" s="5"/>
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="3" t="s">
@@ -2322,23 +2298,21 @@
       <c r="B75" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="C75" s="8"/>
+      <c r="C75" s="4"/>
       <c r="D75" s="5"/>
     </row>
     <row r="76" spans="1:4">
-      <c r="A76" s="3" t="s">
+      <c r="A76" s="6"/>
+      <c r="B76" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="B76" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="C76" s="4"/>
+      <c r="C76" s="7"/>
       <c r="D76" s="5"/>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="6"/>
       <c r="B77" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C77" s="7"/>
       <c r="D77" s="5"/>
@@ -2346,7 +2320,7 @@
     <row r="78" spans="1:4">
       <c r="A78" s="6"/>
       <c r="B78" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C78" s="7"/>
       <c r="D78" s="5"/>
@@ -2354,17 +2328,19 @@
     <row r="79" spans="1:4">
       <c r="A79" s="6"/>
       <c r="B79" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C79" s="7"/>
       <c r="D79" s="5"/>
     </row>
     <row r="80" spans="1:4">
-      <c r="A80" s="6"/>
-      <c r="B80" s="6" t="s">
+      <c r="A80" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B80" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="C80" s="7"/>
+      <c r="C80" s="8"/>
       <c r="D80" s="5"/>
     </row>
     <row r="81" spans="1:4">
@@ -2404,23 +2380,21 @@
       <c r="B84" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="C84" s="8"/>
+      <c r="C84" s="4"/>
       <c r="D84" s="5"/>
     </row>
     <row r="85" spans="1:4">
-      <c r="A85" s="3" t="s">
+      <c r="A85" s="6"/>
+      <c r="B85" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="B85" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="C85" s="4"/>
+      <c r="C85" s="7"/>
       <c r="D85" s="5"/>
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="6"/>
       <c r="B86" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C86" s="7"/>
       <c r="D86" s="5"/>
@@ -2428,7 +2402,7 @@
     <row r="87" spans="1:4">
       <c r="A87" s="6"/>
       <c r="B87" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C87" s="7"/>
       <c r="D87" s="5"/>
@@ -2436,7 +2410,7 @@
     <row r="88" spans="1:4">
       <c r="A88" s="6"/>
       <c r="B88" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C88" s="7"/>
       <c r="D88" s="5"/>
@@ -2444,7 +2418,7 @@
     <row r="89" spans="1:4">
       <c r="A89" s="6"/>
       <c r="B89" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C89" s="7"/>
       <c r="D89" s="5"/>
@@ -2452,7 +2426,7 @@
     <row r="90" spans="1:4">
       <c r="A90" s="6"/>
       <c r="B90" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C90" s="7"/>
       <c r="D90" s="5"/>
@@ -2460,7 +2434,7 @@
     <row r="91" spans="1:4">
       <c r="A91" s="6"/>
       <c r="B91" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C91" s="7"/>
       <c r="D91" s="5"/>
@@ -2468,7 +2442,7 @@
     <row r="92" spans="1:4">
       <c r="A92" s="6"/>
       <c r="B92" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C92" s="7"/>
       <c r="D92" s="5"/>
@@ -2476,7 +2450,7 @@
     <row r="93" spans="1:4">
       <c r="A93" s="6"/>
       <c r="B93" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C93" s="7"/>
       <c r="D93" s="5"/>
@@ -2484,7 +2458,7 @@
     <row r="94" spans="1:4">
       <c r="A94" s="6"/>
       <c r="B94" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C94" s="7"/>
       <c r="D94" s="5"/>
@@ -2492,7 +2466,7 @@
     <row r="95" spans="1:4">
       <c r="A95" s="6"/>
       <c r="B95" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C95" s="7"/>
       <c r="D95" s="5"/>
@@ -2500,7 +2474,7 @@
     <row r="96" spans="1:4">
       <c r="A96" s="6"/>
       <c r="B96" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C96" s="7"/>
       <c r="D96" s="5"/>
@@ -2508,7 +2482,7 @@
     <row r="97" spans="1:4">
       <c r="A97" s="6"/>
       <c r="B97" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C97" s="7"/>
       <c r="D97" s="5"/>
@@ -2516,36 +2490,38 @@
     <row r="98" spans="1:4">
       <c r="A98" s="6"/>
       <c r="B98" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C98" s="7"/>
       <c r="D98" s="5"/>
     </row>
     <row r="99" spans="1:4">
-      <c r="A99" s="6"/>
-      <c r="B99" s="6" t="s">
+      <c r="A99" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B99" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="C99" s="7"/>
+      <c r="C99" s="8"/>
       <c r="D99" s="5"/>
     </row>
     <row r="100" spans="1:4">
-      <c r="A100" s="3" t="s">
+      <c r="A100" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B100" s="4" t="s">
+      <c r="B100" s="1"/>
+      <c r="C100" s="1"/>
+      <c r="D100" s="1"/>
+    </row>
+    <row r="101" spans="1:4">
+      <c r="A101" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="C100" s="8"/>
-      <c r="D100" s="5"/>
-    </row>
-    <row r="101" spans="1:4">
-      <c r="A101" s="1" t="s">
+      <c r="B101" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="B101" s="1"/>
-      <c r="C101" s="1"/>
-      <c r="D101" s="1"/>
+      <c r="C101" s="8"/>
+      <c r="D101" s="5"/>
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="3" t="s">
@@ -2596,16 +2572,6 @@
       </c>
       <c r="C106" s="8"/>
       <c r="D106" s="5"/>
-    </row>
-    <row r="107" spans="1:4">
-      <c r="A107" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="B107" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="C107" s="8"/>
-      <c r="D107" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -2628,7 +2594,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C100">
+  <conditionalFormatting sqref="C101">
     <cfRule type="cellIs" dxfId="0" priority="341" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -2712,20 +2678,6 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C107">
-    <cfRule type="cellIs" dxfId="0" priority="365" operator="equal">
-      <formula>"voldoet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="366" operator="equal">
-      <formula>"voldoet deels"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="367" operator="equal">
-      <formula>"voldoet niet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="368" operator="equal">
-      <formula>"niet van toepassing"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="C11">
     <cfRule type="cellIs" dxfId="0" priority="13" operator="equal">
       <formula>"voldoet"</formula>
@@ -3118,7 +3070,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C41">
+  <conditionalFormatting sqref="C42">
     <cfRule type="cellIs" dxfId="0" priority="125" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3244,7 +3196,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C51">
+  <conditionalFormatting sqref="C52">
     <cfRule type="cellIs" dxfId="0" priority="161" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3510,7 +3462,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C71">
+  <conditionalFormatting sqref="C72">
     <cfRule type="cellIs" dxfId="0" priority="237" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3552,7 +3504,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C75">
+  <conditionalFormatting sqref="C76">
     <cfRule type="cellIs" dxfId="0" priority="249" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3678,7 +3630,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C84">
+  <conditionalFormatting sqref="C85">
     <cfRule type="cellIs" dxfId="0" priority="281" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3902,7 +3854,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="92">
+  <dataValidations count="91">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C8">
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
@@ -3996,7 +3948,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C40">
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C41">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C42">
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C43">
@@ -4023,7 +3975,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C50">
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C51">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C52">
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C53">
@@ -4080,7 +4032,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C70">
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C71">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C72">
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C73">
@@ -4089,7 +4041,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C74">
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C75">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C76">
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C77">
@@ -4113,7 +4065,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C83">
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C84">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C85">
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C86">
@@ -4158,7 +4110,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C99">
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C100">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C101">
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C102">
@@ -4174,9 +4126,6 @@
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C106">
-      <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C107">
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4185,31 +4134,30 @@
     <hyperlink ref="A28" r:id="rId2" location="m32"/>
     <hyperlink ref="A32" r:id="rId3" location="m02"/>
     <hyperlink ref="A39" r:id="rId4" location="m03"/>
-    <hyperlink ref="A40" r:id="rId5" location="m13"/>
-    <hyperlink ref="A41" r:id="rId6" location="m04"/>
-    <hyperlink ref="A42" r:id="rId7" location="m07"/>
-    <hyperlink ref="A52" r:id="rId8" location="m16"/>
-    <hyperlink ref="A70" r:id="rId9" location="m08"/>
-    <hyperlink ref="A71" r:id="rId10" location="m26"/>
-    <hyperlink ref="A73" r:id="rId11" location="m14"/>
-    <hyperlink ref="A74" r:id="rId12" location="m21"/>
-    <hyperlink ref="A75" r:id="rId13" location="m23"/>
-    <hyperlink ref="A76" r:id="rId14" location="m05"/>
-    <hyperlink ref="A81" r:id="rId15" location="m35"/>
-    <hyperlink ref="A82" r:id="rId16" location="m10"/>
-    <hyperlink ref="A83" r:id="rId17" location="m28"/>
-    <hyperlink ref="A84" r:id="rId18" location="m30"/>
-    <hyperlink ref="A85" r:id="rId19" location="m34"/>
-    <hyperlink ref="A100" r:id="rId20" location="m27"/>
-    <hyperlink ref="A102" r:id="rId21" location="m29"/>
-    <hyperlink ref="A103" r:id="rId22" location="m19"/>
-    <hyperlink ref="A104" r:id="rId23" location="m18"/>
-    <hyperlink ref="A105" r:id="rId24" location="m11"/>
-    <hyperlink ref="A106" r:id="rId25" location="m12"/>
-    <hyperlink ref="A107" r:id="rId26" location="m33"/>
+    <hyperlink ref="A40" r:id="rId5" location="m04"/>
+    <hyperlink ref="A41" r:id="rId6" location="m07"/>
+    <hyperlink ref="A51" r:id="rId7" location="m16"/>
+    <hyperlink ref="A69" r:id="rId8" location="m08"/>
+    <hyperlink ref="A70" r:id="rId9" location="m26"/>
+    <hyperlink ref="A72" r:id="rId10" location="m14"/>
+    <hyperlink ref="A73" r:id="rId11" location="m21"/>
+    <hyperlink ref="A74" r:id="rId12" location="m23"/>
+    <hyperlink ref="A75" r:id="rId13" location="m05"/>
+    <hyperlink ref="A80" r:id="rId14" location="m35"/>
+    <hyperlink ref="A81" r:id="rId15" location="m10"/>
+    <hyperlink ref="A82" r:id="rId16" location="m28"/>
+    <hyperlink ref="A83" r:id="rId17" location="m30"/>
+    <hyperlink ref="A84" r:id="rId18" location="m34"/>
+    <hyperlink ref="A99" r:id="rId19" location="m27"/>
+    <hyperlink ref="A101" r:id="rId20" location="m29"/>
+    <hyperlink ref="A102" r:id="rId21" location="m19"/>
+    <hyperlink ref="A103" r:id="rId22" location="m18"/>
+    <hyperlink ref="A104" r:id="rId23" location="m11"/>
+    <hyperlink ref="A105" r:id="rId24" location="m12"/>
+    <hyperlink ref="A106" r:id="rId25" location="m33"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId27"/>
+  <legacyDrawing r:id="rId26"/>
 </worksheet>
 </file>
 
@@ -4226,7 +4174,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4234,10 +4182,10 @@
     </row>
     <row r="2" spans="1:4" ht="30" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>6</v>

--- a/docs/wip/ICTU-Kwaliteitsaanpak-Checklist.xlsx
+++ b/docs/wip/ICTU-Kwaliteitsaanpak-Checklist.xlsx
@@ -327,24 +327,6 @@
             <rFont val="Courier"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">M13: Het project gebruikt ISO-25010 voor de specificatie van productkwaliteitseisen
-Voor specificatie en documentatie van vereiste en gewenste kwaliteitseigenschappen, de niet-functionele eisen, maken projecten gebruik van de terminologie en categorisering uit NEN-ISO/IEC 25010:2023. Projecten gebruiken NEN-ISO/IEC 25010:2023 om te controleren of alle relevante kwaliteitseigenschappen van het op te leveren eindproduct worden meegenomen in de ontwikkeling en/of onderhoud van het product.
-De standaard NEN-ISO/IEC 25010:2023 biedt een model voor het beschrijven van productkwaliteit. Kwaliteitseigenschappen zijn voorzien van een naam, definitie en classificatie. NEN-ISO/IEC 25010:2023 dekt een breed spectrum van kwaliteitseigenschappen af.
-Rationale
-NEN-ISO/IEC 25010:2023 biedt een model voor productkwaliteit. De standaard biedt geen concrete maatregelen, maar biedt wel een begrippenkader en dekt het volledige spectrum van mogelijk relevante kwaliteitseigenschappen af. Het gebruiken van een standaard voor specificatie van kwaliteit voorkomt miscommunicatie over kwaliteitseigenschappen en de breedte van de standaard zorgt ervoor dat alle relevante aspecten aan bod komen.
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B45" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Courier"/>
-            <family val="2"/>
-          </rPr>
           <t xml:space="preserve">M04: Het project borgt de correcte werking van het product met geautomatiseerde regressietests
 Regressietests - tests die verifiëren of eerder ontwikkelde software nog steeds correct werkt na wijzigingen in de software of aansluiting op andere externe koppelvlakken - zijn geautomatiseerd.
 Het project hanteert een norm voor de dekking van regressietests, legt deze vast in Quality-time en bewaakt deze.
@@ -354,7 +336,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B46" authorId="0">
+    <comment ref="B45" authorId="0">
       <text>
         <r>
           <rPr>
@@ -386,7 +368,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C46" authorId="0">
+    <comment ref="C45" authorId="0">
       <text>
         <r>
           <rPr>
@@ -399,7 +381,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B57" authorId="0">
+    <comment ref="B56" authorId="0">
       <text>
         <r>
           <rPr>
@@ -417,17 +399,16 @@
 5. release van software,
 6. maken van testrapportages,
 7. maken van kwaliteitsrapportages,
-8. controleren van de configuratie op aanwezigheid van bekende kwetsbaarheden,
-9. controleren van door de applicatie gebruikte versies van externe software op aanwezigheid van bekende kwetsbaarheden,
-10. statische controle van de software op aanwezigheid van kwetsbare constructies,
-11. dynamische controle van de software op aanwezigheid van kwetsbare constructies,
-12. controleren van container images op aanwezigheid van bekende kwetsbaarheden,
-13. testen van performance en schaalbaarheid,
-14. testen op toegankelijkheid van de applicatie,
-15. produceren van een "software bill of materials" (SBoM),
-16. opslaan van artifacten,
-17. registratie van incidenten bij gebruik en beheer, en
-18. bij het uitvoeren van operationeel beheer; uitrollen van de software in de productieomgeving.
+8. controleren van door de applicatie gebruikte versies van externe software op aanwezigheid van bekende kwetsbaarheden,
+9. statische controle van de software op aanwezigheid van kwetsbare constructies,
+10. dynamische controle van de software op aanwezigheid van kwetsbare constructies,
+11. controleren van container images op aanwezigheid van bekende kwetsbaarheden,
+12. testen van performance en schaalbaarheid,
+13. testen op toegankelijkheid van de applicatie,
+14. produceren van een "software bill of materials" (SBoM),
+15. opslaan van artifacten,
+16. registratie van incidenten bij gebruik en beheer, en
+17. bij het uitvoeren van operationeel beheer; uitrollen van de software in de productieomgeving.
 Onder het ondersteunen van "agile werken" vallen het opvoeren van eisen, het opvoeren van logische testgevallen, het koppelen van logische testgevallen aan eisen, het bijhouden van een werkvoorraad, het plannen van iteraties en het toewijzen van eisen aan iteraties. De 'eisen' worden, conform Scrumterminologie, geregistreerd als epics en/of user stories, de werkvoorraad als product backlog en de iteraties als sprints. Het toewijzen van eisen aan iteraties gebeurt via de sprint backlog.
 ICTU adviseert en ondersteunt voor de genoemde taken onderstaande tools. Projecten gebruiken deze tools, of gelijkwaardige alternatieven:
 1. product en sprint backlog management en agile werken: Azure DevOps of Jira,
@@ -437,24 +418,23 @@
 5. release van software: Releaseserver in het ontwikkelplatform,
 6. maken van testrapportages: JUnit, Robot Framework, TestNG, of hiermee compatible tools,
 7. maken van kwaliteitsrapportages: Quality-time,
-8. controleren van de configuratie op aanwezigheid van bekende kwetsbaarheden in configuratie: OpenVAS (Vulnerability Assessment System),
-9. controleren op aanwezigheid van bekende kwetsbaarheden in externe software: OWASP (Open Web Application Security Project) Dependency-Check en/of Dependency-Track,
-10. statische controle van de software op aanwezigheid van kwetsbare constructies: SonarQube,
-11. dynamische controle van de software op aanwezigheid van kwetsbare constructies: ZAP (Zed Attack Proxy) by Checkmarx,
-12. controleren van container images op aanwezigheid van bekende kwetsbaarheden: Trivy,
-13. testen van performance en schaalbaarheid: JMeter en Performancetestrunner,
-14. testen op toegankelijkheid van de applicatie: Axe,
-15. produceren van een "software bill of materials" (SBoM): tools die een SBoM in CycloneDX-formaat (zie https://cyclonedx.org) genereren,
-16. opslaan van artifacten: Nexus of Harbor,
-17. registratie van incidenten bij gebruik en beheer: Jira, en
-18. bij het uitvoeren van operationeel beheer; uitrollen van de software in de productieomgeving: Ansible.
+8. controleren op aanwezigheid van bekende kwetsbaarheden in externe software: OWASP (Open Web Application Security Project) Dependency-Check en/of Dependency-Track,
+9. statische controle van de software op aanwezigheid van kwetsbare constructies: SonarQube,
+10. dynamische controle van de software op aanwezigheid van kwetsbare constructies: ZAP (Zed Attack Proxy) by Checkmarx,
+11. controleren van container images op aanwezigheid van bekende kwetsbaarheden: Trivy,
+12. testen van performance en schaalbaarheid: JMeter en Performancetestrunner,
+13. testen op toegankelijkheid van de applicatie: Axe,
+14. produceren van een "software bill of materials" (SBoM): tools die een SBoM in CycloneDX-formaat (zie https://cyclonedx.org) genereren,
+15. opslaan van artifacten: Nexus of Harbor,
+16. registratie van incidenten bij gebruik en beheer: Jira, en
+17. bij het uitvoeren van operationeel beheer; uitrollen van de software in de productieomgeving: Ansible.
 Rationale
 Projecten hebben een redelijke vrijheid bij het kiezen en gebruiken van tools, maar voor een aantal taken is het gebruik verplicht gesteld. Deze tools zijn nodig voor een efficiënte uitvoering van de Kwaliteitsaanpak. Uniform gebruik van deze tools maakt het mogelijk koppeling tussen die tools voor alle projecten te standaardiseren; daarnaast bevordert het de uitwisselbaarheid van medewerkers en neemt het risico op het gebruik van onvolwassen tools af. Tot slot is het gebruik in een aantal gevallen, ten behoeve van informatiebeveiliging bij de overheid, verplicht.
 </t>
         </r>
       </text>
     </comment>
-    <comment ref="C57" authorId="0">
+    <comment ref="C56" authorId="0">
       <text>
         <r>
           <rPr>
@@ -467,7 +447,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B76" authorId="0">
+    <comment ref="B74" authorId="0">
       <text>
         <r>
           <rPr>
@@ -487,7 +467,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B77" authorId="0">
+    <comment ref="B75" authorId="0">
       <text>
         <r>
           <rPr>
@@ -509,7 +489,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B79" authorId="0">
+    <comment ref="B77" authorId="0">
       <text>
         <r>
           <rPr>
@@ -530,7 +510,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B80" authorId="0">
+    <comment ref="B78" authorId="0">
       <text>
         <r>
           <rPr>
@@ -547,7 +527,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B81" authorId="0">
+    <comment ref="B79" authorId="0">
       <text>
         <r>
           <rPr>
@@ -564,7 +544,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B82" authorId="0">
+    <comment ref="B80" authorId="0">
       <text>
         <r>
           <rPr>
@@ -587,7 +567,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C82" authorId="0">
+    <comment ref="C80" authorId="0">
       <text>
         <r>
           <rPr>
@@ -600,7 +580,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B87" authorId="0">
+    <comment ref="B85" authorId="0">
       <text>
         <r>
           <rPr>
@@ -621,7 +601,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B88" authorId="0">
+    <comment ref="B86" authorId="0">
       <text>
         <r>
           <rPr>
@@ -646,7 +626,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B89" authorId="0">
+    <comment ref="B87" authorId="0">
       <text>
         <r>
           <rPr>
@@ -673,7 +653,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B90" authorId="0">
+    <comment ref="B88" authorId="0">
       <text>
         <r>
           <rPr>
@@ -691,7 +671,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B91" authorId="0">
+    <comment ref="B89" authorId="0">
       <text>
         <r>
           <rPr>
@@ -723,7 +703,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C91" authorId="0">
+    <comment ref="C89" authorId="0">
       <text>
         <r>
           <rPr>
@@ -736,7 +716,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B106" authorId="0">
+    <comment ref="B104" authorId="0">
       <text>
         <r>
           <rPr>
@@ -756,7 +736,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B108" authorId="0">
+    <comment ref="B106" authorId="0">
       <text>
         <r>
           <rPr>
@@ -776,7 +756,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B109" authorId="0">
+    <comment ref="B107" authorId="0">
       <text>
         <r>
           <rPr>
@@ -795,7 +775,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B110" authorId="0">
+    <comment ref="B108" authorId="0">
       <text>
         <r>
           <rPr>
@@ -816,7 +796,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B111" authorId="0">
+    <comment ref="B109" authorId="0">
       <text>
         <r>
           <rPr>
@@ -835,7 +815,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B112" authorId="0">
+    <comment ref="B110" authorId="0">
       <text>
         <r>
           <rPr>
@@ -853,7 +833,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B113" authorId="0">
+    <comment ref="B111" authorId="0">
       <text>
         <r>
           <rPr>
@@ -884,9 +864,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="146">
-  <si>
-    <t>Onderstaande checklist kan gebruikt worden voor het uitvoeren van een assessment tegen de ICTU Kwaliteitsaanpak Softwareontwikkeling versie wip, 04-03-2025.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="143">
+  <si>
+    <t>Onderstaande checklist kan gebruikt worden voor het uitvoeren van een assessment tegen de ICTU Kwaliteitsaanpak Softwareontwikkeling versie wip, 21-03-2025.</t>
   </si>
   <si>
     <t>Gebruik de 'Status' kolom om aan te geven in hoeverre een maatregel uit de Kwaliteitsaanpak is toegepast. Bij maatregelen met submaatregelen hoeft alleen de status van de submaatregelen te worden ingevuld.</t>
@@ -1039,12 +1019,6 @@
     <t>Het project zorgt dat het product traceerbaar aan eisen voldoet</t>
   </si>
   <si>
-    <t>M13</t>
-  </si>
-  <si>
-    <t>Het project gebruikt ISO-25010 voor de specificatie van productkwaliteitseisen</t>
-  </si>
-  <si>
     <t>M04</t>
   </si>
   <si>
@@ -1114,37 +1088,34 @@
     <t>7. maken van kwaliteitsrapportages: Quality-time,</t>
   </si>
   <si>
-    <t>8. controleren van de configuratie op aanwezigheid van bekende kwetsbaarheden in configuratie: OpenVAS (Vulnerability Assessment System),</t>
-  </si>
-  <si>
-    <t>9. controleren op aanwezigheid van bekende kwetsbaarheden in externe software: OWASP (Open Web Application Security Project) Dependency-Check en/of Dependency-Track,</t>
-  </si>
-  <si>
-    <t>10. statische controle van de software op aanwezigheid van kwetsbare constructies: SonarQube,</t>
-  </si>
-  <si>
-    <t>11. dynamische controle van de software op aanwezigheid van kwetsbare constructies: ZAP (Zed Attack Proxy) by Checkmarx,</t>
-  </si>
-  <si>
-    <t>12. controleren van container images op aanwezigheid van bekende kwetsbaarheden: Trivy,</t>
-  </si>
-  <si>
-    <t>13. testen van performance en schaalbaarheid: JMeter en Performancetestrunner,</t>
-  </si>
-  <si>
-    <t>14. testen op toegankelijkheid van de applicatie: Axe,</t>
-  </si>
-  <si>
-    <t>15. produceren van een "software bill of materials" (SBoM): tools die een SBoM in CycloneDX-formaat (zie https://cyclonedx.org) genereren,</t>
-  </si>
-  <si>
-    <t>16. opslaan van artifacten: Nexus of Harbor,</t>
-  </si>
-  <si>
-    <t>17. registratie van incidenten bij gebruik en beheer: Jira, en</t>
-  </si>
-  <si>
-    <t>18. bij het uitvoeren van operationeel beheer; uitrollen van de software in de productieomgeving: Ansible.</t>
+    <t>8. controleren op aanwezigheid van bekende kwetsbaarheden in externe software: OWASP (Open Web Application Security Project) Dependency-Check en/of Dependency-Track,</t>
+  </si>
+  <si>
+    <t>9. statische controle van de software op aanwezigheid van kwetsbare constructies: SonarQube,</t>
+  </si>
+  <si>
+    <t>10. dynamische controle van de software op aanwezigheid van kwetsbare constructies: ZAP (Zed Attack Proxy) by Checkmarx,</t>
+  </si>
+  <si>
+    <t>11. controleren van container images op aanwezigheid van bekende kwetsbaarheden: Trivy,</t>
+  </si>
+  <si>
+    <t>12. testen van performance en schaalbaarheid: JMeter en Performancetestrunner,</t>
+  </si>
+  <si>
+    <t>13. testen op toegankelijkheid van de applicatie: Axe,</t>
+  </si>
+  <si>
+    <t>14. produceren van een "software bill of materials" (SBoM): tools die een SBoM in CycloneDX-formaat (zie https://cyclonedx.org) genereren,</t>
+  </si>
+  <si>
+    <t>15. opslaan van artifacten: Nexus of Harbor,</t>
+  </si>
+  <si>
+    <t>16. registratie van incidenten bij gebruik en beheer: Jira, en</t>
+  </si>
+  <si>
+    <t>17. bij het uitvoeren van operationeel beheer; uitrollen van de software in de productieomgeving: Ansible.</t>
   </si>
   <si>
     <t>M08</t>
@@ -1752,7 +1723,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D113"/>
+  <dimension ref="A1:D111"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -2142,19 +2113,17 @@
       <c r="D45" s="5"/>
     </row>
     <row r="46" spans="1:4">
-      <c r="A46" s="3" t="s">
+      <c r="A46" s="6"/>
+      <c r="B46" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="B46" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C46" s="4"/>
+      <c r="C46" s="7"/>
       <c r="D46" s="5"/>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="6"/>
       <c r="B47" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C47" s="7"/>
       <c r="D47" s="5"/>
@@ -2162,7 +2131,7 @@
     <row r="48" spans="1:4">
       <c r="A48" s="6"/>
       <c r="B48" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C48" s="7"/>
       <c r="D48" s="5"/>
@@ -2170,7 +2139,7 @@
     <row r="49" spans="1:4">
       <c r="A49" s="6"/>
       <c r="B49" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C49" s="7"/>
       <c r="D49" s="5"/>
@@ -2178,7 +2147,7 @@
     <row r="50" spans="1:4">
       <c r="A50" s="6"/>
       <c r="B50" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C50" s="7"/>
       <c r="D50" s="5"/>
@@ -2186,7 +2155,7 @@
     <row r="51" spans="1:4">
       <c r="A51" s="6"/>
       <c r="B51" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C51" s="7"/>
       <c r="D51" s="5"/>
@@ -2194,7 +2163,7 @@
     <row r="52" spans="1:4">
       <c r="A52" s="6"/>
       <c r="B52" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C52" s="7"/>
       <c r="D52" s="5"/>
@@ -2202,7 +2171,7 @@
     <row r="53" spans="1:4">
       <c r="A53" s="6"/>
       <c r="B53" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C53" s="7"/>
       <c r="D53" s="5"/>
@@ -2210,7 +2179,7 @@
     <row r="54" spans="1:4">
       <c r="A54" s="6"/>
       <c r="B54" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C54" s="7"/>
       <c r="D54" s="5"/>
@@ -2218,33 +2187,33 @@
     <row r="55" spans="1:4">
       <c r="A55" s="6"/>
       <c r="B55" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C55" s="7"/>
       <c r="D55" s="5"/>
     </row>
     <row r="56" spans="1:4">
-      <c r="A56" s="6"/>
-      <c r="B56" s="6" t="s">
+      <c r="A56" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B56" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C56" s="7"/>
+      <c r="C56" s="4"/>
       <c r="D56" s="5"/>
     </row>
     <row r="57" spans="1:4">
-      <c r="A57" s="3" t="s">
+      <c r="A57" s="6"/>
+      <c r="B57" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B57" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C57" s="4"/>
+      <c r="C57" s="7"/>
       <c r="D57" s="5"/>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="6"/>
       <c r="B58" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C58" s="7"/>
       <c r="D58" s="5"/>
@@ -2252,7 +2221,7 @@
     <row r="59" spans="1:4">
       <c r="A59" s="6"/>
       <c r="B59" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C59" s="7"/>
       <c r="D59" s="5"/>
@@ -2260,7 +2229,7 @@
     <row r="60" spans="1:4">
       <c r="A60" s="6"/>
       <c r="B60" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C60" s="7"/>
       <c r="D60" s="5"/>
@@ -2268,7 +2237,7 @@
     <row r="61" spans="1:4">
       <c r="A61" s="6"/>
       <c r="B61" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C61" s="7"/>
       <c r="D61" s="5"/>
@@ -2276,7 +2245,7 @@
     <row r="62" spans="1:4">
       <c r="A62" s="6"/>
       <c r="B62" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C62" s="7"/>
       <c r="D62" s="5"/>
@@ -2284,7 +2253,7 @@
     <row r="63" spans="1:4">
       <c r="A63" s="6"/>
       <c r="B63" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C63" s="7"/>
       <c r="D63" s="5"/>
@@ -2292,7 +2261,7 @@
     <row r="64" spans="1:4">
       <c r="A64" s="6"/>
       <c r="B64" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C64" s="7"/>
       <c r="D64" s="5"/>
@@ -2300,7 +2269,7 @@
     <row r="65" spans="1:4">
       <c r="A65" s="6"/>
       <c r="B65" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C65" s="7"/>
       <c r="D65" s="5"/>
@@ -2308,7 +2277,7 @@
     <row r="66" spans="1:4">
       <c r="A66" s="6"/>
       <c r="B66" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C66" s="7"/>
       <c r="D66" s="5"/>
@@ -2316,7 +2285,7 @@
     <row r="67" spans="1:4">
       <c r="A67" s="6"/>
       <c r="B67" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C67" s="7"/>
       <c r="D67" s="5"/>
@@ -2324,7 +2293,7 @@
     <row r="68" spans="1:4">
       <c r="A68" s="6"/>
       <c r="B68" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C68" s="7"/>
       <c r="D68" s="5"/>
@@ -2332,7 +2301,7 @@
     <row r="69" spans="1:4">
       <c r="A69" s="6"/>
       <c r="B69" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C69" s="7"/>
       <c r="D69" s="5"/>
@@ -2340,7 +2309,7 @@
     <row r="70" spans="1:4">
       <c r="A70" s="6"/>
       <c r="B70" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C70" s="7"/>
       <c r="D70" s="5"/>
@@ -2348,7 +2317,7 @@
     <row r="71" spans="1:4">
       <c r="A71" s="6"/>
       <c r="B71" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C71" s="7"/>
       <c r="D71" s="5"/>
@@ -2356,7 +2325,7 @@
     <row r="72" spans="1:4">
       <c r="A72" s="6"/>
       <c r="B72" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C72" s="7"/>
       <c r="D72" s="5"/>
@@ -2364,36 +2333,38 @@
     <row r="73" spans="1:4">
       <c r="A73" s="6"/>
       <c r="B73" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C73" s="7"/>
       <c r="D73" s="5"/>
     </row>
     <row r="74" spans="1:4">
-      <c r="A74" s="6"/>
-      <c r="B74" s="6" t="s">
+      <c r="A74" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B74" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C74" s="7"/>
+      <c r="C74" s="4"/>
       <c r="D74" s="5"/>
     </row>
     <row r="75" spans="1:4">
-      <c r="A75" s="6"/>
-      <c r="B75" s="6" t="s">
+      <c r="A75" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C75" s="7"/>
+      <c r="B75" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C75" s="4"/>
       <c r="D75" s="5"/>
     </row>
     <row r="76" spans="1:4">
-      <c r="A76" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="B76" s="3" t="s">
+      <c r="A76" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C76" s="4"/>
-      <c r="D76" s="5"/>
+      <c r="B76" s="1"/>
+      <c r="C76" s="1"/>
+      <c r="D76" s="1"/>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="3" t="s">
@@ -2406,57 +2377,55 @@
       <c r="D77" s="5"/>
     </row>
     <row r="78" spans="1:4">
-      <c r="A78" s="1" t="s">
+      <c r="A78" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="B78" s="1"/>
-      <c r="C78" s="1"/>
-      <c r="D78" s="1"/>
+      <c r="B78" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C78" s="4"/>
+      <c r="D78" s="5"/>
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C79" s="4"/>
       <c r="D79" s="5"/>
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C80" s="4"/>
       <c r="D80" s="5"/>
     </row>
     <row r="81" spans="1:4">
-      <c r="A81" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="B81" s="3" t="s">
+      <c r="A81" s="6"/>
+      <c r="B81" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="C81" s="4"/>
+      <c r="C81" s="7"/>
       <c r="D81" s="5"/>
     </row>
     <row r="82" spans="1:4">
-      <c r="A82" s="3" t="s">
+      <c r="A82" s="6"/>
+      <c r="B82" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="B82" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C82" s="4"/>
+      <c r="C82" s="7"/>
       <c r="D82" s="5"/>
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="6"/>
       <c r="B83" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C83" s="7"/>
       <c r="D83" s="5"/>
@@ -2464,81 +2433,81 @@
     <row r="84" spans="1:4">
       <c r="A84" s="6"/>
       <c r="B84" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C84" s="7"/>
       <c r="D84" s="5"/>
     </row>
     <row r="85" spans="1:4">
-      <c r="A85" s="6"/>
-      <c r="B85" s="6" t="s">
+      <c r="A85" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B85" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C85" s="7"/>
+      <c r="C85" s="4"/>
       <c r="D85" s="5"/>
     </row>
     <row r="86" spans="1:4">
-      <c r="A86" s="6"/>
-      <c r="B86" s="6" t="s">
+      <c r="A86" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C86" s="7"/>
+      <c r="B86" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C86" s="4"/>
       <c r="D86" s="5"/>
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C87" s="4"/>
       <c r="D87" s="5"/>
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C88" s="4"/>
       <c r="D88" s="5"/>
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C89" s="4"/>
       <c r="D89" s="5"/>
     </row>
     <row r="90" spans="1:4">
-      <c r="A90" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="B90" s="3" t="s">
+      <c r="A90" s="6"/>
+      <c r="B90" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="C90" s="4"/>
+      <c r="C90" s="7"/>
       <c r="D90" s="5"/>
     </row>
     <row r="91" spans="1:4">
-      <c r="A91" s="3" t="s">
+      <c r="A91" s="6"/>
+      <c r="B91" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="B91" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="C91" s="4"/>
+      <c r="C91" s="7"/>
       <c r="D91" s="5"/>
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="6"/>
       <c r="B92" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C92" s="7"/>
       <c r="D92" s="5"/>
@@ -2546,7 +2515,7 @@
     <row r="93" spans="1:4">
       <c r="A93" s="6"/>
       <c r="B93" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C93" s="7"/>
       <c r="D93" s="5"/>
@@ -2554,7 +2523,7 @@
     <row r="94" spans="1:4">
       <c r="A94" s="6"/>
       <c r="B94" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C94" s="7"/>
       <c r="D94" s="5"/>
@@ -2562,7 +2531,7 @@
     <row r="95" spans="1:4">
       <c r="A95" s="6"/>
       <c r="B95" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C95" s="7"/>
       <c r="D95" s="5"/>
@@ -2570,7 +2539,7 @@
     <row r="96" spans="1:4">
       <c r="A96" s="6"/>
       <c r="B96" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C96" s="7"/>
       <c r="D96" s="5"/>
@@ -2578,7 +2547,7 @@
     <row r="97" spans="1:4">
       <c r="A97" s="6"/>
       <c r="B97" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C97" s="7"/>
       <c r="D97" s="5"/>
@@ -2586,7 +2555,7 @@
     <row r="98" spans="1:4">
       <c r="A98" s="6"/>
       <c r="B98" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C98" s="7"/>
       <c r="D98" s="5"/>
@@ -2594,7 +2563,7 @@
     <row r="99" spans="1:4">
       <c r="A99" s="6"/>
       <c r="B99" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C99" s="7"/>
       <c r="D99" s="5"/>
@@ -2602,7 +2571,7 @@
     <row r="100" spans="1:4">
       <c r="A100" s="6"/>
       <c r="B100" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C100" s="7"/>
       <c r="D100" s="5"/>
@@ -2610,7 +2579,7 @@
     <row r="101" spans="1:4">
       <c r="A101" s="6"/>
       <c r="B101" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C101" s="7"/>
       <c r="D101" s="5"/>
@@ -2618,7 +2587,7 @@
     <row r="102" spans="1:4">
       <c r="A102" s="6"/>
       <c r="B102" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C102" s="7"/>
       <c r="D102" s="5"/>
@@ -2626,26 +2595,28 @@
     <row r="103" spans="1:4">
       <c r="A103" s="6"/>
       <c r="B103" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C103" s="7"/>
       <c r="D103" s="5"/>
     </row>
     <row r="104" spans="1:4">
-      <c r="A104" s="6"/>
-      <c r="B104" s="6" t="s">
+      <c r="A104" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B104" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="C104" s="7"/>
+      <c r="C104" s="4"/>
       <c r="D104" s="5"/>
     </row>
     <row r="105" spans="1:4">
-      <c r="A105" s="6"/>
-      <c r="B105" s="6" t="s">
+      <c r="A105" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="C105" s="7"/>
-      <c r="D105" s="5"/>
+      <c r="B105" s="1"/>
+      <c r="C105" s="1"/>
+      <c r="D105" s="1"/>
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="3" t="s">
@@ -2658,72 +2629,54 @@
       <c r="D106" s="5"/>
     </row>
     <row r="107" spans="1:4">
-      <c r="A107" s="1" t="s">
+      <c r="A107" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="B107" s="1"/>
-      <c r="C107" s="1"/>
-      <c r="D107" s="1"/>
+      <c r="B107" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C107" s="4"/>
+      <c r="D107" s="5"/>
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C108" s="4"/>
       <c r="D108" s="5"/>
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C109" s="4"/>
       <c r="D109" s="5"/>
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C110" s="4"/>
       <c r="D110" s="5"/>
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C111" s="4"/>
       <c r="D111" s="5"/>
-    </row>
-    <row r="112" spans="1:4">
-      <c r="A112" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="B112" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="C112" s="4"/>
-      <c r="D112" s="5"/>
-    </row>
-    <row r="113" spans="1:4">
-      <c r="A113" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="B113" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="C113" s="4"/>
-      <c r="D113" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -2816,7 +2769,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C105">
+  <conditionalFormatting sqref="C106">
     <cfRule type="cellIs" dxfId="0" priority="389" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -2830,7 +2783,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C106">
+  <conditionalFormatting sqref="C107">
     <cfRule type="cellIs" dxfId="0" priority="393" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -2914,34 +2867,6 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C112">
-    <cfRule type="cellIs" dxfId="0" priority="413" operator="equal">
-      <formula>"voldoet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="414" operator="equal">
-      <formula>"voldoet deels"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="415" operator="equal">
-      <formula>"voldoet niet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="416" operator="equal">
-      <formula>"niet van toepassing"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C113">
-    <cfRule type="cellIs" dxfId="0" priority="417" operator="equal">
-      <formula>"voldoet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="418" operator="equal">
-      <formula>"voldoet deels"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="419" operator="equal">
-      <formula>"voldoet niet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="420" operator="equal">
-      <formula>"niet van toepassing"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="C12">
     <cfRule type="cellIs" dxfId="0" priority="21" operator="equal">
       <formula>"voldoet"</formula>
@@ -3852,7 +3777,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C76">
+  <conditionalFormatting sqref="C77">
     <cfRule type="cellIs" dxfId="0" priority="277" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3866,7 +3791,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C77">
+  <conditionalFormatting sqref="C78">
     <cfRule type="cellIs" dxfId="0" priority="281" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -4202,7 +4127,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="105">
+  <dataValidations count="103">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C7">
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
@@ -4410,12 +4335,12 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C75">
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C76">
-      <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C77">
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C78">
+      <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C79">
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
@@ -4494,12 +4419,12 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C104">
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C105">
-      <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C106">
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C107">
+      <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C108">
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
@@ -4510,12 +4435,6 @@
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C111">
-      <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C112">
-      <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C113">
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4537,7 +4456,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4545,10 +4464,10 @@
     </row>
     <row r="2" spans="1:4" ht="30" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>6</v>

--- a/docs/wip/ICTU-Kwaliteitsaanpak-Checklist.xlsx
+++ b/docs/wip/ICTU-Kwaliteitsaanpak-Checklist.xlsx
@@ -374,12 +374,9 @@
 6. Toegankelijkheidstests,
 7. Broncodekwaliteitscontroles,
 8. Installatie van de software in test, acceptatie en/of productieomgevingen,
-9. Produceren van een "software bill of materials" (SBoM),
-10. Oplevering van het totale product, dus inclusief alle deliverables, in de vorm zoals bruikbaar voor en afgesproken met de opdrachtgevende organisatie.
+9. Oplevering van het totale product, dus inclusief alle deliverables, in de vorm zoals bruikbaar voor en afgesproken met de opdrachtgevende organisatie.
 Performance- en beveiligingstests op de software zijn ook onderdeel van de continuous delivery pipeline, maar vanwege doorlooptijden en licenties is dat niet altijd haalbaar; in dat geval vinden de performance- en beveiligingstests zo veel mogelijk, en bij voorkeur dagelijks, plaats. Performance- en beveiligingstests op de software vinden plaats in de testomgeving van het project. Als ICTU verantwoordelijk is voor het operationeel beheer laat ICTU de performance- en beveiligingstesten op de software (ook) uitvoeren in een productie-like omgeving.
 Niet alle testen en controles kunnen altijd geautomatiseerd worden uitgevoerd. Denk aan kwaliteitscontroles op architectuurbeslissingen of het testen van toegankelijkheidseisen. Waar mogelijk wordt wel een zo groot mogelijk deel van de testen en controles geautomatiseerd en als onderdeel van de pipeline uitgevoerd.
-De afdeling ICTU Software Diensten (ISD) voorziet in tools en ondersteuning, zodat projecten deze pipeline kunnen toepassen. Projecten zijn verantwoordelijk voor de correcte werking van de pipeline.
-ICTU gebruikt Jenkins, GitLab CI of Azure DevOps als tool voor de implementatie van de continuous delivery pipeline. ISD biedt de projecten een voorziening om releases van het totale product veilig op te leveren aan opdrachtgevende organisaties en beheerorganisaties.
 Rationale
 Software incrementeel opleveren vereist dat de software frequent gebouwd, getest en opgeleverd kan worden. Om dit efficiënt en foutvrij te doen, dient het proces van bouwen, testen en opleveren geautomatiseerd te zijn; een continuous delivery pipeline faciliteert dit.
 </t>
@@ -399,7 +396,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B57" authorId="0">
+    <comment ref="B56" authorId="0">
       <text>
         <r>
           <rPr>
@@ -409,52 +406,34 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">M16: Het project gebruikt tools voor vastgestelde taken
-ICTU stelt het gebruik van tools verplicht voor de volgende taken:
-1. product en sprint backlog management en agile werken,
-2. inrichten en uitvoeren van een continuous delivery pipeline,
-3. monitoren van de kwaliteit van broncode,
-4. versiebeheer van op te leveren producten,
-5. release van software,
-6. maken van testrapportages,
-7. maken van kwaliteitsrapportages,
-8. controleren van de configuratie op aanwezigheid van bekende kwetsbaarheden,
-9. controleren van door de applicatie gebruikte versies van externe software op aanwezigheid van bekende kwetsbaarheden,
-10. statische controle van de software op aanwezigheid van kwetsbare constructies,
-11. dynamische controle van de software op aanwezigheid van kwetsbare constructies,
-12. controleren van container images op aanwezigheid van bekende kwetsbaarheden,
-13. testen van performance en schaalbaarheid,
-14. testen op toegankelijkheid van de applicatie,
-15. produceren van een "software bill of materials" (SBoM),
-16. opslaan van artifacten,
-17. registratie van incidenten bij gebruik en beheer, en
-18. bij het uitvoeren van operationeel beheer; uitrollen van de software in de productieomgeving.
-Onder het ondersteunen van "agile werken" vallen het opvoeren van eisen, het opvoeren van logische testgevallen, het koppelen van logische testgevallen aan eisen, het bijhouden van een werkvoorraad, het plannen van iteraties en het toewijzen van eisen aan iteraties. De 'eisen' worden, conform Scrumterminologie, geregistreerd als epics en/of user stories, de werkvoorraad als product backlog en de iteraties als sprints. Het toewijzen van eisen aan iteraties gebeurt via de sprint backlog.
-ICTU adviseert en ondersteunt voor de genoemde taken onderstaande tools. Projecten gebruiken deze tools, of gelijkwaardige alternatieven:
-1. product en sprint backlog management en agile werken: Azure DevOps of Jira,
-2. inrichten en uitvoeren van een continuous delivery pipeline: Jenkins, GitLab CI/CD (Continuous Integration, Delivery, and Deployment) of Azure DevOps,
-3. monitoren van de kwaliteit van broncode: SonarQube,
-4. versiebeheer van op te leveren producten: GitLab of Azure DevOps,
-5. release van software: Releaseserver in het ontwikkelplatform,
-6. maken van testrapportages: JUnit, Robot Framework, TestNG, of hiermee compatible tools,
-7. maken van kwaliteitsrapportages: Quality-time,
-8. controleren van de configuratie op aanwezigheid van bekende kwetsbaarheden in configuratie: OpenVAS (Vulnerability Assessment System),
-9. controleren op aanwezigheid van bekende kwetsbaarheden in externe software: OWASP (Open Web Application Security Project) Dependency-Check en/of Dependency-Track,
-10. statische controle van de software op aanwezigheid van kwetsbare constructies: SonarQube,
-11. dynamische controle van de software op aanwezigheid van kwetsbare constructies: ZAP (Zed Attack Proxy) by Checkmarx,
-12. controleren van container images op aanwezigheid van bekende kwetsbaarheden: Trivy,
-13. testen van performance en schaalbaarheid: JMeter en Performancetestrunner,
-14. testen op toegankelijkheid van de applicatie: Axe,
-15. produceren van een "software bill of materials" (SBoM): tools die een SBoM in CycloneDX-formaat (zie https://cyclonedx.org) genereren,
-16. opslaan van artifacten: Nexus of Harbor,
-17. registratie van incidenten bij gebruik en beheer: Jira, en
-18. bij het uitvoeren van operationeel beheer; uitrollen van de software in de productieomgeving: Ansible.
+Voor vastgestelde taken bij het ontwikkelen, onderhouden en operationeel beheren van software, stelt ICTU het gebruik van tools verplicht. ICTU adviseert per taak specifieke tools en ondersteunt projecten bij het gebruik daarvan.
+ICTU adviseert en ondersteunt voor de hieronder genoemde taken specifieke tools. Projecten gebruiken deze tools, of gelijkwaardige alternatieven.
+Activiteit                                                                                   Tools                                                                                    
+Product en sprint backlog management en agile werken                                         Azure DevOps of Jira                                                                     
+Inrichten en uitvoeren van een continuous delivery pipeline                                  Jenkins, GitLab CI/CD (Continuous Integration, Delivery, and Deployment) of Azure DevOps 
+Monitoren van de kwaliteit van broncode                                                      SonarQube                                                                                
+Versiebeheer van op te leveren producten                                                     GitLab of Azure DevOps                                                                   
+Release van software                                                                         Releaseserver in het ontwikkelplatform                                                   
+Maken van testrapportages                                                                    JUnit, Robot Framework, TestNG, of hiermee compatible tools                              
+Maken van kwaliteitsrapportages                                                              Quality-time                                                                             
+Controleren op aanwezigheid van bekende kwetsbaarheden in externe software                   OWASP (Open Web Application Security Project) Dependency-Check en/of Dependency-Track    
+Statische controle van de software op aanwezigheid van kwetsbare constructies                SonarQube                                                                                
+Dynamische controle van de software op aanwezigheid van kwetsbare constructies               ZAP (Zed Attack Proxy) by Checkmarx                                                      
+Controleren van container images op aanwezigheid van bekende kwetsbaarheden                  Trivy                                                                                    
+Testen van performance en schaalbaarheid                                                     JMeter en Performancetestrunner                                                          
+Testen op toegankelijkheid van de applicatie                                                 Axe                                                                                      
+Produceren van een "software bill of materials" (SBoM)                                       Tools die een SBoM in CycloneDX-formaat (zie https://cyclonedx.org) genereren            
+Opslaan van artifacten                                                                       Nexus of Harbor                                                                          
+Registratie van incidenten bij gebruik en beheer                                             Jira                                                                                     
+Bij het uitvoeren van operationeel beheer; uitrollen van de software in de productieomgeving Ansible                                                                                  
+N.B. Onder het ondersteunen van "agile werken" vallen het opvoeren van eisen, het opvoeren van logische testgevallen, het koppelen van logische testgevallen aan eisen, het bijhouden van een werkvoorraad, het plannen van iteraties en het toewijzen van eisen aan iteraties. De 'eisen' worden, conform Scrumterminologie, geregistreerd als epics en/of user stories, de werkvoorraad als product backlog en de iteraties als sprints. Het toewijzen van eisen aan iteraties gebeurt via de sprint backlog.
 Rationale
 Projecten hebben een redelijke vrijheid bij het kiezen en gebruiken van tools, maar voor een aantal taken is het gebruik verplicht gesteld. Deze tools zijn nodig voor een efficiënte uitvoering van de Kwaliteitsaanpak. Uniform gebruik van deze tools maakt het mogelijk koppeling tussen die tools voor alle projecten te standaardiseren; daarnaast bevordert het de uitwisselbaarheid van medewerkers en neemt het risico op het gebruik van onvolwassen tools af. Tot slot is het gebruik in een aantal gevallen, ten behoeve van informatiebeveiliging bij de overheid, verplicht.
 </t>
         </r>
       </text>
     </comment>
-    <comment ref="C57" authorId="0">
+    <comment ref="C56" authorId="0">
       <text>
         <r>
           <rPr>
@@ -467,7 +446,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B76" authorId="0">
+    <comment ref="B74" authorId="0">
       <text>
         <r>
           <rPr>
@@ -487,7 +466,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B77" authorId="0">
+    <comment ref="B75" authorId="0">
       <text>
         <r>
           <rPr>
@@ -509,7 +488,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B79" authorId="0">
+    <comment ref="B77" authorId="0">
       <text>
         <r>
           <rPr>
@@ -530,7 +509,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B80" authorId="0">
+    <comment ref="B78" authorId="0">
       <text>
         <r>
           <rPr>
@@ -547,7 +526,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B81" authorId="0">
+    <comment ref="B79" authorId="0">
       <text>
         <r>
           <rPr>
@@ -564,7 +543,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B82" authorId="0">
+    <comment ref="B80" authorId="0">
       <text>
         <r>
           <rPr>
@@ -587,7 +566,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C82" authorId="0">
+    <comment ref="C80" authorId="0">
       <text>
         <r>
           <rPr>
@@ -600,7 +579,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B87" authorId="0">
+    <comment ref="B85" authorId="0">
       <text>
         <r>
           <rPr>
@@ -621,7 +600,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B88" authorId="0">
+    <comment ref="B86" authorId="0">
       <text>
         <r>
           <rPr>
@@ -646,7 +625,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B89" authorId="0">
+    <comment ref="B87" authorId="0">
       <text>
         <r>
           <rPr>
@@ -673,7 +652,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B90" authorId="0">
+    <comment ref="B88" authorId="0">
       <text>
         <r>
           <rPr>
@@ -691,7 +670,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B91" authorId="0">
+    <comment ref="B89" authorId="0">
       <text>
         <r>
           <rPr>
@@ -723,7 +702,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C91" authorId="0">
+    <comment ref="C89" authorId="0">
       <text>
         <r>
           <rPr>
@@ -736,7 +715,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B106" authorId="0">
+    <comment ref="B104" authorId="0">
       <text>
         <r>
           <rPr>
@@ -756,7 +735,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B108" authorId="0">
+    <comment ref="B106" authorId="0">
       <text>
         <r>
           <rPr>
@@ -776,7 +755,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B109" authorId="0">
+    <comment ref="B107" authorId="0">
       <text>
         <r>
           <rPr>
@@ -795,7 +774,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B110" authorId="0">
+    <comment ref="B108" authorId="0">
       <text>
         <r>
           <rPr>
@@ -806,7 +785,7 @@
           </rPr>
           <t xml:space="preserve">M18: ICTU biedt ondersteuning voor verplicht gestelde tools
 ICTU zorgt voor technische en functionele ondersteuning aan projecten bij het gebruik van alle verplichte tools.
-ICTU zorgt voor ondersteuning van de bij M16: Het project gebruikt tools voor vastgestelde taken verplicht gestelde tools. Een team van specialisten met kennis, ervaring en capaciteit is beschikbaar voor ondersteuning aan projecten.
+ICTU zorgt voor ondersteuning van de in M16: Het project gebruikt tools voor vastgestelde taken verplicht gestelde tools. Een team van specialisten met kennis, ervaring en capaciteit is beschikbaar voor ondersteuning aan projecten. Projecten zijn verantwoordelijk voor de correcte werking van de pipeline.
 Bij de selectie van tools ter ondersteuning van de projectuitvoering geeft ICTU de voorkeur aan open source tools. Ook tools die ICTU zelf ontwikkelt ter ondersteuning van softwareontwikkelprojecten worden bij voorkeur open source beschikbaar gesteld.
 Rationale
 De keuze om het gebruik van een aantal tools verplicht te stellen (M16: Het project gebruikt tools voor vastgestelde taken) volgt uit de belangrijke rol die die tools spelen in de ontwikkelstraat en in Quality-time, het kwaliteitssysteem van ICTU. Met de verplichting komt ook een verantwoordelijkheid: om projecten in staat te stellen snel en effectief met deze tools te werken, moeten die projecten ondersteund worden.
@@ -816,7 +795,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B111" authorId="0">
+    <comment ref="B109" authorId="0">
       <text>
         <r>
           <rPr>
@@ -835,7 +814,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B112" authorId="0">
+    <comment ref="B110" authorId="0">
       <text>
         <r>
           <rPr>
@@ -853,7 +832,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B113" authorId="0">
+    <comment ref="B111" authorId="0">
       <text>
         <r>
           <rPr>
@@ -884,9 +863,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="146">
-  <si>
-    <t>Onderstaande checklist kan gebruikt worden voor het uitvoeren van een assessment tegen de ICTU Kwaliteitsaanpak Softwareontwikkeling versie wip, 04-03-2025.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="144">
+  <si>
+    <t>Onderstaande checklist kan gebruikt worden voor het uitvoeren van een assessment tegen de ICTU Kwaliteitsaanpak Softwareontwikkeling versie wip, 21-03-2025.</t>
   </si>
   <si>
     <t>Gebruik de 'Status' kolom om aan te geven in hoeverre een maatregel uit de Kwaliteitsaanpak is toegepast. Bij maatregelen met submaatregelen hoeft alleen de status van de submaatregelen te worden ingevuld.</t>
@@ -1081,10 +1060,7 @@
     <t>8. Installatie van de software in test, acceptatie en/of productieomgevingen,</t>
   </si>
   <si>
-    <t>9. Produceren van een "software bill of materials" (SBoM),</t>
-  </si>
-  <si>
-    <t>10. Oplevering van het totale product, dus inclusief alle deliverables, in de vorm zoals bruikbaar voor en afgesproken met de opdrachtgevende organisatie.</t>
+    <t>9. Oplevering van het totale product, dus inclusief alle deliverables, in de vorm zoals bruikbaar voor en afgesproken met de opdrachtgevende organisatie.</t>
   </si>
   <si>
     <t>M16</t>
@@ -1093,58 +1069,55 @@
     <t>Het project gebruikt tools voor vastgestelde taken</t>
   </si>
   <si>
-    <t>1. product en sprint backlog management en agile werken: Azure DevOps of Jira,</t>
-  </si>
-  <si>
-    <t>2. inrichten en uitvoeren van een continuous delivery pipeline: Jenkins, GitLab CI/CD (Continuous Integration, Delivery, and Deployment) of Azure DevOps,</t>
-  </si>
-  <si>
-    <t>3. monitoren van de kwaliteit van broncode: SonarQube,</t>
-  </si>
-  <si>
-    <t>4. versiebeheer van op te leveren producten: GitLab of Azure DevOps,</t>
-  </si>
-  <si>
-    <t>5. release van software: Releaseserver in het ontwikkelplatform,</t>
-  </si>
-  <si>
-    <t>6. maken van testrapportages: JUnit, Robot Framework, TestNG, of hiermee compatible tools,</t>
-  </si>
-  <si>
-    <t>7. maken van kwaliteitsrapportages: Quality-time,</t>
-  </si>
-  <si>
-    <t>8. controleren van de configuratie op aanwezigheid van bekende kwetsbaarheden in configuratie: OpenVAS (Vulnerability Assessment System),</t>
-  </si>
-  <si>
-    <t>9. controleren op aanwezigheid van bekende kwetsbaarheden in externe software: OWASP (Open Web Application Security Project) Dependency-Check en/of Dependency-Track,</t>
-  </si>
-  <si>
-    <t>10. statische controle van de software op aanwezigheid van kwetsbare constructies: SonarQube,</t>
-  </si>
-  <si>
-    <t>11. dynamische controle van de software op aanwezigheid van kwetsbare constructies: ZAP (Zed Attack Proxy) by Checkmarx,</t>
-  </si>
-  <si>
-    <t>12. controleren van container images op aanwezigheid van bekende kwetsbaarheden: Trivy,</t>
-  </si>
-  <si>
-    <t>13. testen van performance en schaalbaarheid: JMeter en Performancetestrunner,</t>
-  </si>
-  <si>
-    <t>14. testen op toegankelijkheid van de applicatie: Axe,</t>
-  </si>
-  <si>
-    <t>15. produceren van een "software bill of materials" (SBoM): tools die een SBoM in CycloneDX-formaat (zie https://cyclonedx.org) genereren,</t>
-  </si>
-  <si>
-    <t>16. opslaan van artifacten: Nexus of Harbor,</t>
-  </si>
-  <si>
-    <t>17. registratie van incidenten bij gebruik en beheer: Jira, en</t>
-  </si>
-  <si>
-    <t>18. bij het uitvoeren van operationeel beheer; uitrollen van de software in de productieomgeving: Ansible.</t>
+    <t>1. Product en sprint backlog management en agile werken</t>
+  </si>
+  <si>
+    <t>2. Inrichten en uitvoeren van een continuous delivery pipeline</t>
+  </si>
+  <si>
+    <t>3. Monitoren van de kwaliteit van broncode</t>
+  </si>
+  <si>
+    <t>4. Versiebeheer van op te leveren producten</t>
+  </si>
+  <si>
+    <t>5. Release van software</t>
+  </si>
+  <si>
+    <t>6. Maken van testrapportages</t>
+  </si>
+  <si>
+    <t>7. Maken van kwaliteitsrapportages</t>
+  </si>
+  <si>
+    <t>8. Controleren op aanwezigheid van bekende kwetsbaarheden in externe software</t>
+  </si>
+  <si>
+    <t>9. Statische controle van de software op aanwezigheid van kwetsbare constructies</t>
+  </si>
+  <si>
+    <t>10. Dynamische controle van de software op aanwezigheid van kwetsbare constructies</t>
+  </si>
+  <si>
+    <t>11. Controleren van container images op aanwezigheid van bekende kwetsbaarheden</t>
+  </si>
+  <si>
+    <t>12. Testen van performance en schaalbaarheid</t>
+  </si>
+  <si>
+    <t>13. Testen op toegankelijkheid van de applicatie</t>
+  </si>
+  <si>
+    <t>14. Produceren van een "software bill of materials" (SBoM)</t>
+  </si>
+  <si>
+    <t>15. Opslaan van artifacten</t>
+  </si>
+  <si>
+    <t>16. Registratie van incidenten bij gebruik en beheer</t>
+  </si>
+  <si>
+    <t>17. Bij het uitvoeren van operationeel beheer; uitrollen van de software in de productieomgeving</t>
   </si>
   <si>
     <t>M08</t>
@@ -1752,7 +1725,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D113"/>
+  <dimension ref="A1:D111"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -2224,21 +2197,21 @@
       <c r="D55" s="5"/>
     </row>
     <row r="56" spans="1:4">
-      <c r="A56" s="6"/>
-      <c r="B56" s="6" t="s">
+      <c r="A56" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C56" s="7"/>
+      <c r="B56" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C56" s="4"/>
       <c r="D56" s="5"/>
     </row>
     <row r="57" spans="1:4">
-      <c r="A57" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B57" s="3" t="s">
+      <c r="A57" s="6"/>
+      <c r="B57" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="C57" s="4"/>
+      <c r="C57" s="7"/>
       <c r="D57" s="5"/>
     </row>
     <row r="58" spans="1:4">
@@ -2370,87 +2343,87 @@
       <c r="D73" s="5"/>
     </row>
     <row r="74" spans="1:4">
-      <c r="A74" s="6"/>
-      <c r="B74" s="6" t="s">
+      <c r="A74" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C74" s="7"/>
+      <c r="B74" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C74" s="4"/>
       <c r="D74" s="5"/>
     </row>
     <row r="75" spans="1:4">
-      <c r="A75" s="6"/>
-      <c r="B75" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="C75" s="7"/>
+      <c r="A75" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C75" s="4"/>
       <c r="D75" s="5"/>
     </row>
     <row r="76" spans="1:4">
-      <c r="A76" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="C76" s="4"/>
-      <c r="D76" s="5"/>
+      <c r="A76" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B76" s="1"/>
+      <c r="C76" s="1"/>
+      <c r="D76" s="1"/>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C77" s="4"/>
       <c r="D77" s="5"/>
     </row>
     <row r="78" spans="1:4">
-      <c r="A78" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B78" s="1"/>
-      <c r="C78" s="1"/>
-      <c r="D78" s="1"/>
+      <c r="A78" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C78" s="4"/>
+      <c r="D78" s="5"/>
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C79" s="4"/>
       <c r="D79" s="5"/>
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C80" s="4"/>
       <c r="D80" s="5"/>
     </row>
     <row r="81" spans="1:4">
-      <c r="A81" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="B81" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="C81" s="4"/>
+      <c r="A81" s="6"/>
+      <c r="B81" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C81" s="7"/>
       <c r="D81" s="5"/>
     </row>
     <row r="82" spans="1:4">
-      <c r="A82" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="B82" s="3" t="s">
+      <c r="A82" s="6"/>
+      <c r="B82" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="C82" s="4"/>
+      <c r="C82" s="7"/>
       <c r="D82" s="5"/>
     </row>
     <row r="83" spans="1:4">
@@ -2470,69 +2443,69 @@
       <c r="D84" s="5"/>
     </row>
     <row r="85" spans="1:4">
-      <c r="A85" s="6"/>
-      <c r="B85" s="6" t="s">
+      <c r="A85" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C85" s="7"/>
+      <c r="B85" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C85" s="4"/>
       <c r="D85" s="5"/>
     </row>
     <row r="86" spans="1:4">
-      <c r="A86" s="6"/>
-      <c r="B86" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="C86" s="7"/>
+      <c r="A86" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C86" s="4"/>
       <c r="D86" s="5"/>
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C87" s="4"/>
       <c r="D87" s="5"/>
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C88" s="4"/>
       <c r="D88" s="5"/>
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C89" s="4"/>
       <c r="D89" s="5"/>
     </row>
     <row r="90" spans="1:4">
-      <c r="A90" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="B90" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C90" s="4"/>
+      <c r="A90" s="6"/>
+      <c r="B90" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C90" s="7"/>
       <c r="D90" s="5"/>
     </row>
     <row r="91" spans="1:4">
-      <c r="A91" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="B91" s="3" t="s">
+      <c r="A91" s="6"/>
+      <c r="B91" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="C91" s="4"/>
+      <c r="C91" s="7"/>
       <c r="D91" s="5"/>
     </row>
     <row r="92" spans="1:4">
@@ -2632,98 +2605,82 @@
       <c r="D103" s="5"/>
     </row>
     <row r="104" spans="1:4">
-      <c r="A104" s="6"/>
-      <c r="B104" s="6" t="s">
+      <c r="A104" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="C104" s="7"/>
+      <c r="B104" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C104" s="4"/>
       <c r="D104" s="5"/>
     </row>
     <row r="105" spans="1:4">
-      <c r="A105" s="6"/>
-      <c r="B105" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="C105" s="7"/>
-      <c r="D105" s="5"/>
+      <c r="A105" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B105" s="1"/>
+      <c r="C105" s="1"/>
+      <c r="D105" s="1"/>
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C106" s="4"/>
       <c r="D106" s="5"/>
     </row>
     <row r="107" spans="1:4">
-      <c r="A107" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="B107" s="1"/>
-      <c r="C107" s="1"/>
-      <c r="D107" s="1"/>
+      <c r="A107" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C107" s="4"/>
+      <c r="D107" s="5"/>
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C108" s="4"/>
       <c r="D108" s="5"/>
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C109" s="4"/>
       <c r="D109" s="5"/>
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C110" s="4"/>
       <c r="D110" s="5"/>
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C111" s="4"/>
       <c r="D111" s="5"/>
-    </row>
-    <row r="112" spans="1:4">
-      <c r="A112" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="B112" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="C112" s="4"/>
-      <c r="D112" s="5"/>
-    </row>
-    <row r="113" spans="1:4">
-      <c r="A113" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="B113" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="C113" s="4"/>
-      <c r="D113" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -2816,7 +2773,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C105">
+  <conditionalFormatting sqref="C106">
     <cfRule type="cellIs" dxfId="0" priority="389" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -2830,7 +2787,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C106">
+  <conditionalFormatting sqref="C107">
     <cfRule type="cellIs" dxfId="0" priority="393" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -2914,34 +2871,6 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C112">
-    <cfRule type="cellIs" dxfId="0" priority="413" operator="equal">
-      <formula>"voldoet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="414" operator="equal">
-      <formula>"voldoet deels"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="415" operator="equal">
-      <formula>"voldoet niet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="416" operator="equal">
-      <formula>"niet van toepassing"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C113">
-    <cfRule type="cellIs" dxfId="0" priority="417" operator="equal">
-      <formula>"voldoet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="418" operator="equal">
-      <formula>"voldoet deels"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="419" operator="equal">
-      <formula>"voldoet niet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="420" operator="equal">
-      <formula>"niet van toepassing"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="C12">
     <cfRule type="cellIs" dxfId="0" priority="21" operator="equal">
       <formula>"voldoet"</formula>
@@ -3852,7 +3781,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C76">
+  <conditionalFormatting sqref="C77">
     <cfRule type="cellIs" dxfId="0" priority="277" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3866,7 +3795,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C77">
+  <conditionalFormatting sqref="C78">
     <cfRule type="cellIs" dxfId="0" priority="281" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -4202,7 +4131,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="105">
+  <dataValidations count="103">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C7">
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
@@ -4410,12 +4339,12 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C75">
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C76">
-      <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C77">
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C78">
+      <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C79">
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
@@ -4494,12 +4423,12 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C104">
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C105">
-      <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C106">
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C107">
+      <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C108">
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
@@ -4510,12 +4439,6 @@
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C111">
-      <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C112">
-      <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C113">
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4537,7 +4460,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4545,10 +4468,10 @@
     </row>
     <row r="2" spans="1:4" ht="30" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>6</v>

--- a/docs/wip/ICTU-Kwaliteitsaanpak-Checklist.xlsx
+++ b/docs/wip/ICTU-Kwaliteitsaanpak-Checklist.xlsx
@@ -29,15 +29,32 @@
             <rFont val="Courier"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">M31: Het project beschikt over actuele vastgestelde informatie
-Voor een goede uitvoering van het project is specifieke informatie nodig. De opdrachtgevende organisatie zorgt dat het project bij de start van de voorfase inzicht heeft in de informatie die typisch wordt vastgelegd in een projectstartarchitectuur, business impact analyse en privacy impact assessment. Waar nodig werkt de opdrachtgevende organisatie de informatie bij tijdens de voorfase en realisatiefase.
-De opdrachtgevende organisatie zorgt dat het project vanaf de start van de voorfase beschikt over:
-1. Projectstartarchitectuur,
-2. Business impact analyse,
-3. Privacy impact assessment,
-4. Afspraken tussen opdrachtgevende organisatie en beheerorganisatie.
-Tevens onderhoudt de opdrachtgevende organisatie deze informatie tijdens de voorfase en realisatiefase.
-Als de benodigde informatie niet gereed is bij de start van de voorfase dan maken opdrachtgevende organisatie en ICTU nadere afspraken over de manier waarop de benodigde informatie nog tijdens de voorfase beschikbaar komt voor het project.
+          <t xml:space="preserve">M01: Het project ontvangt en levert in elke fase vastgestelde producten en informatie
+Iedere projectfase heeft informatie nodig en levert informatie op. De opdrachtgevende organisatie zorgt dat het project bij de start van de voorfase inzicht heeft in de informatie die typisch wordt vastgelegd in een projectstartarchitectuur, business impact analyse en privacy impact assessment. Waar nodig werkt de opdrachtgevende organisatie de informatie bij tijdens de voorfase en realisatiefase. De voorfase levert inzicht in de functionele en niet-functionele eisen, ontwerp en architectuur, testplannen, operationele risico's, en benodigde kwaliteitsmaatregelen. Deze informatie wordt tijdens de realisatiefase waar nodig bijgewerkt. De realisatiefase levert één of meerdere werkende versies van de software met regressietests, aangevuld met een vrijgaveadvies, release notes en installatiedocumentatie.
+Opdrachtgevende organisatie, ICTU, beheerorganisatie en andere meewerkende partijen leveren de onderstaande informatie op. Voor een aantal documenten zijn als onderdeel van de Kwaliteitsaanpak templates beschikbaar. Ook kan gebruik worden gemaakt van bestaande templates uit bijvoorbeeld de NORA. Zie M29: ICTU organiseert voor aanvang van een project de interne dienstverlening.
+De onderstaande tabel bevat de in deze paragraaf beschreven producten. Het vinkje (✔) geeft aan in welke fase ze (initieel) worden opgeleverd. Het tandwiel (⚙) geeft aan in welke fase de producten worden onderhouden en bijgewerkt.
+Product                                             Voor start Voorfase Realisatiefase Verantwoordelijke organisatie 
+Projectstartarchitectuur                            x          o        o              opdrachtgever                 
+Business impact analyse                             x          o        o              opdrachtgever                 
+Privacy impact assessment                           x          o        o              opdrachtgever                 
+Beheerafspraken                                     x          o        o              opdrachtgever                 
+Aanvullende informatie                              x          o        o              opdrachtgever                 
+Plan van aanpak: voorfase                           x                                  ICTU                          
+Beschrijving van functionele eisen                             x        o              opdrachtgever                 
+Beschrijving van niet-functionele eisen                        x        o              opdrachtgever                 
+Product backlog                                                x        o              opdrachtgever                 
+Ontwerp- en architectuurdocumentatie                           x        o              ICTU, beheerorganisatie       
+Mastertestplan                                                 x        o              opdrachtgever                 
+Detailtestplannen                                              x        o              ICTU, beheerorganisatie       
+Informatiebeveiligingsplan                                     x        o              opdrachtgever                 
+Kwaliteitsplan                                                 x        o              ICTU                          
+Plan van aanpak: realisatiefase                                x                       ICTU                          
+Deploybare versie van de software                                       x              ICTU                          
+Testrapportages                                                         x              ICTU, beheerorganisatie       
+Documentatie voor deployment en operationeel beheer                     x              ICTU                          
+Software bill of materials                                              x              ICTU                          
+Release notes                                                           x              ICTU                          
+Vrijgaveadvies                                                          x              opdrachtgever                 
 Projectstartarchitectuur
 Een projectstartarchitectuur (PSA) is bedoeld om te borgen dat nieuwe ontwikkelingen en veranderingen in samenhang worden gerealiseerd en passen binnen de toekomstig gewenste informatievoorziening. De PSA is een concreet en doelgericht ICT-architectuurkader waarbinnen het project moet worden uitgevoerd. In de PSA zijn de architectuurvisie, enterprise-architectuur en overige architecturen van de opdrachtgevende organisatie vertaald naar aan het product te stellen eisen. Een PSA bevat in ieder geval de volgende onderwerpen:
 - Een beschrijving van de doelen en ambities waaraan het project bijdraagt en invulling geeft. Dus niet de projectdoelen en -ambitie.
@@ -55,66 +72,11 @@
 Privacy impact assessment
 In een privacy impact assessment (PIA) legt de opdrachtgevende organisatie vast wat de privacy-gevoeligheid is van de gegevens die in een proces of informatiesysteem worden verzameld en verwerkt. De rechtmatigheid van de verwerking wordt beoordeeld. En de PIA stelt grenzen aan de gegevens die mogen worden verzameld en verwerkt. Zicht op privacygevoelige gegevens en het (laten) treffen van adequate en afdoende beschermingsmaatregelen is een wettelijke plicht die een organisatie niet aan een andere partij kan overdragen.
 Als een PIA niet nodig is, dan is een verklaring daaromtrent vereist.
-Afspraken tussen opdrachtgevende organisatie en beheerorganisatie
+Beheerafspraken
 De opdrachtgevende organisatie heeft afspraken gemaakt met een (interne of externe) beheerorganisatie die voornemens is het beheer van de software uit te voeren. De afspraken omvatten in ieder geval de inzet van medewerkers van de beheerorganisatie tijdens de voorfase en het type beheer dat de beheerorganisatie voornemens is te gaan uitvoeren: operationeel beheer, applicatiebeheer en/of functioneel beheer.
 De beheerorganisatie stelt relevante informatie ter beschikking aan het project zoals beveiligingsbeleid, beheeracceptatiecriteria, documentatie van de te gebruiken voorzieningen voor bijvoorbeeld authenticatie en autorisatie en verder te hanteren kaders en richtlijnen.
 Aanvullende informatie
 Waar mogelijk stelt de opdrachtgevende organisatie ook andere relevante informatie ter beschikking aan het project zoals een eventueel programma van eisen, procesbeschrijvingen van te ondersteunen bedrijfsprocessen, documentatie van te koppelen systemen en verder te hanteren kaders en richtlijnen.
-Rationale
-De genoemde producten hebben tot doel om de benodigde omvang, kosten en doorlooptijd van de voorfase te kunnen schatten. De projectstartarchitectuur vormt input voor de tijdens de voorfase te ontwikkelen producten zoals functionele en niet-functionele eisen, functioneel ontwerp en softwarearchitectuur. Een BIA en eventuele PIA zijn richtinggevend voor de in de voorfase te selecteren beveiligingsmaatregelen.
-Als deze producten er niet zijn, niet actueel zijn, en/of niet compleet zijn, dan moeten ze in de voorfase alsnog worden gemaakt, bijgewerkt en/of aangevuld. Dit vereist grote betrokkenheid van de opdrachtgevende organisatie, en is in de regel lastig op korte termijn te organiseren.
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C7" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Tip: bepaal eerst de status per submaatregel en daarna de status van de hoofdmaatregel.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B12" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Courier"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">M01: Het project levert in elke fase vastgestelde producten en informatie op
-Iedere projectfase levert specifieke informatie op. De voorfase levert inzicht in de functionele en niet-functionele eisen, ontwerp en architectuur, testplannen, operationele risico's, en benodigde kwaliteitsmaatregelen. Deze informatie wordt tijdens de realisatiefase waar nodig bijgewerkt. De realisatiefase levert één of meerdere werkende versies van de software met regressietests, aangevuld met een vrijgaveadvies, release notes en installatiedocumentatie.
-Opdrachtgevende organisatie, ICTU, beheerorganisatie en andere meewerkende partijen leveren de onderstaande informatie op. Voor een aantal documenten zijn als onderdeel van de Kwaliteitsaanpak templates beschikbaar. Ook kan gebruik worden gemaakt van bestaande templates uit bijvoorbeeld de NORA. Zie M29: ICTU organiseert voor aanvang van een project de interne dienstverlening.
-De onderstaande tabel bevat de in deze paragraaf beschreven producten. Het vinkje (✔) geeft aan in welke fase ze (initieel) worden opgeleverd. Het tandwiel (⚙) geeft aan in welke fase de producten worden onderhouden en bijgewerkt.
-Product                                             Voor start Voorfase Realisatiefase Verantwoordelijke organisatie 
-Projectstartarchitectuur                            x          o        o              opdrachtgever                 
-Business impact analyse                             x          o        o              opdrachtgever                 
-Privacy impact assessment                           x          o        o              opdrachtgever                 
-Plan van aanpak: voorfase                           x                                  ICTU                          
-Beschrijving van functionele eisen                             x        o              opdrachtgever                 
-Beschrijving van niet-functionele eisen                        x        o              opdrachtgever                 
-Product backlog                                                x        o              opdrachtgever                 
-Ontwerp- en architectuurdocumentatie                           x        o              ICTU, beheerorganisatie       
-Mastertestplan                                                 x        o              opdrachtgever                 
-Detailtestplannen                                              x        o              ICTU, beheerorganisatie       
-Informatiebeveiligingsplan                                     x        o              opdrachtgever                 
-Kwaliteitsplan                                                 x        o              ICTU                          
-Plan van aanpak: realisatiefase                                x                       ICTU                          
-Deploybare versie van de software                                       x              ICTU                          
-Testrapportages                                                         x              ICTU, beheerorganisatie       
-Documentatie voor deployment en operationeel beheer                     x              ICTU                          
-Software bill of materials                                              x              ICTU                          
-Release notes                                                           x              ICTU                          
-Vrijgaveadvies                                                          x              opdrachtgever                 
-Projectstartarchitectuur, business impact analyse en privacy impact assessment
-De opdrachtgevende organisatie zorgt dat het project bij de start van de voorfase inzicht heeft in de informatie die typisch wordt vastgelegd in een projectstartarchitectuur, business impact analyse en privacy impact assessment. Zie M31: Het project beschikt over actuele vastgestelde informatie.
 Plan van aanpak
 Het plan van aanpak voor de voorfase en het plan van aanpak voor de realisatiefase beschrijven de in deze fasen te realiseren producten en diensten, en de planning, werkwijze en verantwoordelijkheden voor de totstandkoming van die producten en diensten.
 Als tijdens de realisatiefase van het project bestaande software dient te worden afgebouwd, onderhouden en/of herbouwd, bevat het plan van aanpak voor de voorfase een onderzoek naar de kwaliteit van deze software, zie M32: Het project onderzoekt de kwaliteit van over te nemen software.
@@ -189,13 +151,15 @@
 Bovenstaande figuur laat de belangrijkste relaties zien tussen de verschillende producten die de input en output van de voorfase vormen. Naast de informatiestromen zoals door de pijlen weergegeven zijn er in de praktijk nog meer verbanden tussen de producten. Zo kan de gekozen oplossing in de architectuur van invloed zijn op de maatregelen in het informatiebeveiligingsplan of leiden niet-functionele eisen tot extra functionele eisen.
 Rationale
 Het uniformeren van op te leveren producten biedt voordelen voor planning (het is bekend welke producten gemaakt moeten worden), voor bemensing (het is bekend welke expertise nodig is) en voor het uitwisselen van medewerkers.
-De voorgeschreven producten stellen de beheerorganisatie in staat om de opgeleverde software uit te rollen, te beheren en eventueel te onderhouden. Daarnaast is duidelijk welke eventueel openstaande punten er nog zijn. De voorgeschreven producten bieden voldoende verantwoording richting de ontvanger voor uitgevoerde werkzaamheden.
+De genoemde producten die voor start beschikbaar zijn hebben tot doel om de benodigde omvang, kosten en doorlooptijd van de voorfase te kunnen schatten. De projectstartarchitectuur vormt input voor de tijdens de voorfase te ontwikkelen producten zoals functionele en niet-functionele eisen, functioneel ontwerp en softwarearchitectuur. Een BIA en eventuele PIA zijn richtinggevend voor de in de voorfase te selecteren beveiligingsmaatregelen.
+Als deze producten er niet zijn, niet actueel zijn, en/of niet compleet zijn, dan moeten ze in de voorfase alsnog worden gemaakt, bijgewerkt en/of aangevuld. Dit vereist grote betrokkenheid van de opdrachtgevende organisatie, en is in de regel lastig op korte termijn te organiseren.
 De genoemde producten uit de voorfase hebben tot doel om enerzijds de omvang, kosten en doorlooptijd van de realisatiefase te kunnen schatten en anderzijds om de kaders voor de realisatiefase te bepalen, zodat de scope, aanpak en oplossingsrichting in grote lijnen bekend zijn.
+De voorgeschreven producten uit de realisatiefase stellen de beheerorganisatie in staat om de opgeleverde software uit te rollen, te beheren en eventueel te onderhouden. Daarnaast is duidelijk welke eventueel openstaande punten er nog zijn. De voorgeschreven producten bieden voldoende verantwoording richting de ontvanger voor uitgevoerde werkzaamheden.
 </t>
         </r>
       </text>
     </comment>
-    <comment ref="C12" authorId="0">
+    <comment ref="C7" authorId="0">
       <text>
         <r>
           <rPr>
@@ -208,7 +172,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B32" authorId="0">
+    <comment ref="B29" authorId="0">
       <text>
         <r>
           <rPr>
@@ -219,7 +183,7 @@
           </rPr>
           <t xml:space="preserve">M32: Het project onderzoekt de kwaliteit van over te nemen software
 Als tijdens een project bestaande software dient te worden afgebouwd, onderhouden en/of herbouwd, vindt een onderzoek plaats naar de kwaliteit van deze software.
-Als tijdens een project bestaande software dient te worden afgebouwd, onderhouden en/of herbouwd, vindt een onderzoek plaats naar de compleetheid en consistentie van de bestaande softwareproducten (zie de tabel in M01: Het project levert in elke fase vastgestelde producten en informatie op, inclusief de deliverables in de kolom 'Realisatiefase') en wordt de kwaliteit van de bestaande softwareproducten getoetst. Dit onderzoek, dat bij ICTU een "due diligence" heet, is onderdeel van de voorfase en wordt uitgevoerd door vertegenwoordigers van ICTU en medewerkers van het desbetreffende project, samen met vertegenwoordigers van de opdrachtgevende organisatie.
+Als tijdens een project bestaande software dient te worden afgebouwd, onderhouden en/of herbouwd, vindt een onderzoek plaats naar de compleetheid en consistentie van de bestaande softwareproducten (zie de tabel in M01: Het project ontvangt en levert in elke fase vastgestelde producten en informatie, inclusief de deliverables in de kolom 'Realisatiefase') en wordt de kwaliteit van de bestaande softwareproducten getoetst. Dit onderzoek, dat bij ICTU een "due diligence" heet, is onderdeel van de voorfase en wordt uitgevoerd door vertegenwoordigers van ICTU en medewerkers van het desbetreffende project, samen met vertegenwoordigers van de opdrachtgevende organisatie.
 De uitkomsten van het onderzoek bestaan uit:
 1. Een rapportage met tenminste de bevindingen, risico's voor opdrachtgevende organisatie en ICTU, en mitigerende maatregelen,
 2. Een transitieplan dat de activiteiten beschrijft die nodig zijn om de software af te bouwen of te herbouwen en te onderhouden, en
@@ -231,7 +195,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C32" authorId="0">
+    <comment ref="C29" authorId="0">
       <text>
         <r>
           <rPr>
@@ -244,7 +208,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B36" authorId="0">
+    <comment ref="B33" authorId="0">
       <text>
         <r>
           <rPr>
@@ -255,7 +219,7 @@
           </rPr>
           <t xml:space="preserve">M02: Het project bewaakt continu dat het product aan de kwaliteitsnormen voldoet
 Projecten bewaken zo snel mogelijk vanaf de start de door het project en ICTU vastgestelde kwaliteitsnormen en voldoen daar zo snel en goed mogelijk aan. De kwaliteit van producten, die nog niet zijn afgerond of nog niet aan de normen voldoen, wordt door het project bewaakt. Het voldoen aan de kwaliteitsnormen is onderdeel van de Definition of Done en herstel van de kwaliteit wordt planmatig opgepakt.
-De kwaliteitsnormen voor het product zijn beschreven in de niet-functionele eisen, het informatiebeveiligingsplan, het kwaliteitsplan en deze Kwaliteitsaanpak, zie M01: Het project levert in elke fase vastgestelde producten en informatie op.
+De kwaliteitsnormen voor het product zijn beschreven in de niet-functionele eisen, het informatiebeveiligingsplan, het kwaliteitsplan en deze Kwaliteitsaanpak, zie M01: Het project ontvangt en levert in elke fase vastgestelde producten en informatie.
 Om continu te bewaken dat het product aan de kwaliteitsnormen voldoet, voert het project de volgende activiteiten uit:
 1. Tijdens de voorfase: het project reviewt de deliverables periodiek.
 2. Tijdens de realisatiefase: het project bewaakt op dagelijkse basis en geautomatiseerd de kwaliteit van de software.
@@ -286,7 +250,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C36" authorId="0">
+    <comment ref="C33" authorId="0">
       <text>
         <r>
           <rPr>
@@ -299,7 +263,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B43" authorId="0">
+    <comment ref="B40" authorId="0">
       <text>
         <r>
           <rPr>
@@ -318,7 +282,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B44" authorId="0">
+    <comment ref="B41" authorId="0">
       <text>
         <r>
           <rPr>
@@ -336,7 +300,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B45" authorId="0">
+    <comment ref="B42" authorId="0">
       <text>
         <r>
           <rPr>
@@ -354,7 +318,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B46" authorId="0">
+    <comment ref="B43" authorId="0">
       <text>
         <r>
           <rPr>
@@ -386,7 +350,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C46" authorId="0">
+    <comment ref="C43" authorId="0">
       <text>
         <r>
           <rPr>
@@ -399,7 +363,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B57" authorId="0">
+    <comment ref="B54" authorId="0">
       <text>
         <r>
           <rPr>
@@ -417,17 +381,16 @@
 5. release van software,
 6. maken van testrapportages,
 7. maken van kwaliteitsrapportages,
-8. controleren van de configuratie op aanwezigheid van bekende kwetsbaarheden,
-9. controleren van door de applicatie gebruikte versies van externe software op aanwezigheid van bekende kwetsbaarheden,
-10. statische controle van de software op aanwezigheid van kwetsbare constructies,
-11. dynamische controle van de software op aanwezigheid van kwetsbare constructies,
-12. controleren van container images op aanwezigheid van bekende kwetsbaarheden,
-13. testen van performance en schaalbaarheid,
-14. testen op toegankelijkheid van de applicatie,
-15. produceren van een "software bill of materials" (SBoM),
-16. opslaan van artifacten,
-17. registratie van incidenten bij gebruik en beheer, en
-18. bij het uitvoeren van operationeel beheer; uitrollen van de software in de productieomgeving.
+8. controleren van door de applicatie gebruikte versies van externe software op aanwezigheid van bekende kwetsbaarheden,
+9. statische controle van de software op aanwezigheid van kwetsbare constructies,
+10. dynamische controle van de software op aanwezigheid van kwetsbare constructies,
+11. controleren van container images op aanwezigheid van bekende kwetsbaarheden,
+12. testen van performance en schaalbaarheid,
+13. testen op toegankelijkheid van de applicatie,
+14. produceren van een "software bill of materials" (SBoM),
+15. opslaan van artifacten,
+16. registratie van incidenten bij gebruik en beheer, en
+17. bij het uitvoeren van operationeel beheer; uitrollen van de software in de productieomgeving.
 Onder het ondersteunen van "agile werken" vallen het opvoeren van eisen, het opvoeren van logische testgevallen, het koppelen van logische testgevallen aan eisen, het bijhouden van een werkvoorraad, het plannen van iteraties en het toewijzen van eisen aan iteraties. De 'eisen' worden, conform Scrumterminologie, geregistreerd als epics en/of user stories, de werkvoorraad als product backlog en de iteraties als sprints. Het toewijzen van eisen aan iteraties gebeurt via de sprint backlog.
 ICTU adviseert en ondersteunt voor de genoemde taken onderstaande tools. Projecten gebruiken deze tools, of gelijkwaardige alternatieven:
 1. product en sprint backlog management en agile werken: Azure DevOps of Jira,
@@ -437,24 +400,23 @@
 5. release van software: Releaseserver in het ontwikkelplatform,
 6. maken van testrapportages: JUnit, Robot Framework, TestNG, of hiermee compatible tools,
 7. maken van kwaliteitsrapportages: Quality-time,
-8. controleren van de configuratie op aanwezigheid van bekende kwetsbaarheden in configuratie: OpenVAS (Vulnerability Assessment System),
-9. controleren op aanwezigheid van bekende kwetsbaarheden in externe software: OWASP (Open Web Application Security Project) Dependency-Check en/of Dependency-Track,
-10. statische controle van de software op aanwezigheid van kwetsbare constructies: SonarQube,
-11. dynamische controle van de software op aanwezigheid van kwetsbare constructies: ZAP (Zed Attack Proxy) by Checkmarx,
-12. controleren van container images op aanwezigheid van bekende kwetsbaarheden: Trivy,
-13. testen van performance en schaalbaarheid: JMeter en Performancetestrunner,
-14. testen op toegankelijkheid van de applicatie: Axe,
-15. produceren van een "software bill of materials" (SBoM): tools die een SBoM in CycloneDX-formaat (zie https://cyclonedx.org) genereren,
-16. opslaan van artifacten: Nexus of Harbor,
-17. registratie van incidenten bij gebruik en beheer: Jira, en
-18. bij het uitvoeren van operationeel beheer; uitrollen van de software in de productieomgeving: Ansible.
+8. controleren op aanwezigheid van bekende kwetsbaarheden in externe software: OWASP (Open Web Application Security Project) Dependency-Check en/of Dependency-Track,
+9. statische controle van de software op aanwezigheid van kwetsbare constructies: SonarQube,
+10. dynamische controle van de software op aanwezigheid van kwetsbare constructies: ZAP (Zed Attack Proxy) by Checkmarx,
+11. controleren van container images op aanwezigheid van bekende kwetsbaarheden: Trivy,
+12. testen van performance en schaalbaarheid: JMeter en Performancetestrunner,
+13. testen op toegankelijkheid van de applicatie: Axe,
+14. produceren van een "software bill of materials" (SBoM): tools die een SBoM in CycloneDX-formaat (zie https://cyclonedx.org) genereren,
+15. opslaan van artifacten: Nexus of Harbor,
+16. registratie van incidenten bij gebruik en beheer: Jira, en
+17. bij het uitvoeren van operationeel beheer; uitrollen van de software in de productieomgeving: Ansible.
 Rationale
 Projecten hebben een redelijke vrijheid bij het kiezen en gebruiken van tools, maar voor een aantal taken is het gebruik verplicht gesteld. Deze tools zijn nodig voor een efficiënte uitvoering van de Kwaliteitsaanpak. Uniform gebruik van deze tools maakt het mogelijk koppeling tussen die tools voor alle projecten te standaardiseren; daarnaast bevordert het de uitwisselbaarheid van medewerkers en neemt het risico op het gebruik van onvolwassen tools af. Tot slot is het gebruik in een aantal gevallen, ten behoeve van informatiebeveiliging bij de overheid, verplicht.
 </t>
         </r>
       </text>
     </comment>
-    <comment ref="C57" authorId="0">
+    <comment ref="C54" authorId="0">
       <text>
         <r>
           <rPr>
@@ -467,7 +429,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B76" authorId="0">
+    <comment ref="B72" authorId="0">
       <text>
         <r>
           <rPr>
@@ -487,7 +449,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B77" authorId="0">
+    <comment ref="B73" authorId="0">
       <text>
         <r>
           <rPr>
@@ -509,7 +471,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B79" authorId="0">
+    <comment ref="B75" authorId="0">
       <text>
         <r>
           <rPr>
@@ -525,12 +487,12 @@
 Als tijdens de realisatiefase blijkt dat de kaders van het project significant wijzigen, dan stemmen opdrachtgevende organisatie, ICTU en andere betrokken partijen af welke onderdelen van de voorfase opnieuw moeten worden uitgevoerd. Denk bij significante wijzigingen aan grote aanpassingen aan de scope, het budget, de belanghebbenden en/of de planning van het project.
 Rationale
 Het doel van de voorfase is ten eerste om uitgangspunten, risico's en randvoorwaarden voor verdere projectuitvoering te bepalen en ten tweede om te zorgen dat aan de randvoorwaarden wordt voldaan en voor zoveel mogelijk projectspecifieke risico's maatregelen genomen zijn. Het doel van de realisatiefase is het daadwerkelijk bouwen en onderhouden van de software. Een expliciete splitsing zorgt ervoor dat projecten doordacht van start gaan.
-Al tijdens de voorfase moeten keuzes gemaakt worden die invloed hebben op de beveiligingsmaatregelen. Aanwezigheid van een voldoende gemandateerde vertegenwoordiger van de opdrachtgevende organisatie zorgt dat deze keuzes gemaakt en bekrachtigd kunnen worden. De keuzes komen onder meer tot uitdrukking in de ontwerp- en architectuurdocumentatie, zie M01: Het project levert in elke fase vastgestelde producten en informatie op. De infrastructuur gerelateerde documentatie wordt opgesteld door de beoogd beheerder en dekt een deel van de totale beveiligingsmaatregelen af. Aanwezigheid van de beoogd beheerder in de voorfase zorgt dat dekking van dit deel van de beveiligingsmaatregelen geborgd blijft gedurende de realisatie en exploitatie.
+Al tijdens de voorfase moeten keuzes gemaakt worden die invloed hebben op de beveiligingsmaatregelen. Aanwezigheid van een voldoende gemandateerde vertegenwoordiger van de opdrachtgevende organisatie zorgt dat deze keuzes gemaakt en bekrachtigd kunnen worden. De keuzes komen onder meer tot uitdrukking in de ontwerp- en architectuurdocumentatie, zie M01: Het project ontvangt en levert in elke fase vastgestelde producten en informatie. De infrastructuur gerelateerde documentatie wordt opgesteld door de beoogd beheerder en dekt een deel van de totale beveiligingsmaatregelen af. Aanwezigheid van de beoogd beheerder in de voorfase zorgt dat dekking van dit deel van de beveiligingsmaatregelen geborgd blijft gedurende de realisatie en exploitatie.
 </t>
         </r>
       </text>
     </comment>
-    <comment ref="B80" authorId="0">
+    <comment ref="B76" authorId="0">
       <text>
         <r>
           <rPr>
@@ -547,7 +509,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B81" authorId="0">
+    <comment ref="B77" authorId="0">
       <text>
         <r>
           <rPr>
@@ -564,7 +526,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B82" authorId="0">
+    <comment ref="B78" authorId="0">
       <text>
         <r>
           <rPr>
@@ -587,7 +549,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C82" authorId="0">
+    <comment ref="C78" authorId="0">
       <text>
         <r>
           <rPr>
@@ -600,7 +562,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B87" authorId="0">
+    <comment ref="B83" authorId="0">
       <text>
         <r>
           <rPr>
@@ -621,7 +583,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B88" authorId="0">
+    <comment ref="B84" authorId="0">
       <text>
         <r>
           <rPr>
@@ -646,7 +608,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B89" authorId="0">
+    <comment ref="B85" authorId="0">
       <text>
         <r>
           <rPr>
@@ -673,7 +635,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B90" authorId="0">
+    <comment ref="B86" authorId="0">
       <text>
         <r>
           <rPr>
@@ -691,7 +653,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B91" authorId="0">
+    <comment ref="B87" authorId="0">
       <text>
         <r>
           <rPr>
@@ -723,7 +685,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C91" authorId="0">
+    <comment ref="C87" authorId="0">
       <text>
         <r>
           <rPr>
@@ -736,7 +698,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B106" authorId="0">
+    <comment ref="B102" authorId="0">
       <text>
         <r>
           <rPr>
@@ -756,7 +718,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B108" authorId="0">
+    <comment ref="B104" authorId="0">
       <text>
         <r>
           <rPr>
@@ -776,7 +738,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B109" authorId="0">
+    <comment ref="B105" authorId="0">
       <text>
         <r>
           <rPr>
@@ -795,7 +757,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B110" authorId="0">
+    <comment ref="B106" authorId="0">
       <text>
         <r>
           <rPr>
@@ -816,7 +778,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B111" authorId="0">
+    <comment ref="B107" authorId="0">
       <text>
         <r>
           <rPr>
@@ -835,7 +797,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B112" authorId="0">
+    <comment ref="B108" authorId="0">
       <text>
         <r>
           <rPr>
@@ -853,7 +815,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B113" authorId="0">
+    <comment ref="B109" authorId="0">
       <text>
         <r>
           <rPr>
@@ -884,9 +846,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="146">
-  <si>
-    <t>Onderstaande checklist kan gebruikt worden voor het uitvoeren van een assessment tegen de ICTU Kwaliteitsaanpak Softwareontwikkeling versie wip, 04-03-2025.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="141">
+  <si>
+    <t>Onderstaande checklist kan gebruikt worden voor het uitvoeren van een assessment tegen de ICTU Kwaliteitsaanpak Softwareontwikkeling versie wip, 21-03-2025.</t>
   </si>
   <si>
     <t>Gebruik de 'Status' kolom om aan te geven in hoeverre een maatregel uit de Kwaliteitsaanpak is toegepast. Bij maatregelen met submaatregelen hoeft alleen de status van de submaatregelen te worden ingevuld.</t>
@@ -913,28 +875,10 @@
     <t>Producten</t>
   </si>
   <si>
-    <t>M31</t>
-  </si>
-  <si>
-    <t>Het project beschikt over actuele vastgestelde informatie</t>
-  </si>
-  <si>
-    <t>1. Projectstartarchitectuur,</t>
-  </si>
-  <si>
-    <t>2. Business impact analyse,</t>
-  </si>
-  <si>
-    <t>3. Privacy impact assessment,</t>
-  </si>
-  <si>
-    <t>4. Afspraken tussen opdrachtgevende organisatie en beheerorganisatie.</t>
-  </si>
-  <si>
     <t>M01</t>
   </si>
   <si>
-    <t>Het project levert in elke fase vastgestelde producten en informatie op</t>
+    <t>Het project ontvangt en levert in elke fase vastgestelde producten en informatie</t>
   </si>
   <si>
     <t>1. Projectstartarchitectuur</t>
@@ -946,52 +890,58 @@
     <t>3. Privacy impact assessment</t>
   </si>
   <si>
-    <t>4. Plan van aanpak: voorfase</t>
-  </si>
-  <si>
-    <t>5. Beschrijving van functionele eisen</t>
-  </si>
-  <si>
-    <t>6. Beschrijving van niet-functionele eisen</t>
-  </si>
-  <si>
-    <t>7. Product backlog</t>
-  </si>
-  <si>
-    <t>8. Ontwerp- en architectuurdocumentatie</t>
-  </si>
-  <si>
-    <t>9. Mastertestplan</t>
-  </si>
-  <si>
-    <t>10. Detailtestplannen</t>
-  </si>
-  <si>
-    <t>11. Informatiebeveiligingsplan</t>
-  </si>
-  <si>
-    <t>12. Kwaliteitsplan</t>
-  </si>
-  <si>
-    <t>13. Plan van aanpak: realisatiefase</t>
-  </si>
-  <si>
-    <t>14. Deploybare versie van de software</t>
-  </si>
-  <si>
-    <t>15. Testrapportages</t>
-  </si>
-  <si>
-    <t>16. Documentatie voor deployment en operationeel beheer</t>
-  </si>
-  <si>
-    <t>17. Software bill of materials</t>
-  </si>
-  <si>
-    <t>18. Release notes</t>
-  </si>
-  <si>
-    <t>19. Vrijgaveadvies</t>
+    <t>4. Beheerafspraken</t>
+  </si>
+  <si>
+    <t>5. Aanvullende informatie</t>
+  </si>
+  <si>
+    <t>6. Plan van aanpak: voorfase</t>
+  </si>
+  <si>
+    <t>7. Beschrijving van functionele eisen</t>
+  </si>
+  <si>
+    <t>8. Beschrijving van niet-functionele eisen</t>
+  </si>
+  <si>
+    <t>9. Product backlog</t>
+  </si>
+  <si>
+    <t>10. Ontwerp- en architectuurdocumentatie</t>
+  </si>
+  <si>
+    <t>11. Mastertestplan</t>
+  </si>
+  <si>
+    <t>12. Detailtestplannen</t>
+  </si>
+  <si>
+    <t>13. Informatiebeveiligingsplan</t>
+  </si>
+  <si>
+    <t>14. Kwaliteitsplan</t>
+  </si>
+  <si>
+    <t>15. Plan van aanpak: realisatiefase</t>
+  </si>
+  <si>
+    <t>16. Deploybare versie van de software</t>
+  </si>
+  <si>
+    <t>17. Testrapportages</t>
+  </si>
+  <si>
+    <t>18. Documentatie voor deployment en operationeel beheer</t>
+  </si>
+  <si>
+    <t>19. Software bill of materials</t>
+  </si>
+  <si>
+    <t>20. Release notes</t>
+  </si>
+  <si>
+    <t>21. Vrijgaveadvies</t>
   </si>
   <si>
     <t>M32</t>
@@ -1114,37 +1064,34 @@
     <t>7. maken van kwaliteitsrapportages: Quality-time,</t>
   </si>
   <si>
-    <t>8. controleren van de configuratie op aanwezigheid van bekende kwetsbaarheden in configuratie: OpenVAS (Vulnerability Assessment System),</t>
-  </si>
-  <si>
-    <t>9. controleren op aanwezigheid van bekende kwetsbaarheden in externe software: OWASP (Open Web Application Security Project) Dependency-Check en/of Dependency-Track,</t>
-  </si>
-  <si>
-    <t>10. statische controle van de software op aanwezigheid van kwetsbare constructies: SonarQube,</t>
-  </si>
-  <si>
-    <t>11. dynamische controle van de software op aanwezigheid van kwetsbare constructies: ZAP (Zed Attack Proxy) by Checkmarx,</t>
-  </si>
-  <si>
-    <t>12. controleren van container images op aanwezigheid van bekende kwetsbaarheden: Trivy,</t>
-  </si>
-  <si>
-    <t>13. testen van performance en schaalbaarheid: JMeter en Performancetestrunner,</t>
-  </si>
-  <si>
-    <t>14. testen op toegankelijkheid van de applicatie: Axe,</t>
-  </si>
-  <si>
-    <t>15. produceren van een "software bill of materials" (SBoM): tools die een SBoM in CycloneDX-formaat (zie https://cyclonedx.org) genereren,</t>
-  </si>
-  <si>
-    <t>16. opslaan van artifacten: Nexus of Harbor,</t>
-  </si>
-  <si>
-    <t>17. registratie van incidenten bij gebruik en beheer: Jira, en</t>
-  </si>
-  <si>
-    <t>18. bij het uitvoeren van operationeel beheer; uitrollen van de software in de productieomgeving: Ansible.</t>
+    <t>8. controleren op aanwezigheid van bekende kwetsbaarheden in externe software: OWASP (Open Web Application Security Project) Dependency-Check en/of Dependency-Track,</t>
+  </si>
+  <si>
+    <t>9. statische controle van de software op aanwezigheid van kwetsbare constructies: SonarQube,</t>
+  </si>
+  <si>
+    <t>10. dynamische controle van de software op aanwezigheid van kwetsbare constructies: ZAP (Zed Attack Proxy) by Checkmarx,</t>
+  </si>
+  <si>
+    <t>11. controleren van container images op aanwezigheid van bekende kwetsbaarheden: Trivy,</t>
+  </si>
+  <si>
+    <t>12. testen van performance en schaalbaarheid: JMeter en Performancetestrunner,</t>
+  </si>
+  <si>
+    <t>13. testen op toegankelijkheid van de applicatie: Axe,</t>
+  </si>
+  <si>
+    <t>14. produceren van een "software bill of materials" (SBoM): tools die een SBoM in CycloneDX-formaat (zie https://cyclonedx.org) genereren,</t>
+  </si>
+  <si>
+    <t>15. opslaan van artifacten: Nexus of Harbor,</t>
+  </si>
+  <si>
+    <t>16. registratie van incidenten bij gebruik en beheer: Jira, en</t>
+  </si>
+  <si>
+    <t>17. bij het uitvoeren van operationeel beheer; uitrollen van de software in de productieomgeving: Ansible.</t>
   </si>
   <si>
     <t>M08</t>
@@ -1752,7 +1699,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D113"/>
+  <dimension ref="A1:D109"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -1858,19 +1805,17 @@
       <c r="D11" s="5"/>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="6"/>
+      <c r="B12" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" s="4"/>
+      <c r="C12" s="7"/>
       <c r="D12" s="5"/>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="6"/>
       <c r="B13" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="5"/>
@@ -1878,7 +1823,7 @@
     <row r="14" spans="1:4">
       <c r="A14" s="6"/>
       <c r="B14" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="5"/>
@@ -1886,7 +1831,7 @@
     <row r="15" spans="1:4">
       <c r="A15" s="6"/>
       <c r="B15" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C15" s="7"/>
       <c r="D15" s="5"/>
@@ -1894,7 +1839,7 @@
     <row r="16" spans="1:4">
       <c r="A16" s="6"/>
       <c r="B16" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C16" s="7"/>
       <c r="D16" s="5"/>
@@ -1902,7 +1847,7 @@
     <row r="17" spans="1:4">
       <c r="A17" s="6"/>
       <c r="B17" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C17" s="7"/>
       <c r="D17" s="5"/>
@@ -1910,7 +1855,7 @@
     <row r="18" spans="1:4">
       <c r="A18" s="6"/>
       <c r="B18" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C18" s="7"/>
       <c r="D18" s="5"/>
@@ -1918,7 +1863,7 @@
     <row r="19" spans="1:4">
       <c r="A19" s="6"/>
       <c r="B19" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C19" s="7"/>
       <c r="D19" s="5"/>
@@ -1926,7 +1871,7 @@
     <row r="20" spans="1:4">
       <c r="A20" s="6"/>
       <c r="B20" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C20" s="7"/>
       <c r="D20" s="5"/>
@@ -1934,7 +1879,7 @@
     <row r="21" spans="1:4">
       <c r="A21" s="6"/>
       <c r="B21" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C21" s="7"/>
       <c r="D21" s="5"/>
@@ -1942,7 +1887,7 @@
     <row r="22" spans="1:4">
       <c r="A22" s="6"/>
       <c r="B22" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C22" s="7"/>
       <c r="D22" s="5"/>
@@ -1950,7 +1895,7 @@
     <row r="23" spans="1:4">
       <c r="A23" s="6"/>
       <c r="B23" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C23" s="7"/>
       <c r="D23" s="5"/>
@@ -1958,7 +1903,7 @@
     <row r="24" spans="1:4">
       <c r="A24" s="6"/>
       <c r="B24" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C24" s="7"/>
       <c r="D24" s="5"/>
@@ -1966,7 +1911,7 @@
     <row r="25" spans="1:4">
       <c r="A25" s="6"/>
       <c r="B25" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C25" s="7"/>
       <c r="D25" s="5"/>
@@ -1974,7 +1919,7 @@
     <row r="26" spans="1:4">
       <c r="A26" s="6"/>
       <c r="B26" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C26" s="7"/>
       <c r="D26" s="5"/>
@@ -1982,7 +1927,7 @@
     <row r="27" spans="1:4">
       <c r="A27" s="6"/>
       <c r="B27" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C27" s="7"/>
       <c r="D27" s="5"/>
@@ -1990,17 +1935,19 @@
     <row r="28" spans="1:4">
       <c r="A28" s="6"/>
       <c r="B28" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C28" s="7"/>
       <c r="D28" s="5"/>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="6"/>
-      <c r="B29" s="6" t="s">
+      <c r="A29" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B29" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C29" s="7"/>
+      <c r="C29" s="4"/>
       <c r="D29" s="5"/>
     </row>
     <row r="30" spans="1:4">
@@ -2020,21 +1967,21 @@
       <c r="D31" s="5"/>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="3" t="s">
+      <c r="A32" s="6"/>
+      <c r="B32" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="C32" s="7"/>
+      <c r="D32" s="5"/>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C32" s="4"/>
-      <c r="D32" s="5"/>
-    </row>
-    <row r="33" spans="1:4">
-      <c r="A33" s="6"/>
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C33" s="7"/>
+      <c r="C33" s="4"/>
       <c r="D33" s="5"/>
     </row>
     <row r="34" spans="1:4">
@@ -2054,19 +2001,17 @@
       <c r="D35" s="5"/>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="3" t="s">
+      <c r="A36" s="6"/>
+      <c r="B36" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C36" s="4"/>
+      <c r="C36" s="7"/>
       <c r="D36" s="5"/>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="6"/>
       <c r="B37" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C37" s="7"/>
       <c r="D37" s="5"/>
@@ -2074,7 +2019,7 @@
     <row r="38" spans="1:4">
       <c r="A38" s="6"/>
       <c r="B38" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C38" s="7"/>
       <c r="D38" s="5"/>
@@ -2082,79 +2027,79 @@
     <row r="39" spans="1:4">
       <c r="A39" s="6"/>
       <c r="B39" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C39" s="7"/>
       <c r="D39" s="5"/>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40" s="6"/>
-      <c r="B40" s="6" t="s">
+      <c r="A40" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B40" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C40" s="7"/>
+      <c r="C40" s="4"/>
       <c r="D40" s="5"/>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" s="6"/>
-      <c r="B41" s="6" t="s">
+      <c r="A41" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C41" s="7"/>
+      <c r="B41" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C41" s="4"/>
       <c r="D41" s="5"/>
     </row>
     <row r="42" spans="1:4">
-      <c r="A42" s="6"/>
-      <c r="B42" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C42" s="7"/>
+      <c r="A42" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C42" s="4"/>
       <c r="D42" s="5"/>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C43" s="4"/>
       <c r="D43" s="5"/>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C44" s="4"/>
+      <c r="A44" s="6"/>
+      <c r="B44" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C44" s="7"/>
       <c r="D44" s="5"/>
     </row>
     <row r="45" spans="1:4">
-      <c r="A45" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B45" s="3" t="s">
+      <c r="A45" s="6"/>
+      <c r="B45" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="C45" s="4"/>
+      <c r="C45" s="7"/>
       <c r="D45" s="5"/>
     </row>
     <row r="46" spans="1:4">
-      <c r="A46" s="3" t="s">
+      <c r="A46" s="6"/>
+      <c r="B46" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="B46" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C46" s="4"/>
+      <c r="C46" s="7"/>
       <c r="D46" s="5"/>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="6"/>
       <c r="B47" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C47" s="7"/>
       <c r="D47" s="5"/>
@@ -2162,7 +2107,7 @@
     <row r="48" spans="1:4">
       <c r="A48" s="6"/>
       <c r="B48" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C48" s="7"/>
       <c r="D48" s="5"/>
@@ -2170,7 +2115,7 @@
     <row r="49" spans="1:4">
       <c r="A49" s="6"/>
       <c r="B49" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C49" s="7"/>
       <c r="D49" s="5"/>
@@ -2178,7 +2123,7 @@
     <row r="50" spans="1:4">
       <c r="A50" s="6"/>
       <c r="B50" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C50" s="7"/>
       <c r="D50" s="5"/>
@@ -2186,7 +2131,7 @@
     <row r="51" spans="1:4">
       <c r="A51" s="6"/>
       <c r="B51" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C51" s="7"/>
       <c r="D51" s="5"/>
@@ -2194,7 +2139,7 @@
     <row r="52" spans="1:4">
       <c r="A52" s="6"/>
       <c r="B52" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C52" s="7"/>
       <c r="D52" s="5"/>
@@ -2202,17 +2147,19 @@
     <row r="53" spans="1:4">
       <c r="A53" s="6"/>
       <c r="B53" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C53" s="7"/>
       <c r="D53" s="5"/>
     </row>
     <row r="54" spans="1:4">
-      <c r="A54" s="6"/>
-      <c r="B54" s="6" t="s">
+      <c r="A54" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B54" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C54" s="7"/>
+      <c r="C54" s="4"/>
       <c r="D54" s="5"/>
     </row>
     <row r="55" spans="1:4">
@@ -2232,19 +2179,17 @@
       <c r="D56" s="5"/>
     </row>
     <row r="57" spans="1:4">
-      <c r="A57" s="3" t="s">
+      <c r="A57" s="6"/>
+      <c r="B57" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B57" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C57" s="4"/>
+      <c r="C57" s="7"/>
       <c r="D57" s="5"/>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="6"/>
       <c r="B58" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C58" s="7"/>
       <c r="D58" s="5"/>
@@ -2252,7 +2197,7 @@
     <row r="59" spans="1:4">
       <c r="A59" s="6"/>
       <c r="B59" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C59" s="7"/>
       <c r="D59" s="5"/>
@@ -2260,7 +2205,7 @@
     <row r="60" spans="1:4">
       <c r="A60" s="6"/>
       <c r="B60" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C60" s="7"/>
       <c r="D60" s="5"/>
@@ -2268,7 +2213,7 @@
     <row r="61" spans="1:4">
       <c r="A61" s="6"/>
       <c r="B61" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C61" s="7"/>
       <c r="D61" s="5"/>
@@ -2276,7 +2221,7 @@
     <row r="62" spans="1:4">
       <c r="A62" s="6"/>
       <c r="B62" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C62" s="7"/>
       <c r="D62" s="5"/>
@@ -2284,7 +2229,7 @@
     <row r="63" spans="1:4">
       <c r="A63" s="6"/>
       <c r="B63" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C63" s="7"/>
       <c r="D63" s="5"/>
@@ -2292,7 +2237,7 @@
     <row r="64" spans="1:4">
       <c r="A64" s="6"/>
       <c r="B64" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C64" s="7"/>
       <c r="D64" s="5"/>
@@ -2300,7 +2245,7 @@
     <row r="65" spans="1:4">
       <c r="A65" s="6"/>
       <c r="B65" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C65" s="7"/>
       <c r="D65" s="5"/>
@@ -2308,7 +2253,7 @@
     <row r="66" spans="1:4">
       <c r="A66" s="6"/>
       <c r="B66" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C66" s="7"/>
       <c r="D66" s="5"/>
@@ -2316,7 +2261,7 @@
     <row r="67" spans="1:4">
       <c r="A67" s="6"/>
       <c r="B67" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C67" s="7"/>
       <c r="D67" s="5"/>
@@ -2324,7 +2269,7 @@
     <row r="68" spans="1:4">
       <c r="A68" s="6"/>
       <c r="B68" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C68" s="7"/>
       <c r="D68" s="5"/>
@@ -2332,7 +2277,7 @@
     <row r="69" spans="1:4">
       <c r="A69" s="6"/>
       <c r="B69" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C69" s="7"/>
       <c r="D69" s="5"/>
@@ -2340,7 +2285,7 @@
     <row r="70" spans="1:4">
       <c r="A70" s="6"/>
       <c r="B70" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C70" s="7"/>
       <c r="D70" s="5"/>
@@ -2348,197 +2293,197 @@
     <row r="71" spans="1:4">
       <c r="A71" s="6"/>
       <c r="B71" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C71" s="7"/>
       <c r="D71" s="5"/>
     </row>
     <row r="72" spans="1:4">
-      <c r="A72" s="6"/>
-      <c r="B72" s="6" t="s">
+      <c r="A72" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B72" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C72" s="7"/>
+      <c r="C72" s="4"/>
       <c r="D72" s="5"/>
     </row>
     <row r="73" spans="1:4">
-      <c r="A73" s="6"/>
-      <c r="B73" s="6" t="s">
+      <c r="A73" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C73" s="7"/>
+      <c r="B73" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C73" s="4"/>
       <c r="D73" s="5"/>
     </row>
     <row r="74" spans="1:4">
-      <c r="A74" s="6"/>
-      <c r="B74" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="C74" s="7"/>
-      <c r="D74" s="5"/>
+      <c r="A74" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B74" s="1"/>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
     </row>
     <row r="75" spans="1:4">
-      <c r="A75" s="6"/>
-      <c r="B75" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="C75" s="7"/>
+      <c r="A75" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C75" s="4"/>
       <c r="D75" s="5"/>
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C76" s="4"/>
       <c r="D76" s="5"/>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C77" s="4"/>
       <c r="D77" s="5"/>
     </row>
     <row r="78" spans="1:4">
-      <c r="A78" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B78" s="1"/>
-      <c r="C78" s="1"/>
-      <c r="D78" s="1"/>
+      <c r="A78" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C78" s="4"/>
+      <c r="D78" s="5"/>
     </row>
     <row r="79" spans="1:4">
-      <c r="A79" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C79" s="4"/>
+      <c r="A79" s="6"/>
+      <c r="B79" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C79" s="7"/>
       <c r="D79" s="5"/>
     </row>
     <row r="80" spans="1:4">
-      <c r="A80" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="C80" s="4"/>
+      <c r="A80" s="6"/>
+      <c r="B80" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C80" s="7"/>
       <c r="D80" s="5"/>
     </row>
     <row r="81" spans="1:4">
-      <c r="A81" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="B81" s="3" t="s">
+      <c r="A81" s="6"/>
+      <c r="B81" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="C81" s="4"/>
+      <c r="C81" s="7"/>
       <c r="D81" s="5"/>
     </row>
     <row r="82" spans="1:4">
-      <c r="A82" s="3" t="s">
+      <c r="A82" s="6"/>
+      <c r="B82" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="B82" s="3" t="s">
+      <c r="C82" s="7"/>
+      <c r="D82" s="5"/>
+    </row>
+    <row r="83" spans="1:4">
+      <c r="A83" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="C82" s="4"/>
-      <c r="D82" s="5"/>
-    </row>
-    <row r="83" spans="1:4">
-      <c r="A83" s="6"/>
-      <c r="B83" s="6" t="s">
+      <c r="B83" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C83" s="7"/>
+      <c r="C83" s="4"/>
       <c r="D83" s="5"/>
     </row>
     <row r="84" spans="1:4">
-      <c r="A84" s="6"/>
-      <c r="B84" s="6" t="s">
+      <c r="A84" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="C84" s="7"/>
+      <c r="B84" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C84" s="4"/>
       <c r="D84" s="5"/>
     </row>
     <row r="85" spans="1:4">
-      <c r="A85" s="6"/>
-      <c r="B85" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="C85" s="7"/>
+      <c r="A85" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C85" s="4"/>
       <c r="D85" s="5"/>
     </row>
     <row r="86" spans="1:4">
-      <c r="A86" s="6"/>
-      <c r="B86" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="C86" s="7"/>
+      <c r="A86" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C86" s="4"/>
       <c r="D86" s="5"/>
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C87" s="4"/>
       <c r="D87" s="5"/>
     </row>
     <row r="88" spans="1:4">
-      <c r="A88" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="B88" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="C88" s="4"/>
+      <c r="A88" s="6"/>
+      <c r="B88" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="C88" s="7"/>
       <c r="D88" s="5"/>
     </row>
     <row r="89" spans="1:4">
-      <c r="A89" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="B89" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="C89" s="4"/>
+      <c r="A89" s="6"/>
+      <c r="B89" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="C89" s="7"/>
       <c r="D89" s="5"/>
     </row>
     <row r="90" spans="1:4">
-      <c r="A90" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="B90" s="3" t="s">
+      <c r="A90" s="6"/>
+      <c r="B90" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="C90" s="4"/>
+      <c r="C90" s="7"/>
       <c r="D90" s="5"/>
     </row>
     <row r="91" spans="1:4">
-      <c r="A91" s="3" t="s">
+      <c r="A91" s="6"/>
+      <c r="B91" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="B91" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="C91" s="4"/>
+      <c r="C91" s="7"/>
       <c r="D91" s="5"/>
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="6"/>
       <c r="B92" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C92" s="7"/>
       <c r="D92" s="5"/>
@@ -2546,7 +2491,7 @@
     <row r="93" spans="1:4">
       <c r="A93" s="6"/>
       <c r="B93" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C93" s="7"/>
       <c r="D93" s="5"/>
@@ -2554,7 +2499,7 @@
     <row r="94" spans="1:4">
       <c r="A94" s="6"/>
       <c r="B94" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C94" s="7"/>
       <c r="D94" s="5"/>
@@ -2562,7 +2507,7 @@
     <row r="95" spans="1:4">
       <c r="A95" s="6"/>
       <c r="B95" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C95" s="7"/>
       <c r="D95" s="5"/>
@@ -2570,7 +2515,7 @@
     <row r="96" spans="1:4">
       <c r="A96" s="6"/>
       <c r="B96" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C96" s="7"/>
       <c r="D96" s="5"/>
@@ -2578,7 +2523,7 @@
     <row r="97" spans="1:4">
       <c r="A97" s="6"/>
       <c r="B97" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C97" s="7"/>
       <c r="D97" s="5"/>
@@ -2586,7 +2531,7 @@
     <row r="98" spans="1:4">
       <c r="A98" s="6"/>
       <c r="B98" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C98" s="7"/>
       <c r="D98" s="5"/>
@@ -2594,7 +2539,7 @@
     <row r="99" spans="1:4">
       <c r="A99" s="6"/>
       <c r="B99" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C99" s="7"/>
       <c r="D99" s="5"/>
@@ -2602,7 +2547,7 @@
     <row r="100" spans="1:4">
       <c r="A100" s="6"/>
       <c r="B100" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C100" s="7"/>
       <c r="D100" s="5"/>
@@ -2610,120 +2555,88 @@
     <row r="101" spans="1:4">
       <c r="A101" s="6"/>
       <c r="B101" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C101" s="7"/>
       <c r="D101" s="5"/>
     </row>
     <row r="102" spans="1:4">
-      <c r="A102" s="6"/>
-      <c r="B102" s="6" t="s">
+      <c r="A102" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B102" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="C102" s="7"/>
+      <c r="C102" s="4"/>
       <c r="D102" s="5"/>
     </row>
     <row r="103" spans="1:4">
-      <c r="A103" s="6"/>
-      <c r="B103" s="6" t="s">
+      <c r="A103" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C103" s="7"/>
-      <c r="D103" s="5"/>
+      <c r="B103" s="1"/>
+      <c r="C103" s="1"/>
+      <c r="D103" s="1"/>
     </row>
     <row r="104" spans="1:4">
-      <c r="A104" s="6"/>
-      <c r="B104" s="6" t="s">
+      <c r="A104" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="C104" s="7"/>
+      <c r="B104" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C104" s="4"/>
       <c r="D104" s="5"/>
     </row>
     <row r="105" spans="1:4">
-      <c r="A105" s="6"/>
-      <c r="B105" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="C105" s="7"/>
+      <c r="A105" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C105" s="4"/>
       <c r="D105" s="5"/>
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C106" s="4"/>
       <c r="D106" s="5"/>
     </row>
     <row r="107" spans="1:4">
-      <c r="A107" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="B107" s="1"/>
-      <c r="C107" s="1"/>
-      <c r="D107" s="1"/>
+      <c r="A107" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C107" s="4"/>
+      <c r="D107" s="5"/>
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C108" s="4"/>
       <c r="D108" s="5"/>
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="3" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C109" s="4"/>
       <c r="D109" s="5"/>
-    </row>
-    <row r="110" spans="1:4">
-      <c r="A110" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="B110" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="C110" s="4"/>
-      <c r="D110" s="5"/>
-    </row>
-    <row r="111" spans="1:4">
-      <c r="A111" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="B111" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="C111" s="4"/>
-      <c r="D111" s="5"/>
-    </row>
-    <row r="112" spans="1:4">
-      <c r="A112" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="B112" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="C112" s="4"/>
-      <c r="D112" s="5"/>
-    </row>
-    <row r="113" spans="1:4">
-      <c r="A113" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="B113" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="C113" s="4"/>
-      <c r="D113" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -2788,7 +2701,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C103">
+  <conditionalFormatting sqref="C104">
     <cfRule type="cellIs" dxfId="0" priority="381" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -2802,7 +2715,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C104">
+  <conditionalFormatting sqref="C105">
     <cfRule type="cellIs" dxfId="0" priority="385" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -2816,7 +2729,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C105">
+  <conditionalFormatting sqref="C106">
     <cfRule type="cellIs" dxfId="0" priority="389" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -2830,7 +2743,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C106">
+  <conditionalFormatting sqref="C107">
     <cfRule type="cellIs" dxfId="0" priority="393" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -2886,62 +2799,6 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C110">
-    <cfRule type="cellIs" dxfId="0" priority="405" operator="equal">
-      <formula>"voldoet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="406" operator="equal">
-      <formula>"voldoet deels"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="407" operator="equal">
-      <formula>"voldoet niet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="408" operator="equal">
-      <formula>"niet van toepassing"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C111">
-    <cfRule type="cellIs" dxfId="0" priority="409" operator="equal">
-      <formula>"voldoet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="410" operator="equal">
-      <formula>"voldoet deels"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="411" operator="equal">
-      <formula>"voldoet niet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="412" operator="equal">
-      <formula>"niet van toepassing"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C112">
-    <cfRule type="cellIs" dxfId="0" priority="413" operator="equal">
-      <formula>"voldoet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="414" operator="equal">
-      <formula>"voldoet deels"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="415" operator="equal">
-      <formula>"voldoet niet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="416" operator="equal">
-      <formula>"niet van toepassing"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C113">
-    <cfRule type="cellIs" dxfId="0" priority="417" operator="equal">
-      <formula>"voldoet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="418" operator="equal">
-      <formula>"voldoet deels"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="419" operator="equal">
-      <formula>"voldoet niet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="420" operator="equal">
-      <formula>"niet van toepassing"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="C12">
     <cfRule type="cellIs" dxfId="0" priority="21" operator="equal">
       <formula>"voldoet"</formula>
@@ -3824,7 +3681,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C74">
+  <conditionalFormatting sqref="C75">
     <cfRule type="cellIs" dxfId="0" priority="269" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3838,7 +3695,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C75">
+  <conditionalFormatting sqref="C76">
     <cfRule type="cellIs" dxfId="0" priority="273" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3852,7 +3709,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C76">
+  <conditionalFormatting sqref="C77">
     <cfRule type="cellIs" dxfId="0" priority="277" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3866,7 +3723,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C77">
+  <conditionalFormatting sqref="C78">
     <cfRule type="cellIs" dxfId="0" priority="281" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -4202,7 +4059,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="105">
+  <dataValidations count="101">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C7">
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
@@ -4404,9 +4261,6 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C73">
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C74">
-      <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C75">
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
@@ -4416,6 +4270,9 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C77">
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C78">
+      <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C79">
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
@@ -4488,9 +4345,6 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C102">
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C103">
-      <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C104">
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
@@ -4500,22 +4354,13 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C106">
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C107">
+      <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C108">
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C109">
-      <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C110">
-      <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C111">
-      <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C112">
-      <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C113">
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4537,7 +4382,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4545,10 +4390,10 @@
     </row>
     <row r="2" spans="1:4" ht="30" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>6</v>

--- a/docs/wip/ICTU-Kwaliteitsaanpak-Checklist.xlsx
+++ b/docs/wip/ICTU-Kwaliteitsaanpak-Checklist.xlsx
@@ -76,7 +76,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Tip: bepaal eerst de status per submaatregel en daarna de status van de hoofdmaatregel.</t>
+          <t>Bepaal a.u.b. de status per submaatregel.</t>
         </r>
       </text>
     </comment>
@@ -204,7 +204,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Tip: bepaal eerst de status per submaatregel en daarna de status van de hoofdmaatregel.</t>
+          <t>Bepaal a.u.b. de status per submaatregel.</t>
         </r>
       </text>
     </comment>
@@ -240,7 +240,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Tip: bepaal eerst de status per submaatregel en daarna de status van de hoofdmaatregel.</t>
+          <t>Bepaal a.u.b. de status per submaatregel.</t>
         </r>
       </text>
     </comment>
@@ -295,7 +295,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Tip: bepaal eerst de status per submaatregel en daarna de status van de hoofdmaatregel.</t>
+          <t>Bepaal a.u.b. de status per submaatregel.</t>
         </r>
       </text>
     </comment>
@@ -395,7 +395,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Tip: bepaal eerst de status per submaatregel en daarna de status van de hoofdmaatregel.</t>
+          <t>Bepaal a.u.b. de status per submaatregel.</t>
         </r>
       </text>
     </comment>
@@ -463,7 +463,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Tip: bepaal eerst de status per submaatregel en daarna de status van de hoofdmaatregel.</t>
+          <t>Bepaal a.u.b. de status per submaatregel.</t>
         </r>
       </text>
     </comment>
@@ -596,7 +596,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Tip: bepaal eerst de status per submaatregel en daarna de status van de hoofdmaatregel.</t>
+          <t>Bepaal a.u.b. de status per submaatregel.</t>
         </r>
       </text>
     </comment>
@@ -732,7 +732,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Tip: bepaal eerst de status per submaatregel en daarna de status van de hoofdmaatregel.</t>
+          <t>Bepaal a.u.b. de status per submaatregel.</t>
         </r>
       </text>
     </comment>
@@ -886,10 +886,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="146">
   <si>
-    <t>Onderstaande checklist kan gebruikt worden voor het uitvoeren van een assessment tegen de ICTU Kwaliteitsaanpak Softwareontwikkeling versie wip, 04-03-2025.</t>
-  </si>
-  <si>
-    <t>Gebruik de 'Status' kolom om aan te geven in hoeverre een maatregel uit de Kwaliteitsaanpak is toegepast. Bij maatregelen met submaatregelen hoeft alleen de status van de submaatregelen te worden ingevuld.</t>
+    <t>Onderstaande checklist kan gebruikt worden voor het uitvoeren van een assessment tegen de ICTU Kwaliteitsaanpak Softwareontwikkeling versie wip, 21-03-2025.</t>
+  </si>
+  <si>
+    <t>Gebruik de 'Status' kolom om aan te geven in hoeverre een maatregel uit de Kwaliteitsaanpak is toegepast. Vul bij maatregelen met submaatregelen alleen de status van de submaatregelen in.</t>
   </si>
   <si>
     <t>Bij maatregelen die primair door een project moeten worden toegepast geeft de status aan in hoevere het project dat doet. Bij maatregelen die primair door ICTU moeten worden toegepast geeft de status aan in hoeverre ICTU dat doet, gezien vanuit het perspectief van het project.</t>
@@ -1379,13 +1379,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFED32D"/>
+        <fgColor rgb="FFFFFFA5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFA5"/>
+        <fgColor rgb="FFFED32D"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1416,14 +1416,14 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" indent="1" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" indent="1" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1822,40 +1822,40 @@
       <c r="B7" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="5"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="4"/>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6" t="s">
+      <c r="A8" s="5"/>
+      <c r="B8" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="5"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="4"/>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6" t="s">
+      <c r="A9" s="5"/>
+      <c r="B9" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="5"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="4"/>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6" t="s">
+      <c r="A10" s="5"/>
+      <c r="B10" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="5"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="4"/>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6" t="s">
+      <c r="A11" s="5"/>
+      <c r="B11" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="7"/>
-      <c r="D11" s="5"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="4"/>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="3" t="s">
@@ -1864,160 +1864,160 @@
       <c r="B12" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="4"/>
-      <c r="D12" s="5"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="4"/>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6" t="s">
+      <c r="A13" s="5"/>
+      <c r="B13" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="7"/>
-      <c r="D13" s="5"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="4"/>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6" t="s">
+      <c r="A14" s="5"/>
+      <c r="B14" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="5"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="4"/>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6" t="s">
+      <c r="A15" s="5"/>
+      <c r="B15" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="7"/>
-      <c r="D15" s="5"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="4"/>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6" t="s">
+      <c r="A16" s="5"/>
+      <c r="B16" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="7"/>
-      <c r="D16" s="5"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="4"/>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6" t="s">
+      <c r="A17" s="5"/>
+      <c r="B17" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="7"/>
-      <c r="D17" s="5"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="4"/>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="6"/>
-      <c r="B18" s="6" t="s">
+      <c r="A18" s="5"/>
+      <c r="B18" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="5"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="4"/>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="6"/>
-      <c r="B19" s="6" t="s">
+      <c r="A19" s="5"/>
+      <c r="B19" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C19" s="7"/>
-      <c r="D19" s="5"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="4"/>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="6"/>
-      <c r="B20" s="6" t="s">
+      <c r="A20" s="5"/>
+      <c r="B20" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="7"/>
-      <c r="D20" s="5"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="4"/>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="6"/>
-      <c r="B21" s="6" t="s">
+      <c r="A21" s="5"/>
+      <c r="B21" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="7"/>
-      <c r="D21" s="5"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="4"/>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="6"/>
-      <c r="B22" s="6" t="s">
+      <c r="A22" s="5"/>
+      <c r="B22" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C22" s="7"/>
-      <c r="D22" s="5"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="4"/>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="6"/>
-      <c r="B23" s="6" t="s">
+      <c r="A23" s="5"/>
+      <c r="B23" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C23" s="7"/>
-      <c r="D23" s="5"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="4"/>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="6"/>
-      <c r="B24" s="6" t="s">
+      <c r="A24" s="5"/>
+      <c r="B24" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C24" s="7"/>
-      <c r="D24" s="5"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="4"/>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="6"/>
-      <c r="B25" s="6" t="s">
+      <c r="A25" s="5"/>
+      <c r="B25" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C25" s="7"/>
-      <c r="D25" s="5"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="4"/>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="6"/>
-      <c r="B26" s="6" t="s">
+      <c r="A26" s="5"/>
+      <c r="B26" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="5"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="4"/>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="6"/>
-      <c r="B27" s="6" t="s">
+      <c r="A27" s="5"/>
+      <c r="B27" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C27" s="7"/>
-      <c r="D27" s="5"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="4"/>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28" s="6"/>
-      <c r="B28" s="6" t="s">
+      <c r="A28" s="5"/>
+      <c r="B28" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C28" s="7"/>
-      <c r="D28" s="5"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="4"/>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="6"/>
-      <c r="B29" s="6" t="s">
+      <c r="A29" s="5"/>
+      <c r="B29" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C29" s="7"/>
-      <c r="D29" s="5"/>
+      <c r="C29" s="6"/>
+      <c r="D29" s="4"/>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="6"/>
-      <c r="B30" s="6" t="s">
+      <c r="A30" s="5"/>
+      <c r="B30" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C30" s="7"/>
-      <c r="D30" s="5"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="4"/>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="6"/>
-      <c r="B31" s="6" t="s">
+      <c r="A31" s="5"/>
+      <c r="B31" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C31" s="7"/>
-      <c r="D31" s="5"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="4"/>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="3" t="s">
@@ -2026,32 +2026,32 @@
       <c r="B32" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C32" s="4"/>
-      <c r="D32" s="5"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="4"/>
     </row>
     <row r="33" spans="1:4">
-      <c r="A33" s="6"/>
-      <c r="B33" s="6" t="s">
+      <c r="A33" s="5"/>
+      <c r="B33" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C33" s="7"/>
-      <c r="D33" s="5"/>
+      <c r="C33" s="6"/>
+      <c r="D33" s="4"/>
     </row>
     <row r="34" spans="1:4">
-      <c r="A34" s="6"/>
-      <c r="B34" s="6" t="s">
+      <c r="A34" s="5"/>
+      <c r="B34" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="C34" s="7"/>
-      <c r="D34" s="5"/>
+      <c r="C34" s="6"/>
+      <c r="D34" s="4"/>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="6"/>
-      <c r="B35" s="6" t="s">
+      <c r="A35" s="5"/>
+      <c r="B35" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C35" s="7"/>
-      <c r="D35" s="5"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="4"/>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="3" t="s">
@@ -2060,56 +2060,56 @@
       <c r="B36" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C36" s="4"/>
-      <c r="D36" s="5"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="4"/>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37" s="6"/>
-      <c r="B37" s="6" t="s">
+      <c r="A37" s="5"/>
+      <c r="B37" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C37" s="7"/>
-      <c r="D37" s="5"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="4"/>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="6"/>
-      <c r="B38" s="6" t="s">
+      <c r="A38" s="5"/>
+      <c r="B38" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C38" s="7"/>
-      <c r="D38" s="5"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="4"/>
     </row>
     <row r="39" spans="1:4">
-      <c r="A39" s="6"/>
-      <c r="B39" s="6" t="s">
+      <c r="A39" s="5"/>
+      <c r="B39" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C39" s="7"/>
-      <c r="D39" s="5"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="4"/>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40" s="6"/>
-      <c r="B40" s="6" t="s">
+      <c r="A40" s="5"/>
+      <c r="B40" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C40" s="7"/>
-      <c r="D40" s="5"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="4"/>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" s="6"/>
-      <c r="B41" s="6" t="s">
+      <c r="A41" s="5"/>
+      <c r="B41" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C41" s="7"/>
-      <c r="D41" s="5"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="4"/>
     </row>
     <row r="42" spans="1:4">
-      <c r="A42" s="6"/>
-      <c r="B42" s="6" t="s">
+      <c r="A42" s="5"/>
+      <c r="B42" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C42" s="7"/>
-      <c r="D42" s="5"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="4"/>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="3" t="s">
@@ -2118,8 +2118,8 @@
       <c r="B43" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C43" s="4"/>
-      <c r="D43" s="5"/>
+      <c r="C43" s="7"/>
+      <c r="D43" s="4"/>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="3" t="s">
@@ -2128,8 +2128,8 @@
       <c r="B44" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C44" s="4"/>
-      <c r="D44" s="5"/>
+      <c r="C44" s="7"/>
+      <c r="D44" s="4"/>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="3" t="s">
@@ -2138,8 +2138,8 @@
       <c r="B45" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C45" s="4"/>
-      <c r="D45" s="5"/>
+      <c r="C45" s="7"/>
+      <c r="D45" s="4"/>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="3" t="s">
@@ -2148,88 +2148,88 @@
       <c r="B46" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C46" s="4"/>
-      <c r="D46" s="5"/>
+      <c r="C46" s="3"/>
+      <c r="D46" s="4"/>
     </row>
     <row r="47" spans="1:4">
-      <c r="A47" s="6"/>
-      <c r="B47" s="6" t="s">
+      <c r="A47" s="5"/>
+      <c r="B47" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C47" s="7"/>
-      <c r="D47" s="5"/>
+      <c r="C47" s="6"/>
+      <c r="D47" s="4"/>
     </row>
     <row r="48" spans="1:4">
-      <c r="A48" s="6"/>
-      <c r="B48" s="6" t="s">
+      <c r="A48" s="5"/>
+      <c r="B48" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="C48" s="7"/>
-      <c r="D48" s="5"/>
+      <c r="C48" s="6"/>
+      <c r="D48" s="4"/>
     </row>
     <row r="49" spans="1:4">
-      <c r="A49" s="6"/>
-      <c r="B49" s="6" t="s">
+      <c r="A49" s="5"/>
+      <c r="B49" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C49" s="7"/>
-      <c r="D49" s="5"/>
+      <c r="C49" s="6"/>
+      <c r="D49" s="4"/>
     </row>
     <row r="50" spans="1:4">
-      <c r="A50" s="6"/>
-      <c r="B50" s="6" t="s">
+      <c r="A50" s="5"/>
+      <c r="B50" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="C50" s="7"/>
-      <c r="D50" s="5"/>
+      <c r="C50" s="6"/>
+      <c r="D50" s="4"/>
     </row>
     <row r="51" spans="1:4">
-      <c r="A51" s="6"/>
-      <c r="B51" s="6" t="s">
+      <c r="A51" s="5"/>
+      <c r="B51" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C51" s="7"/>
-      <c r="D51" s="5"/>
+      <c r="C51" s="6"/>
+      <c r="D51" s="4"/>
     </row>
     <row r="52" spans="1:4">
-      <c r="A52" s="6"/>
-      <c r="B52" s="6" t="s">
+      <c r="A52" s="5"/>
+      <c r="B52" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="C52" s="7"/>
-      <c r="D52" s="5"/>
+      <c r="C52" s="6"/>
+      <c r="D52" s="4"/>
     </row>
     <row r="53" spans="1:4">
-      <c r="A53" s="6"/>
-      <c r="B53" s="6" t="s">
+      <c r="A53" s="5"/>
+      <c r="B53" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="C53" s="7"/>
-      <c r="D53" s="5"/>
+      <c r="C53" s="6"/>
+      <c r="D53" s="4"/>
     </row>
     <row r="54" spans="1:4">
-      <c r="A54" s="6"/>
-      <c r="B54" s="6" t="s">
+      <c r="A54" s="5"/>
+      <c r="B54" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="C54" s="7"/>
-      <c r="D54" s="5"/>
+      <c r="C54" s="6"/>
+      <c r="D54" s="4"/>
     </row>
     <row r="55" spans="1:4">
-      <c r="A55" s="6"/>
-      <c r="B55" s="6" t="s">
+      <c r="A55" s="5"/>
+      <c r="B55" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="C55" s="7"/>
-      <c r="D55" s="5"/>
+      <c r="C55" s="6"/>
+      <c r="D55" s="4"/>
     </row>
     <row r="56" spans="1:4">
-      <c r="A56" s="6"/>
-      <c r="B56" s="6" t="s">
+      <c r="A56" s="5"/>
+      <c r="B56" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C56" s="7"/>
-      <c r="D56" s="5"/>
+      <c r="C56" s="6"/>
+      <c r="D56" s="4"/>
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="3" t="s">
@@ -2238,152 +2238,152 @@
       <c r="B57" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C57" s="4"/>
-      <c r="D57" s="5"/>
+      <c r="C57" s="3"/>
+      <c r="D57" s="4"/>
     </row>
     <row r="58" spans="1:4">
-      <c r="A58" s="6"/>
-      <c r="B58" s="6" t="s">
+      <c r="A58" s="5"/>
+      <c r="B58" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="C58" s="7"/>
-      <c r="D58" s="5"/>
+      <c r="C58" s="6"/>
+      <c r="D58" s="4"/>
     </row>
     <row r="59" spans="1:4">
-      <c r="A59" s="6"/>
-      <c r="B59" s="6" t="s">
+      <c r="A59" s="5"/>
+      <c r="B59" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="C59" s="7"/>
-      <c r="D59" s="5"/>
+      <c r="C59" s="6"/>
+      <c r="D59" s="4"/>
     </row>
     <row r="60" spans="1:4">
-      <c r="A60" s="6"/>
-      <c r="B60" s="6" t="s">
+      <c r="A60" s="5"/>
+      <c r="B60" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="C60" s="7"/>
-      <c r="D60" s="5"/>
+      <c r="C60" s="6"/>
+      <c r="D60" s="4"/>
     </row>
     <row r="61" spans="1:4">
-      <c r="A61" s="6"/>
-      <c r="B61" s="6" t="s">
+      <c r="A61" s="5"/>
+      <c r="B61" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="C61" s="7"/>
-      <c r="D61" s="5"/>
+      <c r="C61" s="6"/>
+      <c r="D61" s="4"/>
     </row>
     <row r="62" spans="1:4">
-      <c r="A62" s="6"/>
-      <c r="B62" s="6" t="s">
+      <c r="A62" s="5"/>
+      <c r="B62" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="C62" s="7"/>
-      <c r="D62" s="5"/>
+      <c r="C62" s="6"/>
+      <c r="D62" s="4"/>
     </row>
     <row r="63" spans="1:4">
-      <c r="A63" s="6"/>
-      <c r="B63" s="6" t="s">
+      <c r="A63" s="5"/>
+      <c r="B63" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="C63" s="7"/>
-      <c r="D63" s="5"/>
+      <c r="C63" s="6"/>
+      <c r="D63" s="4"/>
     </row>
     <row r="64" spans="1:4">
-      <c r="A64" s="6"/>
-      <c r="B64" s="6" t="s">
+      <c r="A64" s="5"/>
+      <c r="B64" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="C64" s="7"/>
-      <c r="D64" s="5"/>
+      <c r="C64" s="6"/>
+      <c r="D64" s="4"/>
     </row>
     <row r="65" spans="1:4">
-      <c r="A65" s="6"/>
-      <c r="B65" s="6" t="s">
+      <c r="A65" s="5"/>
+      <c r="B65" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="C65" s="7"/>
-      <c r="D65" s="5"/>
+      <c r="C65" s="6"/>
+      <c r="D65" s="4"/>
     </row>
     <row r="66" spans="1:4">
-      <c r="A66" s="6"/>
-      <c r="B66" s="6" t="s">
+      <c r="A66" s="5"/>
+      <c r="B66" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="C66" s="7"/>
-      <c r="D66" s="5"/>
+      <c r="C66" s="6"/>
+      <c r="D66" s="4"/>
     </row>
     <row r="67" spans="1:4">
-      <c r="A67" s="6"/>
-      <c r="B67" s="6" t="s">
+      <c r="A67" s="5"/>
+      <c r="B67" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="C67" s="7"/>
-      <c r="D67" s="5"/>
+      <c r="C67" s="6"/>
+      <c r="D67" s="4"/>
     </row>
     <row r="68" spans="1:4">
-      <c r="A68" s="6"/>
-      <c r="B68" s="6" t="s">
+      <c r="A68" s="5"/>
+      <c r="B68" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C68" s="7"/>
-      <c r="D68" s="5"/>
+      <c r="C68" s="6"/>
+      <c r="D68" s="4"/>
     </row>
     <row r="69" spans="1:4">
-      <c r="A69" s="6"/>
-      <c r="B69" s="6" t="s">
+      <c r="A69" s="5"/>
+      <c r="B69" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="C69" s="7"/>
-      <c r="D69" s="5"/>
+      <c r="C69" s="6"/>
+      <c r="D69" s="4"/>
     </row>
     <row r="70" spans="1:4">
-      <c r="A70" s="6"/>
-      <c r="B70" s="6" t="s">
+      <c r="A70" s="5"/>
+      <c r="B70" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="C70" s="7"/>
-      <c r="D70" s="5"/>
+      <c r="C70" s="6"/>
+      <c r="D70" s="4"/>
     </row>
     <row r="71" spans="1:4">
-      <c r="A71" s="6"/>
-      <c r="B71" s="6" t="s">
+      <c r="A71" s="5"/>
+      <c r="B71" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="C71" s="7"/>
-      <c r="D71" s="5"/>
+      <c r="C71" s="6"/>
+      <c r="D71" s="4"/>
     </row>
     <row r="72" spans="1:4">
-      <c r="A72" s="6"/>
-      <c r="B72" s="6" t="s">
+      <c r="A72" s="5"/>
+      <c r="B72" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="C72" s="7"/>
-      <c r="D72" s="5"/>
+      <c r="C72" s="6"/>
+      <c r="D72" s="4"/>
     </row>
     <row r="73" spans="1:4">
-      <c r="A73" s="6"/>
-      <c r="B73" s="6" t="s">
+      <c r="A73" s="5"/>
+      <c r="B73" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="C73" s="7"/>
-      <c r="D73" s="5"/>
+      <c r="C73" s="6"/>
+      <c r="D73" s="4"/>
     </row>
     <row r="74" spans="1:4">
-      <c r="A74" s="6"/>
-      <c r="B74" s="6" t="s">
+      <c r="A74" s="5"/>
+      <c r="B74" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="C74" s="7"/>
-      <c r="D74" s="5"/>
+      <c r="C74" s="6"/>
+      <c r="D74" s="4"/>
     </row>
     <row r="75" spans="1:4">
-      <c r="A75" s="6"/>
-      <c r="B75" s="6" t="s">
+      <c r="A75" s="5"/>
+      <c r="B75" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="C75" s="7"/>
-      <c r="D75" s="5"/>
+      <c r="C75" s="6"/>
+      <c r="D75" s="4"/>
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="3" t="s">
@@ -2392,8 +2392,8 @@
       <c r="B76" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="C76" s="4"/>
-      <c r="D76" s="5"/>
+      <c r="C76" s="7"/>
+      <c r="D76" s="4"/>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="3" t="s">
@@ -2402,8 +2402,8 @@
       <c r="B77" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="C77" s="4"/>
-      <c r="D77" s="5"/>
+      <c r="C77" s="7"/>
+      <c r="D77" s="4"/>
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="1" t="s">
@@ -2420,8 +2420,8 @@
       <c r="B79" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C79" s="4"/>
-      <c r="D79" s="5"/>
+      <c r="C79" s="7"/>
+      <c r="D79" s="4"/>
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="3" t="s">
@@ -2430,8 +2430,8 @@
       <c r="B80" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C80" s="4"/>
-      <c r="D80" s="5"/>
+      <c r="C80" s="7"/>
+      <c r="D80" s="4"/>
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="3" t="s">
@@ -2440,8 +2440,8 @@
       <c r="B81" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C81" s="4"/>
-      <c r="D81" s="5"/>
+      <c r="C81" s="7"/>
+      <c r="D81" s="4"/>
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="3" t="s">
@@ -2450,40 +2450,40 @@
       <c r="B82" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="C82" s="4"/>
-      <c r="D82" s="5"/>
+      <c r="C82" s="3"/>
+      <c r="D82" s="4"/>
     </row>
     <row r="83" spans="1:4">
-      <c r="A83" s="6"/>
-      <c r="B83" s="6" t="s">
+      <c r="A83" s="5"/>
+      <c r="B83" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="C83" s="7"/>
-      <c r="D83" s="5"/>
+      <c r="C83" s="6"/>
+      <c r="D83" s="4"/>
     </row>
     <row r="84" spans="1:4">
-      <c r="A84" s="6"/>
-      <c r="B84" s="6" t="s">
+      <c r="A84" s="5"/>
+      <c r="B84" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="C84" s="7"/>
-      <c r="D84" s="5"/>
+      <c r="C84" s="6"/>
+      <c r="D84" s="4"/>
     </row>
     <row r="85" spans="1:4">
-      <c r="A85" s="6"/>
-      <c r="B85" s="6" t="s">
+      <c r="A85" s="5"/>
+      <c r="B85" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="C85" s="7"/>
-      <c r="D85" s="5"/>
+      <c r="C85" s="6"/>
+      <c r="D85" s="4"/>
     </row>
     <row r="86" spans="1:4">
-      <c r="A86" s="6"/>
-      <c r="B86" s="6" t="s">
+      <c r="A86" s="5"/>
+      <c r="B86" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="C86" s="7"/>
-      <c r="D86" s="5"/>
+      <c r="C86" s="6"/>
+      <c r="D86" s="4"/>
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="3" t="s">
@@ -2492,8 +2492,8 @@
       <c r="B87" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="C87" s="4"/>
-      <c r="D87" s="5"/>
+      <c r="C87" s="7"/>
+      <c r="D87" s="4"/>
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="3" t="s">
@@ -2502,8 +2502,8 @@
       <c r="B88" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="C88" s="4"/>
-      <c r="D88" s="5"/>
+      <c r="C88" s="7"/>
+      <c r="D88" s="4"/>
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="3" t="s">
@@ -2512,8 +2512,8 @@
       <c r="B89" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="C89" s="4"/>
-      <c r="D89" s="5"/>
+      <c r="C89" s="7"/>
+      <c r="D89" s="4"/>
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="3" t="s">
@@ -2522,8 +2522,8 @@
       <c r="B90" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="C90" s="4"/>
-      <c r="D90" s="5"/>
+      <c r="C90" s="7"/>
+      <c r="D90" s="4"/>
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="3" t="s">
@@ -2532,120 +2532,120 @@
       <c r="B91" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="C91" s="4"/>
-      <c r="D91" s="5"/>
+      <c r="C91" s="3"/>
+      <c r="D91" s="4"/>
     </row>
     <row r="92" spans="1:4">
-      <c r="A92" s="6"/>
-      <c r="B92" s="6" t="s">
+      <c r="A92" s="5"/>
+      <c r="B92" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="C92" s="7"/>
-      <c r="D92" s="5"/>
+      <c r="C92" s="6"/>
+      <c r="D92" s="4"/>
     </row>
     <row r="93" spans="1:4">
-      <c r="A93" s="6"/>
-      <c r="B93" s="6" t="s">
+      <c r="A93" s="5"/>
+      <c r="B93" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="C93" s="7"/>
-      <c r="D93" s="5"/>
+      <c r="C93" s="6"/>
+      <c r="D93" s="4"/>
     </row>
     <row r="94" spans="1:4">
-      <c r="A94" s="6"/>
-      <c r="B94" s="6" t="s">
+      <c r="A94" s="5"/>
+      <c r="B94" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="C94" s="7"/>
-      <c r="D94" s="5"/>
+      <c r="C94" s="6"/>
+      <c r="D94" s="4"/>
     </row>
     <row r="95" spans="1:4">
-      <c r="A95" s="6"/>
-      <c r="B95" s="6" t="s">
+      <c r="A95" s="5"/>
+      <c r="B95" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="C95" s="7"/>
-      <c r="D95" s="5"/>
+      <c r="C95" s="6"/>
+      <c r="D95" s="4"/>
     </row>
     <row r="96" spans="1:4">
-      <c r="A96" s="6"/>
-      <c r="B96" s="6" t="s">
+      <c r="A96" s="5"/>
+      <c r="B96" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="C96" s="7"/>
-      <c r="D96" s="5"/>
+      <c r="C96" s="6"/>
+      <c r="D96" s="4"/>
     </row>
     <row r="97" spans="1:4">
-      <c r="A97" s="6"/>
-      <c r="B97" s="6" t="s">
+      <c r="A97" s="5"/>
+      <c r="B97" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="C97" s="7"/>
-      <c r="D97" s="5"/>
+      <c r="C97" s="6"/>
+      <c r="D97" s="4"/>
     </row>
     <row r="98" spans="1:4">
-      <c r="A98" s="6"/>
-      <c r="B98" s="6" t="s">
+      <c r="A98" s="5"/>
+      <c r="B98" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="C98" s="7"/>
-      <c r="D98" s="5"/>
+      <c r="C98" s="6"/>
+      <c r="D98" s="4"/>
     </row>
     <row r="99" spans="1:4">
-      <c r="A99" s="6"/>
-      <c r="B99" s="6" t="s">
+      <c r="A99" s="5"/>
+      <c r="B99" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="C99" s="7"/>
-      <c r="D99" s="5"/>
+      <c r="C99" s="6"/>
+      <c r="D99" s="4"/>
     </row>
     <row r="100" spans="1:4">
-      <c r="A100" s="6"/>
-      <c r="B100" s="6" t="s">
+      <c r="A100" s="5"/>
+      <c r="B100" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="C100" s="7"/>
-      <c r="D100" s="5"/>
+      <c r="C100" s="6"/>
+      <c r="D100" s="4"/>
     </row>
     <row r="101" spans="1:4">
-      <c r="A101" s="6"/>
-      <c r="B101" s="6" t="s">
+      <c r="A101" s="5"/>
+      <c r="B101" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="C101" s="7"/>
-      <c r="D101" s="5"/>
+      <c r="C101" s="6"/>
+      <c r="D101" s="4"/>
     </row>
     <row r="102" spans="1:4">
-      <c r="A102" s="6"/>
-      <c r="B102" s="6" t="s">
+      <c r="A102" s="5"/>
+      <c r="B102" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="C102" s="7"/>
-      <c r="D102" s="5"/>
+      <c r="C102" s="6"/>
+      <c r="D102" s="4"/>
     </row>
     <row r="103" spans="1:4">
-      <c r="A103" s="6"/>
-      <c r="B103" s="6" t="s">
+      <c r="A103" s="5"/>
+      <c r="B103" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="C103" s="7"/>
-      <c r="D103" s="5"/>
+      <c r="C103" s="6"/>
+      <c r="D103" s="4"/>
     </row>
     <row r="104" spans="1:4">
-      <c r="A104" s="6"/>
-      <c r="B104" s="6" t="s">
+      <c r="A104" s="5"/>
+      <c r="B104" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="C104" s="7"/>
-      <c r="D104" s="5"/>
+      <c r="C104" s="6"/>
+      <c r="D104" s="4"/>
     </row>
     <row r="105" spans="1:4">
-      <c r="A105" s="6"/>
-      <c r="B105" s="6" t="s">
+      <c r="A105" s="5"/>
+      <c r="B105" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="C105" s="7"/>
-      <c r="D105" s="5"/>
+      <c r="C105" s="6"/>
+      <c r="D105" s="4"/>
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="3" t="s">
@@ -2654,8 +2654,8 @@
       <c r="B106" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="C106" s="4"/>
-      <c r="D106" s="5"/>
+      <c r="C106" s="7"/>
+      <c r="D106" s="4"/>
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="1" t="s">
@@ -2672,8 +2672,8 @@
       <c r="B108" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="C108" s="4"/>
-      <c r="D108" s="5"/>
+      <c r="C108" s="7"/>
+      <c r="D108" s="4"/>
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="3" t="s">
@@ -2682,8 +2682,8 @@
       <c r="B109" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="C109" s="4"/>
-      <c r="D109" s="5"/>
+      <c r="C109" s="7"/>
+      <c r="D109" s="4"/>
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="3" t="s">
@@ -2692,8 +2692,8 @@
       <c r="B110" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="C110" s="4"/>
-      <c r="D110" s="5"/>
+      <c r="C110" s="7"/>
+      <c r="D110" s="4"/>
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="3" t="s">
@@ -2702,8 +2702,8 @@
       <c r="B111" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="C111" s="4"/>
-      <c r="D111" s="5"/>
+      <c r="C111" s="7"/>
+      <c r="D111" s="4"/>
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="3" t="s">
@@ -2712,8 +2712,8 @@
       <c r="B112" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="C112" s="4"/>
-      <c r="D112" s="5"/>
+      <c r="C112" s="7"/>
+      <c r="D112" s="4"/>
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="3" t="s">
@@ -2722,8 +2722,8 @@
       <c r="B113" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="C113" s="4"/>
-      <c r="D113" s="5"/>
+      <c r="C113" s="7"/>
+      <c r="D113" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -2733,6 +2733,146 @@
     <mergeCell ref="A4:D4"/>
   </mergeCells>
   <conditionalFormatting sqref="C10">
+    <cfRule type="cellIs" dxfId="0" priority="9" operator="equal">
+      <formula>"voldoet"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="10" operator="equal">
+      <formula>"voldoet deels"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="11" operator="equal">
+      <formula>"voldoet niet"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="12" operator="equal">
+      <formula>"niet van toepassing"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C100">
+    <cfRule type="cellIs" dxfId="0" priority="337" operator="equal">
+      <formula>"voldoet"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="338" operator="equal">
+      <formula>"voldoet deels"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="339" operator="equal">
+      <formula>"voldoet niet"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="340" operator="equal">
+      <formula>"niet van toepassing"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C101">
+    <cfRule type="cellIs" dxfId="0" priority="341" operator="equal">
+      <formula>"voldoet"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="342" operator="equal">
+      <formula>"voldoet deels"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="343" operator="equal">
+      <formula>"voldoet niet"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="344" operator="equal">
+      <formula>"niet van toepassing"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C102">
+    <cfRule type="cellIs" dxfId="0" priority="345" operator="equal">
+      <formula>"voldoet"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="346" operator="equal">
+      <formula>"voldoet deels"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="347" operator="equal">
+      <formula>"voldoet niet"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="348" operator="equal">
+      <formula>"niet van toepassing"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C103">
+    <cfRule type="cellIs" dxfId="0" priority="349" operator="equal">
+      <formula>"voldoet"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="350" operator="equal">
+      <formula>"voldoet deels"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="351" operator="equal">
+      <formula>"voldoet niet"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="352" operator="equal">
+      <formula>"niet van toepassing"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C104">
+    <cfRule type="cellIs" dxfId="0" priority="353" operator="equal">
+      <formula>"voldoet"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="354" operator="equal">
+      <formula>"voldoet deels"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="355" operator="equal">
+      <formula>"voldoet niet"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="356" operator="equal">
+      <formula>"niet van toepassing"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C105">
+    <cfRule type="cellIs" dxfId="0" priority="357" operator="equal">
+      <formula>"voldoet"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="358" operator="equal">
+      <formula>"voldoet deels"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="359" operator="equal">
+      <formula>"voldoet niet"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="360" operator="equal">
+      <formula>"niet van toepassing"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C106">
+    <cfRule type="cellIs" dxfId="0" priority="361" operator="equal">
+      <formula>"voldoet"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="362" operator="equal">
+      <formula>"voldoet deels"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="363" operator="equal">
+      <formula>"voldoet niet"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="364" operator="equal">
+      <formula>"niet van toepassing"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C108">
+    <cfRule type="cellIs" dxfId="0" priority="365" operator="equal">
+      <formula>"voldoet"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="366" operator="equal">
+      <formula>"voldoet deels"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="367" operator="equal">
+      <formula>"voldoet niet"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="368" operator="equal">
+      <formula>"niet van toepassing"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C109">
+    <cfRule type="cellIs" dxfId="0" priority="369" operator="equal">
+      <formula>"voldoet"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="370" operator="equal">
+      <formula>"voldoet deels"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="371" operator="equal">
+      <formula>"voldoet niet"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="372" operator="equal">
+      <formula>"niet van toepassing"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C11">
     <cfRule type="cellIs" dxfId="0" priority="13" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -2746,21 +2886,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C100">
-    <cfRule type="cellIs" dxfId="0" priority="369" operator="equal">
-      <formula>"voldoet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="370" operator="equal">
-      <formula>"voldoet deels"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="371" operator="equal">
-      <formula>"voldoet niet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="372" operator="equal">
-      <formula>"niet van toepassing"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C101">
+  <conditionalFormatting sqref="C110">
     <cfRule type="cellIs" dxfId="0" priority="373" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -2774,7 +2900,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C102">
+  <conditionalFormatting sqref="C111">
     <cfRule type="cellIs" dxfId="0" priority="377" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -2788,7 +2914,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C103">
+  <conditionalFormatting sqref="C112">
     <cfRule type="cellIs" dxfId="0" priority="381" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -2802,7 +2928,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C104">
+  <conditionalFormatting sqref="C113">
     <cfRule type="cellIs" dxfId="0" priority="385" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -2816,63 +2942,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C105">
-    <cfRule type="cellIs" dxfId="0" priority="389" operator="equal">
-      <formula>"voldoet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="390" operator="equal">
-      <formula>"voldoet deels"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="391" operator="equal">
-      <formula>"voldoet niet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="392" operator="equal">
-      <formula>"niet van toepassing"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C106">
-    <cfRule type="cellIs" dxfId="0" priority="393" operator="equal">
-      <formula>"voldoet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="394" operator="equal">
-      <formula>"voldoet deels"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="395" operator="equal">
-      <formula>"voldoet niet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="396" operator="equal">
-      <formula>"niet van toepassing"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C108">
-    <cfRule type="cellIs" dxfId="0" priority="397" operator="equal">
-      <formula>"voldoet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="398" operator="equal">
-      <formula>"voldoet deels"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="399" operator="equal">
-      <formula>"voldoet niet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="400" operator="equal">
-      <formula>"niet van toepassing"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C109">
-    <cfRule type="cellIs" dxfId="0" priority="401" operator="equal">
-      <formula>"voldoet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="402" operator="equal">
-      <formula>"voldoet deels"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="403" operator="equal">
-      <formula>"voldoet niet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="404" operator="equal">
-      <formula>"niet van toepassing"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C11">
+  <conditionalFormatting sqref="C13">
     <cfRule type="cellIs" dxfId="0" priority="17" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -2886,63 +2956,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C110">
-    <cfRule type="cellIs" dxfId="0" priority="405" operator="equal">
-      <formula>"voldoet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="406" operator="equal">
-      <formula>"voldoet deels"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="407" operator="equal">
-      <formula>"voldoet niet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="408" operator="equal">
-      <formula>"niet van toepassing"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C111">
-    <cfRule type="cellIs" dxfId="0" priority="409" operator="equal">
-      <formula>"voldoet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="410" operator="equal">
-      <formula>"voldoet deels"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="411" operator="equal">
-      <formula>"voldoet niet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="412" operator="equal">
-      <formula>"niet van toepassing"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C112">
-    <cfRule type="cellIs" dxfId="0" priority="413" operator="equal">
-      <formula>"voldoet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="414" operator="equal">
-      <formula>"voldoet deels"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="415" operator="equal">
-      <formula>"voldoet niet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="416" operator="equal">
-      <formula>"niet van toepassing"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C113">
-    <cfRule type="cellIs" dxfId="0" priority="417" operator="equal">
-      <formula>"voldoet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="418" operator="equal">
-      <formula>"voldoet deels"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="419" operator="equal">
-      <formula>"voldoet niet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="420" operator="equal">
-      <formula>"niet van toepassing"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C12">
+  <conditionalFormatting sqref="C14">
     <cfRule type="cellIs" dxfId="0" priority="21" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -2956,7 +2970,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C13">
+  <conditionalFormatting sqref="C15">
     <cfRule type="cellIs" dxfId="0" priority="25" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -2970,7 +2984,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C14">
+  <conditionalFormatting sqref="C16">
     <cfRule type="cellIs" dxfId="0" priority="29" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -2984,7 +2998,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C15">
+  <conditionalFormatting sqref="C17">
     <cfRule type="cellIs" dxfId="0" priority="33" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -2998,7 +3012,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C16">
+  <conditionalFormatting sqref="C18">
     <cfRule type="cellIs" dxfId="0" priority="37" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3012,7 +3026,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C17">
+  <conditionalFormatting sqref="C19">
     <cfRule type="cellIs" dxfId="0" priority="41" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3026,7 +3040,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C18">
+  <conditionalFormatting sqref="C20">
     <cfRule type="cellIs" dxfId="0" priority="45" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3040,7 +3054,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C19">
+  <conditionalFormatting sqref="C21">
     <cfRule type="cellIs" dxfId="0" priority="49" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3054,7 +3068,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C20">
+  <conditionalFormatting sqref="C22">
     <cfRule type="cellIs" dxfId="0" priority="53" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3068,7 +3082,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C21">
+  <conditionalFormatting sqref="C23">
     <cfRule type="cellIs" dxfId="0" priority="57" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3082,7 +3096,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C22">
+  <conditionalFormatting sqref="C24">
     <cfRule type="cellIs" dxfId="0" priority="61" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3096,7 +3110,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C23">
+  <conditionalFormatting sqref="C25">
     <cfRule type="cellIs" dxfId="0" priority="65" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3110,7 +3124,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C24">
+  <conditionalFormatting sqref="C26">
     <cfRule type="cellIs" dxfId="0" priority="69" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3124,7 +3138,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C25">
+  <conditionalFormatting sqref="C27">
     <cfRule type="cellIs" dxfId="0" priority="73" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3138,7 +3152,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C26">
+  <conditionalFormatting sqref="C28">
     <cfRule type="cellIs" dxfId="0" priority="77" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3152,7 +3166,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C27">
+  <conditionalFormatting sqref="C29">
     <cfRule type="cellIs" dxfId="0" priority="81" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3166,7 +3180,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C28">
+  <conditionalFormatting sqref="C30">
     <cfRule type="cellIs" dxfId="0" priority="85" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3180,7 +3194,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C29">
+  <conditionalFormatting sqref="C31">
     <cfRule type="cellIs" dxfId="0" priority="89" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3194,7 +3208,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C30">
+  <conditionalFormatting sqref="C33">
     <cfRule type="cellIs" dxfId="0" priority="93" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3208,7 +3222,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C31">
+  <conditionalFormatting sqref="C34">
     <cfRule type="cellIs" dxfId="0" priority="97" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3222,7 +3236,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C32">
+  <conditionalFormatting sqref="C35">
     <cfRule type="cellIs" dxfId="0" priority="101" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3236,7 +3250,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C33">
+  <conditionalFormatting sqref="C37">
     <cfRule type="cellIs" dxfId="0" priority="105" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3250,7 +3264,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C34">
+  <conditionalFormatting sqref="C38">
     <cfRule type="cellIs" dxfId="0" priority="109" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3264,7 +3278,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C35">
+  <conditionalFormatting sqref="C39">
     <cfRule type="cellIs" dxfId="0" priority="113" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3278,7 +3292,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C36">
+  <conditionalFormatting sqref="C40">
     <cfRule type="cellIs" dxfId="0" priority="117" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3292,7 +3306,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C37">
+  <conditionalFormatting sqref="C41">
     <cfRule type="cellIs" dxfId="0" priority="121" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3306,7 +3320,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C38">
+  <conditionalFormatting sqref="C42">
     <cfRule type="cellIs" dxfId="0" priority="125" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3320,7 +3334,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C39">
+  <conditionalFormatting sqref="C43">
     <cfRule type="cellIs" dxfId="0" priority="129" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3334,7 +3348,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C40">
+  <conditionalFormatting sqref="C44">
     <cfRule type="cellIs" dxfId="0" priority="133" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3348,7 +3362,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C41">
+  <conditionalFormatting sqref="C45">
     <cfRule type="cellIs" dxfId="0" priority="137" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3362,7 +3376,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C42">
+  <conditionalFormatting sqref="C47">
     <cfRule type="cellIs" dxfId="0" priority="141" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3376,7 +3390,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C43">
+  <conditionalFormatting sqref="C48">
     <cfRule type="cellIs" dxfId="0" priority="145" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3390,7 +3404,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C44">
+  <conditionalFormatting sqref="C49">
     <cfRule type="cellIs" dxfId="0" priority="149" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3404,7 +3418,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C45">
+  <conditionalFormatting sqref="C50">
     <cfRule type="cellIs" dxfId="0" priority="153" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3418,7 +3432,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C46">
+  <conditionalFormatting sqref="C51">
     <cfRule type="cellIs" dxfId="0" priority="157" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3432,7 +3446,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C47">
+  <conditionalFormatting sqref="C52">
     <cfRule type="cellIs" dxfId="0" priority="161" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3446,7 +3460,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C48">
+  <conditionalFormatting sqref="C53">
     <cfRule type="cellIs" dxfId="0" priority="165" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3460,7 +3474,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C49">
+  <conditionalFormatting sqref="C54">
     <cfRule type="cellIs" dxfId="0" priority="169" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3474,7 +3488,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C50">
+  <conditionalFormatting sqref="C55">
     <cfRule type="cellIs" dxfId="0" priority="173" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3488,7 +3502,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C51">
+  <conditionalFormatting sqref="C56">
     <cfRule type="cellIs" dxfId="0" priority="177" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3502,7 +3516,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C52">
+  <conditionalFormatting sqref="C58">
     <cfRule type="cellIs" dxfId="0" priority="181" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3516,7 +3530,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C53">
+  <conditionalFormatting sqref="C59">
     <cfRule type="cellIs" dxfId="0" priority="185" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3530,7 +3544,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C54">
+  <conditionalFormatting sqref="C60">
     <cfRule type="cellIs" dxfId="0" priority="189" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3544,7 +3558,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C55">
+  <conditionalFormatting sqref="C61">
     <cfRule type="cellIs" dxfId="0" priority="193" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3558,7 +3572,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C56">
+  <conditionalFormatting sqref="C62">
     <cfRule type="cellIs" dxfId="0" priority="197" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3572,7 +3586,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C57">
+  <conditionalFormatting sqref="C63">
     <cfRule type="cellIs" dxfId="0" priority="201" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3586,7 +3600,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C58">
+  <conditionalFormatting sqref="C64">
     <cfRule type="cellIs" dxfId="0" priority="205" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3600,7 +3614,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C59">
+  <conditionalFormatting sqref="C65">
     <cfRule type="cellIs" dxfId="0" priority="209" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3614,7 +3628,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C60">
+  <conditionalFormatting sqref="C66">
     <cfRule type="cellIs" dxfId="0" priority="213" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3628,7 +3642,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C61">
+  <conditionalFormatting sqref="C67">
     <cfRule type="cellIs" dxfId="0" priority="217" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3642,7 +3656,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C62">
+  <conditionalFormatting sqref="C68">
     <cfRule type="cellIs" dxfId="0" priority="221" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3656,7 +3670,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C63">
+  <conditionalFormatting sqref="C69">
     <cfRule type="cellIs" dxfId="0" priority="225" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3670,7 +3684,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C64">
+  <conditionalFormatting sqref="C70">
     <cfRule type="cellIs" dxfId="0" priority="229" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3684,7 +3698,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C65">
+  <conditionalFormatting sqref="C71">
     <cfRule type="cellIs" dxfId="0" priority="233" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3698,7 +3712,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C66">
+  <conditionalFormatting sqref="C72">
     <cfRule type="cellIs" dxfId="0" priority="237" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3712,7 +3726,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C67">
+  <conditionalFormatting sqref="C73">
     <cfRule type="cellIs" dxfId="0" priority="241" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3726,7 +3740,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C68">
+  <conditionalFormatting sqref="C74">
     <cfRule type="cellIs" dxfId="0" priority="245" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3740,7 +3754,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C69">
+  <conditionalFormatting sqref="C75">
     <cfRule type="cellIs" dxfId="0" priority="249" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3754,7 +3768,49 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C7">
+  <conditionalFormatting sqref="C76">
+    <cfRule type="cellIs" dxfId="0" priority="253" operator="equal">
+      <formula>"voldoet"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="254" operator="equal">
+      <formula>"voldoet deels"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="255" operator="equal">
+      <formula>"voldoet niet"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="256" operator="equal">
+      <formula>"niet van toepassing"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C77">
+    <cfRule type="cellIs" dxfId="0" priority="257" operator="equal">
+      <formula>"voldoet"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="258" operator="equal">
+      <formula>"voldoet deels"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="259" operator="equal">
+      <formula>"voldoet niet"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="260" operator="equal">
+      <formula>"niet van toepassing"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C79">
+    <cfRule type="cellIs" dxfId="0" priority="261" operator="equal">
+      <formula>"voldoet"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="262" operator="equal">
+      <formula>"voldoet deels"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="263" operator="equal">
+      <formula>"voldoet niet"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="264" operator="equal">
+      <formula>"niet van toepassing"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C8">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3768,49 +3824,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C70">
-    <cfRule type="cellIs" dxfId="0" priority="253" operator="equal">
-      <formula>"voldoet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="254" operator="equal">
-      <formula>"voldoet deels"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="255" operator="equal">
-      <formula>"voldoet niet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="256" operator="equal">
-      <formula>"niet van toepassing"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C71">
-    <cfRule type="cellIs" dxfId="0" priority="257" operator="equal">
-      <formula>"voldoet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="258" operator="equal">
-      <formula>"voldoet deels"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="259" operator="equal">
-      <formula>"voldoet niet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="260" operator="equal">
-      <formula>"niet van toepassing"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C72">
-    <cfRule type="cellIs" dxfId="0" priority="261" operator="equal">
-      <formula>"voldoet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="262" operator="equal">
-      <formula>"voldoet deels"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="263" operator="equal">
-      <formula>"voldoet niet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="264" operator="equal">
-      <formula>"niet van toepassing"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C73">
+  <conditionalFormatting sqref="C80">
     <cfRule type="cellIs" dxfId="0" priority="265" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3824,7 +3838,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C74">
+  <conditionalFormatting sqref="C81">
     <cfRule type="cellIs" dxfId="0" priority="269" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3838,7 +3852,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C75">
+  <conditionalFormatting sqref="C83">
     <cfRule type="cellIs" dxfId="0" priority="273" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3852,7 +3866,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C76">
+  <conditionalFormatting sqref="C84">
     <cfRule type="cellIs" dxfId="0" priority="277" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3866,7 +3880,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C77">
+  <conditionalFormatting sqref="C85">
     <cfRule type="cellIs" dxfId="0" priority="281" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3880,7 +3894,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C79">
+  <conditionalFormatting sqref="C86">
     <cfRule type="cellIs" dxfId="0" priority="285" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3894,7 +3908,49 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C8">
+  <conditionalFormatting sqref="C87">
+    <cfRule type="cellIs" dxfId="0" priority="289" operator="equal">
+      <formula>"voldoet"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="290" operator="equal">
+      <formula>"voldoet deels"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="291" operator="equal">
+      <formula>"voldoet niet"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="292" operator="equal">
+      <formula>"niet van toepassing"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C88">
+    <cfRule type="cellIs" dxfId="0" priority="293" operator="equal">
+      <formula>"voldoet"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="294" operator="equal">
+      <formula>"voldoet deels"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="295" operator="equal">
+      <formula>"voldoet niet"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="296" operator="equal">
+      <formula>"niet van toepassing"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C89">
+    <cfRule type="cellIs" dxfId="0" priority="297" operator="equal">
+      <formula>"voldoet"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="298" operator="equal">
+      <formula>"voldoet deels"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="299" operator="equal">
+      <formula>"voldoet niet"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="300" operator="equal">
+      <formula>"niet van toepassing"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C9">
     <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3908,49 +3964,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C80">
-    <cfRule type="cellIs" dxfId="0" priority="289" operator="equal">
-      <formula>"voldoet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="290" operator="equal">
-      <formula>"voldoet deels"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="291" operator="equal">
-      <formula>"voldoet niet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="292" operator="equal">
-      <formula>"niet van toepassing"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C81">
-    <cfRule type="cellIs" dxfId="0" priority="293" operator="equal">
-      <formula>"voldoet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="294" operator="equal">
-      <formula>"voldoet deels"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="295" operator="equal">
-      <formula>"voldoet niet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="296" operator="equal">
-      <formula>"niet van toepassing"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C82">
-    <cfRule type="cellIs" dxfId="0" priority="297" operator="equal">
-      <formula>"voldoet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="298" operator="equal">
-      <formula>"voldoet deels"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="299" operator="equal">
-      <formula>"voldoet niet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="300" operator="equal">
-      <formula>"niet van toepassing"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C83">
+  <conditionalFormatting sqref="C90">
     <cfRule type="cellIs" dxfId="0" priority="301" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3964,7 +3978,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C84">
+  <conditionalFormatting sqref="C92">
     <cfRule type="cellIs" dxfId="0" priority="305" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3978,7 +3992,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C85">
+  <conditionalFormatting sqref="C93">
     <cfRule type="cellIs" dxfId="0" priority="309" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -3992,7 +4006,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C86">
+  <conditionalFormatting sqref="C94">
     <cfRule type="cellIs" dxfId="0" priority="313" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -4006,7 +4020,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C87">
+  <conditionalFormatting sqref="C95">
     <cfRule type="cellIs" dxfId="0" priority="317" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -4020,7 +4034,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C88">
+  <conditionalFormatting sqref="C96">
     <cfRule type="cellIs" dxfId="0" priority="321" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -4034,7 +4048,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C89">
+  <conditionalFormatting sqref="C97">
     <cfRule type="cellIs" dxfId="0" priority="325" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -4048,21 +4062,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C9">
-    <cfRule type="cellIs" dxfId="0" priority="9" operator="equal">
-      <formula>"voldoet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="10" operator="equal">
-      <formula>"voldoet deels"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="11" operator="equal">
-      <formula>"voldoet niet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="12" operator="equal">
-      <formula>"niet van toepassing"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C90">
+  <conditionalFormatting sqref="C98">
     <cfRule type="cellIs" dxfId="0" priority="329" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -4076,7 +4076,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C91">
+  <conditionalFormatting sqref="C99">
     <cfRule type="cellIs" dxfId="0" priority="333" operator="equal">
       <formula>"voldoet"</formula>
     </cfRule>
@@ -4090,122 +4090,7 @@
       <formula>"niet van toepassing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C92">
-    <cfRule type="cellIs" dxfId="0" priority="337" operator="equal">
-      <formula>"voldoet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="338" operator="equal">
-      <formula>"voldoet deels"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="339" operator="equal">
-      <formula>"voldoet niet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="340" operator="equal">
-      <formula>"niet van toepassing"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C93">
-    <cfRule type="cellIs" dxfId="0" priority="341" operator="equal">
-      <formula>"voldoet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="342" operator="equal">
-      <formula>"voldoet deels"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="343" operator="equal">
-      <formula>"voldoet niet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="344" operator="equal">
-      <formula>"niet van toepassing"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C94">
-    <cfRule type="cellIs" dxfId="0" priority="345" operator="equal">
-      <formula>"voldoet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="346" operator="equal">
-      <formula>"voldoet deels"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="347" operator="equal">
-      <formula>"voldoet niet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="348" operator="equal">
-      <formula>"niet van toepassing"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C95">
-    <cfRule type="cellIs" dxfId="0" priority="349" operator="equal">
-      <formula>"voldoet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="350" operator="equal">
-      <formula>"voldoet deels"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="351" operator="equal">
-      <formula>"voldoet niet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="352" operator="equal">
-      <formula>"niet van toepassing"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C96">
-    <cfRule type="cellIs" dxfId="0" priority="353" operator="equal">
-      <formula>"voldoet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="354" operator="equal">
-      <formula>"voldoet deels"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="355" operator="equal">
-      <formula>"voldoet niet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="356" operator="equal">
-      <formula>"niet van toepassing"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C97">
-    <cfRule type="cellIs" dxfId="0" priority="357" operator="equal">
-      <formula>"voldoet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="358" operator="equal">
-      <formula>"voldoet deels"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="359" operator="equal">
-      <formula>"voldoet niet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="360" operator="equal">
-      <formula>"niet van toepassing"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C98">
-    <cfRule type="cellIs" dxfId="0" priority="361" operator="equal">
-      <formula>"voldoet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="362" operator="equal">
-      <formula>"voldoet deels"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="363" operator="equal">
-      <formula>"voldoet niet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="364" operator="equal">
-      <formula>"niet van toepassing"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C99">
-    <cfRule type="cellIs" dxfId="0" priority="365" operator="equal">
-      <formula>"voldoet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="366" operator="equal">
-      <formula>"voldoet deels"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="367" operator="equal">
-      <formula>"voldoet niet"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="368" operator="equal">
-      <formula>"niet van toepassing"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations count="105">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C7">
-      <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
-    </dataValidation>
+  <dataValidations count="97">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C8">
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
@@ -4218,9 +4103,6 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C11">
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C12">
-      <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C13">
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
@@ -4278,9 +4160,6 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C31">
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C32">
-      <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C33">
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
@@ -4290,9 +4169,6 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C35">
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C36">
-      <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C37">
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
@@ -4320,9 +4196,6 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C45">
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C46">
-      <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C47">
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
@@ -4353,9 +4226,6 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C56">
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C57">
-      <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C58">
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
@@ -4425,9 +4295,6 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C81">
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C82">
-      <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C83">
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
@@ -4450,9 +4317,6 @@
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C90">
-      <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C91">
       <formula1>"voldoet,voldoet deels,voldoet niet,niet van toepassing"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C92">

--- a/docs/wip/ICTU-Kwaliteitsaanpak-Checklist.xlsx
+++ b/docs/wip/ICTU-Kwaliteitsaanpak-Checklist.xlsx
@@ -62,6 +62,7 @@
 Als een DPIA niet nodig is, dan is een verklaring daaromtrent vereist.
 Impact assessment mensenrechten en algoritmes
 Een impact assessment voor mensenrechten bij de inzet van algoritmes is een instrument voor discussie en besluitvorming door overheidsorganen over de ontwikkeling en/of inzet van een algoritmisch systeem. Met een dergelijke impact assessment kan een interdisciplinaire dialoog gevoerd worden tussen relevante partijen bij de afweging om wel of niet een algoritmische toepassing te gaan ontwikkelen. En het helpt om de gekozen ontwikkeling en implementatie vervolgens op een verantwoorde manier te doen. In het IAMA worden verbanden gelegd met relevante regels, instrumenten en toetskaders op het gebied van algoritmen.
+Een IAMA wordt ingezet in alle gevallen waarin een overheidsorgaan overweegt een algoritme te (laten) ontwikkelen, in te kopen, aan te passen en/of in te gaan zetten.
 Zie https://www.rijksoverheid.nl/documenten/rapporten/2021/02/25/impact-assessment-mensenrechten-en-algoritmes.
 Voor meer informatie over het gezamenlijk gebruik van IAMA en DPIA, zie https://www.cip-overheid.nl/media/av0dmahv/20230614-gezamenlijk-gebruik-iama-en-model-dpia-rijksdienst-v1-0.pdf.
 Projectstartarchitectuur en solution architectuur
@@ -487,9 +488,9 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">M23: Het project zorgt voor de aanwezigheid van kennis van en ervaring met de Kwaliteitsaanpak
-De software delivery manager zorgt ervoor dat bij nieuwe projecten wordt gestart met ten minste twee projectleden die bekend zijn met de Kwaliteitsaanpak. Projectleden die nog niet bekend zijn met de Kwaliteitsaanpak krijgen uitleg over de inhoud en achtergrond van de Kwaliteitsaanpak.
+De software delivery manager zorgt ervoor dat bij nieuwe projecten wordt gestart met ten minste twee projectleden die bekend zijn met de Kwaliteitsaanpak. Projectleden, inclusief projectleider, die nog niet bekend zijn met de Kwaliteitsaanpak krijgen uitleg over de inhoud en achtergrond van de Kwaliteitsaanpak.
 Rationale
-Het inzetten van teamleden die bekend zijn met de Kwaliteitsaanpak zorgt voor een soepeler start van een nieuw project omdat zij bekend zijn met de inhoud van de Kwaliteitsaanpak, zoals kwaliteitsnormen en tools, en omdat zij al doende nieuwe teamleden bekend kunnen maken met de Kwaliteitsaanpak.
+Het inzetten van projectleden die bekend zijn met de Kwaliteitsaanpak zorgt voor een soepeler start van een nieuw project omdat zij bekend zijn met de inhoud van de Kwaliteitsaanpak, zoals kwaliteitsnormen en tools, en omdat zij al doende nieuwe projectleden bekend kunnen maken met de Kwaliteitsaanpak.
 </t>
         </r>
       </text>
@@ -816,7 +817,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="138">
   <si>
-    <t>Onderstaande checklist kan gebruikt worden voor het uitvoeren van een assessment tegen de ICTU Kwaliteitsaanpak Softwareontwikkeling versie wip, 11-04-2025.</t>
+    <t>Onderstaande checklist kan gebruikt worden voor het uitvoeren van een assessment tegen de ICTU Kwaliteitsaanpak Softwareontwikkeling versie wip, 19-09-2025.</t>
   </si>
   <si>
     <t>Gebruik de 'Status' kolom om aan te geven in hoeverre een maatregel uit de Kwaliteitsaanpak is toegepast. Vul bij maatregelen met submaatregelen alleen de status van de submaatregelen in.</t>

--- a/docs/wip/ICTU-Kwaliteitsaanpak-Checklist.xlsx
+++ b/docs/wip/ICTU-Kwaliteitsaanpak-Checklist.xlsx
@@ -817,7 +817,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="138">
   <si>
-    <t>Onderstaande checklist kan gebruikt worden voor het uitvoeren van een assessment tegen de ICTU Kwaliteitsaanpak Softwareontwikkeling versie wip, 13-11-2025.</t>
+    <t>Onderstaande checklist kan gebruikt worden voor het uitvoeren van een assessment tegen de ICTU Kwaliteitsaanpak Softwareontwikkeling versie wip, 23-12-2025.</t>
   </si>
   <si>
     <t>Gebruik de 'Status' kolom om aan te geven in hoeverre een maatregel uit de Kwaliteitsaanpak is toegepast. Vul bij maatregelen met submaatregelen alleen de status van de submaatregelen in.</t>

--- a/docs/wip/ICTU-Kwaliteitsaanpak-Checklist.xlsx
+++ b/docs/wip/ICTU-Kwaliteitsaanpak-Checklist.xlsx
@@ -817,7 +817,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="138">
   <si>
-    <t>Onderstaande checklist kan gebruikt worden voor het uitvoeren van een assessment tegen de ICTU Kwaliteitsaanpak Softwareontwikkeling versie wip, 13-11-2025.</t>
+    <t>Onderstaande checklist kan gebruikt worden voor het uitvoeren van een assessment tegen de ICTU Kwaliteitsaanpak Softwareontwikkeling versie wip, 24-12-2025.</t>
   </si>
   <si>
     <t>Gebruik de 'Status' kolom om aan te geven in hoeverre een maatregel uit de Kwaliteitsaanpak is toegepast. Vul bij maatregelen met submaatregelen alleen de status van de submaatregelen in.</t>

--- a/docs/wip/ICTU-Kwaliteitsaanpak-Checklist.xlsx
+++ b/docs/wip/ICTU-Kwaliteitsaanpak-Checklist.xlsx
@@ -63,8 +63,8 @@
 Impact assessment mensenrechten en algoritmes
 Een impact assessment voor mensenrechten bij de inzet van algoritmes is een instrument voor discussie en besluitvorming door overheidsorganen over de ontwikkeling en/of inzet van een algoritmisch systeem. Met een dergelijke impact assessment kan een interdisciplinaire dialoog gevoerd worden tussen relevante partijen bij de afweging om wel of niet een algoritmische toepassing te gaan ontwikkelen. En het helpt om de gekozen ontwikkeling en implementatie vervolgens op een verantwoorde manier te doen. In het IAMA worden verbanden gelegd met relevante regels, instrumenten en toetskaders op het gebied van algoritmen.
 Een IAMA wordt ingezet in alle gevallen waarin een overheidsorgaan overweegt een algoritme te (laten) ontwikkelen, in te kopen, aan te passen en/of in te gaan zetten.
-Zie https://www.rijksoverheid.nl/documenten/rapporten/2021/02/25/impact-assessment-mensenrechten-en-algoritmes.
-Voor meer informatie over het gezamenlijk gebruik van IAMA en DPIA, zie https://www.cip-overheid.nl/media/av0dmahv/20230614-gezamenlijk-gebruik-iama-en-model-dpia-rijksdienst-v1-0.pdf.
+Zie https://www.rijksoverheid.nl/documenten/rapporten/2026/02/16/impact-assessment-mensenrechten-en-algoritmes.
+Voor meer informatie over het gezamenlijk gebruik van IAMA en DPIA, zie https://www.cip-overheid.nl/producten-en-diensten/handreiking-gebruik-iama-samen-met-model-dpia-rijksdienst/.
 Projectstartarchitectuur en solution architectuur
 Een projectstartarchitectuur (PSA) is bedoeld om te borgen dat nieuwe ontwikkelingen en veranderingen in samenhang worden gerealiseerd en passen binnen de toekomstig gewenste informatievoorziening. De PSA is een concreet en doelgericht ICT-architectuurkader waarbinnen het project moet worden uitgevoerd. In de PSA zijn de architectuurvisie, enterprise-architectuur en overige architecturen van de opdrachtgevende organisatie vertaald naar aan het product te stellen eisen. BIA, DPIA en IAMA zijn input voor de PSA. Een PSA bevat in ieder geval de volgende onderwerpen:
 - Een beschrijving van de doelen en ambities waaraan het project bijdraagt en invulling geeft. Dus niet de projectdoelen en -ambitie.
@@ -76,7 +76,7 @@
 - Standaarden en normen (open standaarden van het Forum Standaardisatie en domeinspecifieke standaarden).
 Zie https://www.noraonline.nl/wiki/PSA.
 Conform NORA werkt de opdrachtgevende organisatie na de start van het project de PSA uit in een solution architectuur (SA).
-Zie https://www.noraonline.nl/wiki/Solution-architectuur.
+Zie typen architecturen in NORA.
 Afspraken met de beheerorganisatie
 De opdrachtgevende organisatie heeft afspraken gemaakt met een (interne of externe) beheerorganisatie die voornemens is het beheer van de software uit te voeren. De afspraken omvatten in ieder geval de inzet van medewerkers van de beheerorganisatie tijdens de voorfase en het type beheer dat de beheerorganisatie voornemens is te gaan uitvoeren: operationeel beheer, applicatiebeheer en/of functioneel beheer.
 De beheerorganisatie stelt relevante informatie ter beschikking aan het project zoals beveiligingsbeleid, beheeracceptatiecriteria, documentatie van de te gebruiken voorzieningen voor bijvoorbeeld authenticatie en autorisatie en verder te hanteren kaders en richtlijnen.
@@ -95,7 +95,7 @@
 - NEN-ISO/IEC 25010:2023,
 - Wet beveiliging netwerk- en informatiesystemen (Wbni),
 - Baseline Informatiebeveiliging Overheid (BIO),
-- methode Grip op SDD (Secure Software Development) van het Centrum Informatiebeveiliging en Privacybescherming (CIP),
+- methode Grip op SSD (Secure Software Development) van het Centrum Informatiebeveiliging en Privacybescherming (CIP),
 - Algemene verordening gegevensbescherming (AVG),
 - ISO 9241-210:2019 Ergonomics of human-system interaction - Part 210: Human-centred design for interactive systems,
 - Web Content Accessibility Guidelines versie 2.2, niveau A en AA. Hiermee wordt invulling gegeven aan hoofdstuk 9 van de Europese Standaard EN 301 549 die verwijst naar WCAG versie 2.1,
@@ -743,7 +743,7 @@
 Rationale
 De keuze om het gebruik van een aantal tools verplicht te stellen (M16: Het project gebruikt tools voor vastgestelde taken) volgt uit de belangrijke rol die die tools spelen in de ontwikkelstraat en in Quality-time, het kwaliteitssysteem van ICTU. Met de verplichting komt ook een verantwoordelijkheid: om projecten in staat te stellen snel en effectief met deze tools te werken, moeten die projecten ondersteund worden.
 De verplicht gestelde tools zijn beperkt in aantal, bewezen en gangbaar; veel medewerkers zullen deze tools al kennen.
-De voorkeur voor open source tools is conform de rationale uit NORA (Nederlandse Overheid Referentiearchitectuur) voor het gebruik van open source tools, zoals beschreven in NORA v3.0 drijfveer "Beleid open standaarden". De voorkeur voor het open source beschikbaar stellen van eigen ontwikkelde tools is conform de "Beleidsbrief vrijgeven van de broncode van overheidssoftware" van de staatssecretaris van Binnenlandse Zaken en Koninkrijksrelaties, 17 april 2020.
+De voorkeur voor open source tools is conform het NORA (Nederlandse Overheid Referentiearchitectuur)-architectuurprincipe "Hergebruik vóór kopen vóór maken". De voorkeur voor het open source beschikbaar stellen van eigen ontwikkelde tools is conform de "Beleidsbrief vrijgeven van de broncode van overheidssoftware" van de staatssecretaris van Binnenlandse Zaken en Koninkrijksrelaties, 17 april 2020.
 </t>
         </r>
       </text>
@@ -818,7 +818,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="138">
   <si>
-    <t>Onderstaande checklist kan gebruikt worden voor het uitvoeren van een assessment tegen de ICTU Kwaliteitsaanpak Softwareontwikkeling versie wip, 06-01-2026.</t>
+    <t>Onderstaande checklist kan gebruikt worden voor het uitvoeren van een assessment tegen de ICTU Kwaliteitsaanpak Softwareontwikkeling versie wip, 14-04-2026.</t>
   </si>
   <si>
     <t>Gebruik de 'Status' kolom om aan te geven in hoeverre een maatregel uit de Kwaliteitsaanpak is toegepast. Vul bij maatregelen met submaatregelen alleen de status van de submaatregelen in.</t>

--- a/docs/wip/ICTU-Kwaliteitsaanpak-Checklist.xlsx
+++ b/docs/wip/ICTU-Kwaliteitsaanpak-Checklist.xlsx
@@ -818,7 +818,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="138">
   <si>
-    <t>Onderstaande checklist kan gebruikt worden voor het uitvoeren van een assessment tegen de ICTU Kwaliteitsaanpak Softwareontwikkeling versie wip, 19-06-2026.</t>
+    <t>Onderstaande checklist kan gebruikt worden voor het uitvoeren van een assessment tegen de ICTU Kwaliteitsaanpak Softwareontwikkeling versie wip, 23-06-2026.</t>
   </si>
   <si>
     <t>Gebruik de 'Status' kolom om aan te geven in hoeverre een maatregel uit de Kwaliteitsaanpak is toegepast. Vul bij maatregelen met submaatregelen alleen de status van de submaatregelen in.</t>
